--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0023.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0023.xlsx
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Nhận Shield sẽ tăng Crit. DMG.</t>
+          <t>Nhận Khiên sẽ tăng Crit. DMG.</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Resonator được khiên bảo vệ có Tấn Công tăng lên.</t>
+          <t>Resonator được khiên bảo vệ có ATK tăng lên.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Chuông băng được triệu hồi gây thêm sát thương.</t>
+          <t>Chuông băng được triệu hồi gây thêm DMG.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Resonator đang kích hoạt gây thêm sát thương sau khi hồi phục.</t>
+          <t>Resonator đang kích hoạt gây thêm DMG sau khi hồi phục.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Attack gây thêm sát thương dựa trên HP hiện tại.</t>
+          <t>Tấn Công gây thêm sát thương dựa trên HP hiện tại.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Khi có khiên, tăng DEF.</t>
+          <t>Khi được bảo vệ bởi khiên, Phòng Ngự sẽ tăng lên.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Đánh bại kẻ địch phục hồi HP.</t>
+          <t>Tiêu diệt kẻ địch sẽ hồi phục HP.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng Resonance Liberation, tăng khả năng kháng cự gián đoạn và giảm sát thương nhận vào.</t>
+          <t>Sau khi sử dụng Resonance Liberation, tăng khả năng kháng cự gián đoạn và giảm DMG nhận vào.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Hạ gục kẻ địch phục hồi HP.</t>
+          <t>Hóa Đá kẻ địch sẽ phục hồi HP.</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Tăng DEF.</t>
+          <t>Phòng Ngự được tăng.</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Giảm Cooldown chiêu Resonance Liberation và Resonance Energy tối đa.</t>
+          <t>Giảm Thời gian hồi chiêu Resonance Liberation và Resonance Energy tối đa.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation lập tức đặt lại Cooldown chiêu Resonance Liberation và hồi toàn bộ Resonance Energy.</t>
+          <t>Kích hoạt Resonance Liberation lập tức đặt lại Thời gian hồi chiêu Resonance Liberation và hồi toàn bộ Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Tăng DMG Resonance Liberation.</t>
+          <t>Tăng Sát Thương Giải Cứu Cộng Hưởng.</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Critical Hit hồi phục thêm Resonance Energy.</t>
+          <t>Bạo Kích hồi phục thêm Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Mỗi Basic Attack thực hiện sẽ giảm Cooldown chiêu của Resonance Skill và Resonance Liberation.</t>
+          <t>Mỗi Đòn Basic Attack thực hiện sẽ giảm Thời gian hồi chiêu của Resonance Skill và Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Skill sẽ giảm Cooldown chiêu của Resonance Skill.</t>
+          <t>Kích hoạt Resonance Skill sẽ giảm thời gian hồi chiêu của Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Mỗi đòn Basic Attack trúng đích sẽ hồi phục thêm Resonance Energy.</t>
+          <t>Mỗi đòn Đòn Basic Attack trúng đích sẽ hồi phục thêm Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Critical Hit hồi phục Resonance Energy.</t>
+          <t>Bạo Kích hồi phục Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Resonance Skill tăng Crit. Rate khi trúng đích.</t>
+          <t>Kỹ năng Cộng Hưởng tăng Crit. Rate khi trúng đích.</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Giảm Năng Lượng Cộng Hưởng tối đa.</t>
+          <t>Giảm Resonance Energy tối đa.</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Tăng DMG Resonance Liberation.</t>
+          <t>Tăng Sát Thương Giải Cứu Cộng Hưởng.</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Gây sát thương bằng Kỹ Năng Echo sẽ triệu hồi thêm 3 lần Cơn Gió Đột Kích.</t>
+          <t>Gây DMG bằng Kỹ Năng Echo sẽ triệu hồi thêm 3 lần Cơn Gió Đột Kích.</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Skill Khởi Động còn triệu hồi Luồng Gió 5 lần khi trúng mục tiêu.</t>
+          <t>Kỹ năng Khởi Động còn triệu hồi Luồng Gió 5 lần khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation tăng Sát Thương Kỹ Năng Echo.</t>
+          <t>Kích hoạt Giải Cứu Cộng Hưởng tăng Sát Thương Kỹ Năng Echo.</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Tăng Sát Thương Intro Skill của Đồng Đội Concerto.</t>
+          <t>Tăng Sát Thương Kỹ Năng Khởi Động của Đồng Đội Concerto.</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Dodge Counter phục hồi Concerto Energy và giảm Cooldown chiêu Kỹ Năng Vọng Âm.</t>
+          <t>Dodge Counter phục hồi Năng Lượng Giao Hưởng và giảm Thời gian hồi chiêu Kỹ Năng Vọng Âm.</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Giảm Cooldown chiêu Kỹ Năng Echo.</t>
+          <t>Giảm Thời gian hồi chiêu Kỹ Năng Echo.</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Tăng DMG Kỹ Năng Echo.</t>
+          <t>Tăng Sát Thương Kỹ Năng Echo.</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Critical Hit từ Đồng Hành Concerto tăng Tỷ Lệ Critical Hit và Sát Thương Critical Hit cho Resonator đang hoạt động.</t>
+          <t>Bạo Kích từ Đồng Hành Concerto tăng Crit. Rate và Crit. DMG cho Resonator đang hoạt động.</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Tiêu diệt kẻ địch sẽ giảm Cooldown chiêu Kỹ Năng Echo.</t>
+          <t>Tiêu diệt kẻ địch sẽ giảm Thời gian hồi chiêu Kỹ Năng Echo.</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Kích hoạt Kỹ Năng Echo sẽ tăng Tấn Công.</t>
+          <t>Kích hoạt Kỹ Năng Echo sẽ tăng ATK.</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Kích hoạt Kỹ Năng Echo sẽ tăng Tấn Công.</t>
+          <t>Kích hoạt Kỹ Năng Echo sẽ tăng ATK.</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Status Tiêu Cực lên kẻ địch còn gây thêm hiệu ứng Chaos.</t>
+          <t>Gây Sát Thương Trạng Thái Tiêu Cực lên kẻ địch còn gây thêm hiệu ứng Hỗn Loạn.</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Mỗi khi kẻ địch chịu Sát Thương Status Tiêu Cực, tất cả thành viên trong đội sẽ được hồi HP.</t>
+          <t>Mỗi khi kẻ địch chịu Sát Thương Trạng Thái Tiêu Cực, tất cả thành viên trong đội sẽ được hồi HP.</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Kẻ địch chịu nhiều hơn sát thương từ Spectro Frazzle, Aero Erosion và Fusion Burst.</t>
+          <t>Kẻ địch chịu nhiều hơn DMG từ Spectro Frazzle, Aero Erosion và Fusion Burst.</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Mỗi khi kẻ địch chịu Spectro DMG Frazzle, Aero Erosion hoặc Fusion Burst, Resonator đang hoạt động sẽ hồi Resonance Energy.</t>
+          <t>Mỗi khi kẻ địch chịu Sát Thương Spectro Frazzle, Aero Erosion hoặc Fusion Burst, Resonator đang hoạt động sẽ hồi Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Mỗi tầng Hỗn Độn làm giảm thêm Tấn Công của kẻ địch.</t>
+          <t>Mỗi tầng Hỗn Độn làm giảm thêm ATK của kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Kẻ địch chịu thêm sát thương tương ứng với mỗi loại Status Tiêu Cực mà chúng đang mang.</t>
+          <t>Kẻ địch chịu thêm DMG tương ứng với mỗi loại Trạng Thái Tiêu Cực mà chúng đang mang.</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Resonators bỏ qua một phần Phòng Ngự của kẻ địch.</t>
+          <t>Resonator bỏ qua một phần Phòng Ngự của kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Kẻ địch chịu thêm sát thương khi bị Spectro Frazzle hoặc Aero Erosion.</t>
+          <t>Kẻ địch chịu thêm DMG khi bị Spectro Frazzle hoặc Aero Erosion.</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Mỗi khi kẻ địch chịu Sát Thương Status Tiêu Cực, Resonator đang hoạt động sẽ được hồi HP.</t>
+          <t>Mỗi khi kẻ địch chịu Sát Thương Trạng Thái Tiêu Cực, Resonator đang hoạt động sẽ được hồi HP.</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Basic Attack vào kẻ địch bị Hiệu Ứng Havoc sẽ gây thêm sát thương.</t>
+          <t>Basic Attack vào kẻ địch bị Hiệu Ứng Havoc sẽ gây thêm DMG.</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Vụ Nổ Hợp Thể còn làm giảm Concerto Vibrancy.</t>
+          <t>Gây Sát Thương Vụ Nổ Hợp Thể còn làm giảm Sức Mạnh Rung Động.</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Spectro Frazzle hoặc Erosion Aero giảm Cooldown chiêu Resonance Skill khi gây sát thương.</t>
+          <t>Rối Loạn Spectro hoặc Xói Mòn Aero giảm Thời gian hồi chiêu Resonance Skill khi gây sát thương.</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Skill Concerto giảm Phòng Ngự của kẻ địch mang Tật Havoc khi trúng đòn.</t>
+          <t>Kỹ năng Concerto giảm Phòng Ngự của kẻ địch mang Tật Havoc khi trúng đòn.</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Resonators bỏ qua một phần Phòng Ngự của kẻ địch.</t>
+          <t>Resonator bỏ qua một phần Phòng Ngự của kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Tăng Tấn Công, Phòng Ngự và HP tối đa.</t>
+          <t>Tăng ATK, Phòng Ngự và HP tối đa.</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Resonators bỏ qua một phần Phòng Ngự của kẻ địch cho mỗi Havoc đạt được.</t>
+          <t>Resonator bỏ qua một phần Phòng Ngự của kẻ địch cho mỗi Havoc đạt được.</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Khi sử dụng Kỹ Năng Phá Tune lên kẻ địch, đồng thời kích hoạt thêm Ngọn Giáo Hổ Phách.</t>
+          <t>Khi sử dụng Kỹ Năng Phá Điệu lên kẻ địch, đồng thời kích hoạt thêm Ngọn Giáo Hổ Phách.</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Khi sử dụng Kỹ Năng Phá Tune lên kẻ địch, ngay lập tức loại bỏ khả năng miễn nhiễm trạng thái Lệch Tune và giảm Phòng Ngự của nó.</t>
+          <t>Khi sử dụng Kỹ Năng Phá Điệu lên kẻ địch, ngay lập tức loại bỏ khả năng miễn nhiễm trạng thái Lệch Điệu và giảm Phòng Ngự của nó.</t>
         </is>
       </c>
     </row>
@@ -6492,8 +6492,8 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Khi sử dụng Kỹ Năng Phá Tune lên kẻ địch, gây hiệu ứng Căng Tune - Kích Hoạt.
-Gây sát thương lên kẻ địch đang bị Căng Tune - Kích Hoạt sẽ tăng thêm Crit. DMG.</t>
+          <t>Khi sử dụng Kỹ Năng Phá Điệu lên kẻ địch, gây hiệu ứng Căng Điệu - Kích Hoạt.
+Gây DMG lên kẻ địch đang bị Căng Điệu - Kích Hoạt sẽ tăng thêm Crit. DMG.</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation tăng Tỷ Lệ deplete Vibration Strength và Tấn Công.</t>
+          <t>Kích hoạt Resonance Liberation tăng Tỷ Lệ Giảm Sức Rung và ATK.</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Ngọn Giáo Hổ Phách gây thêm sát thương một lần.</t>
+          <t>Ngọn Giáo Hổ Phách gây thêm DMG một lần.</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Khi sử dụng Kỹ Năng Phá Tune lên kẻ địch, tăng Tấn Công.</t>
+          <t>Khi sử dụng Kỹ Năng Phá Điệu lên kẻ địch, tăng ATK.</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Kẻ địch bị hạ gục chịu nhiều DMG hơn.</t>
+          <t>Kẻ địch bị Hóa Bất Động chịu nhiều DMG hơn.</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Khi sử dụng Kỹ Năng Phá Tune, phục hồi Resonance Energy.</t>
+          <t>Khi sử dụng Kỹ Năng Phá Điệu, phục hồi Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Khi sử dụng Kỹ Năng Phá Tune lên kẻ địch, phục hồi HP.</t>
+          <t>Khi sử dụng Kỹ Năng Phá Điệu lên kẻ địch, phục hồi HP.</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Tăng Off-Tune Level của kẻ địch sẽ gia tăng Tấn Công.</t>
+          <t>Tăng Mức Lệch Tần của kẻ địch sẽ gia tăng ATK.</t>
         </is>
       </c>
     </row>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Tăng Off-Tune Level của kẻ địch sẽ gia tăng Phòng Ngự.</t>
+          <t>Tăng Mức Lệch Tần của kẻ địch sẽ gia tăng Phòng Ngự.</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Tăng thêm Tỷ Lệ deplete Vibration Strength cho Companions Concerto.</t>
+          <t>Tăng thêm Tỷ Lệ Giảm Sức Rung cho Đồng Hành Concerto.</t>
         </is>
       </c>
     </row>
@@ -7469,8 +7469,8 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Gây sát thương bằng Heavy Attack, Resonance Skill hoặc Resonance Liberation sẽ lần lượt nhận được {0}, {1} hoặc {2} tầng Lệnh Quy Hồi.
-Khi đạt {3} tầng Lệnh Quy Hồi, tất cả tầng sẽ được tiêu hao để triệu hồi Sigillum, gây sát thương bằng {4} Attack {5} lần. Cooldown chiêu: {6} giây.</t>
+          <t>Gây DMG bằng Đòn Heavy Attack, Resonance Skill hoặc Resonance Liberation sẽ lần lượt nhận được {0}, {1} hoặc {2} tầng Lệnh Quy Hồi.
+Khi đạt {3} tầng Lệnh Quy Hồi, tất cả tầng sẽ được tiêu hao để triệu hồi Sigillum, gây DMG bằng {4} ATK {5} lần. Thời gian hồi chiêu: {6} giây.</t>
         </is>
       </c>
     </row>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Gây sát thương lên mục tiêu bị Mất Nhịp sẽ gây thêm sát thương bằng {0} Tấn Công {1} lần. Hiệu ứng này chỉ kích hoạt một lần trên mỗi mục tiêu, nhưng có thể làm mới bằng cách gây sát thương Phá Nhịp lên mục tiêu đó.</t>
+          <t>Gây DMG lên mục tiêu bị Mất Nhịp sẽ gây thêm DMG bằng {0} ATK {1} lần. Hiệu ứng này chỉ kích hoạt một lần trên mỗi mục tiêu, nhưng có thể làm mới bằng cách gây DMG Phá Nhịp lên mục tiêu đó.</t>
         </is>
       </c>
     </row>
@@ -7600,7 +7600,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Tune Break Skill khi trúng đích sẽ triệu hồi Sigillum gây sát thương bằng {0} Tấn Công, {1} lần cộng thêm sát thương bằng {2} Tấn Công một lần. Đòn tấn công này sẽ đặt lại Kháng Trạng Thái Mistune của mục tiêu và đẩy Mức Độ Mistune lên tối đa. Cooldown chiêu: {3} giây.</t>
+          <t>Kỹ Năng Phá Tần khi trúng đích sẽ triệu hồi Sigillum gây DMG bằng {0} ATK, {1} lần cộng thêm DMG bằng {2} ATK một lần. Đòn tấn công này sẽ đặt lại Kháng Trạng Thái Lệch Tần của mục tiêu và đẩy Mức Độ Lệch Tần lên tối đa. Thời gian hồi chiêu: {3} giây.</t>
         </is>
       </c>
     </row>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Sigillum nhận {0} DMG Amplification. Mỗi khi Sigillum gây sát thương, Mức Độ Lệch Nhịp của mục tiêu sẽ tăng thêm.</t>
+          <t>Sigillum nhận {0} Khuếch Đại Sát Thương. Mỗi khi Sigillum gây DMG, Mức Độ Lệch Nhịp của mục tiêu sẽ tăng thêm.</t>
         </is>
       </c>
     </row>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Tune Break Skill khi trúng đích sẽ triệu hồi Sigillum tấn công và đẩy Mức Độ Mistune của mục tiêu lên tối đa.</t>
+          <t>Kỹ Năng Phá Tần khi trúng đích sẽ triệu hồi Sigillum tấn công và đẩy Mức Độ Lệch Tần của mục tiêu lên tối đa.</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Sigillum tăng cường Sát Thương Khuếch Đại. Mỗi khi Sigillum gây sát thương, Mức Độ Lệch Nhịp của mục tiêu sẽ tăng thêm.</t>
+          <t>Sigillum tăng cường Sát Thương Khuếch Đại. Mỗi khi Sigillum gây DMG, Mức Độ Lệch Nhịp của mục tiêu sẽ tăng thêm.</t>
         </is>
       </c>
     </row>
@@ -7925,7 +7925,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Kỹ năng Dark Slash gây sát thương thuộc {2} thuộc tính bằng {3} sức tấn công khi trúng mục tiêu. Với mỗi &lt;SapTag=4&gt;{4}&lt;/SapTag&gt; {Cus:Sap,S=cấp P=cấp trạng thái tiêu cực SapTag=4} trạng thái tiêu cực trên mục tiêu, hệ số sát thương của thuộc tính tương ứng trong đòn tấn công này sẽ tăng thêm {5}. Sau đó, kỹ năng sẽ áp đặt {1} cấp của {0} trạng thái tiêu cực khác nhau lên mục tiêu.</t>
+          <t>Kỹ năng Dark Slash gây DMG thuộc {2} thuộc tính bằng {3} sức tấn công khi trúng mục tiêu. Với mỗi &lt;SapTag=4&gt;{4}&lt;/SapTag&gt; {Cus:Sap,S=cấp P=cấp trạng thái tiêu cực SapTag=4} trạng thái tiêu cực trên mục tiêu, hệ số DMG của thuộc tính tương ứng trong đòn tấn công này sẽ tăng thêm {5}. Sau đó, kỹ năng sẽ áp đặt {1} cấp của {0} trạng thái tiêu cực khác nhau lên mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -7990,7 +7990,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Đòn Kiếm Bóng Tối gây thêm Sát Thương bằng {0} Tấn Công và Khuếch Đại Sát Thương Status Tiêu Cực tác động lên mục tiêu thêm {1} trong {2} giây.</t>
+          <t>Đòn Kiếm Bóng Tối gây thêm Sát Thương bằng {0} ATK và Khuếch Đại Sát Thương Trạng Thái Tiêu Cực tác động lên mục tiêu thêm {1} trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Mỗi &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=trạng thái tiêu cực P=trạng thái tiêu cực SapTag=0} gây ra trên mục tiêu sẽ triệu hồi Kẻ Giả Dối Hóa Vương để thi triển Phán Quyết Đại Hồng Thủy, gây sát thương bằng {1} Tấn Công, {2} lần. Hồi chiêu: {3} giây.</t>
+          <t>Mỗi &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=trạng thái tiêu cực P=trạng thái tiêu cực SapTag=0} gây ra trên mục tiêu sẽ triệu hồi Kẻ Giả Dối Hóa Vương để thi triển Phán Quyết Đại Hồng Thủy, gây DMG bằng {1} ATK, {2} lần. Thời gian hồi: {3} giây.</t>
         </is>
       </c>
     </row>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Deluge Judgment gây Sát Thương thuộc tính {0} bằng {1} Tấn Công khi trúng mục tiêu. Với mỗi &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; trạng thái Tiêu Cực trên mục tiêu, Hệ Số Sát Thương thuộc tính tương ứng của đòn tấn công này sẽ tăng thêm {3}.</t>
+          <t>Deluge Judgment gây Sát Thương thuộc tính {0} bằng {1} ATK khi trúng mục tiêu. Với mỗi &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; trạng thái Tiêu Cực trên mục tiêu, Hệ Số Sát Thương thuộc tính tương ứng của đòn tấn công này sẽ tăng thêm {3}.</t>
         </is>
       </c>
     </row>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Đòn Kiếm Bóng Tối gây thêm Sát Thương khi trúng đích. Mục tiêu chịu nhiều Sát Thương hơn với mỗi tầng Status Tiêu Cực. Kỹ năng này còn gây ra nhiều loại Status Tiêu Cực khác nhau.</t>
+          <t>Đòn Kiếm Bóng Tối gây thêm Sát Thương khi trúng đích. Mục tiêu chịu nhiều Sát Thương hơn với mỗi tầng Trạng Thái Tiêu Cực. Kỹ năng này còn gây ra nhiều loại Trạng Thái Tiêu Cực khác nhau.</t>
         </is>
       </c>
     </row>
@@ -8250,7 +8250,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>["Status Tiêu Cực"] False Sovereign giáng mọi loại Status Tiêu Cực lên kẻ địch, gây sát thương khủng khiếp tỉ lệ thuận với tổng số lượt cộng dồn chúng đang mang.</t>
+          <t>["Trạng Thái Tiêu Cực"] False Sovereign giáng mọi loại Trạng Thái Tiêu Cực lên kẻ địch, gây sát thương khủng khiếp tỉ lệ thuận với tổng số lượt cộng dồn chúng đang mang.</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>["Đột Tune Break Số"] Sigillum hỗ trợ chiến đấu, Mistuning nhắm mục tiêu nhanh hơn, và kích hoạt Đột Tune Break Số thường xuyên hơn.</t>
+          <t>["Đột Phá Tần Số"] Sigillum hỗ trợ chiến đấu, Mistuning nhắm mục tiêu nhanh hơn, và kích hoạt Đột Phá Tần Số thường xuyên hơn.</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       <c r="M122" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Electro DMG tăng thêm {0}. Khi Năng Lượng Thăng Hoa đầy và trạng thái Resonance Skill - Ánh Dương Bất Tử chưa kích hoạt, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack trên không để tiêu hao toàn bộ Năng Lượng Thăng Hoa và thi triển Resonance Skill - Ánh Dương Bất Tử: Lao Xuống.</t>
+DMG Electro tăng thêm {0}. Khi Năng Lượng Thăng Hoa đầy và trạng thái Resonance Skill - Ánh Dương Bất Tử chưa kích hoạt, {Cus: Ipt,Touch=tap PC=press Gamepad=press} Normal Attack in mid-air to consume all Ascendancy and cast Resonance Skill - Undying Sunlight: Plunge.</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       <c r="M123" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Nhận Shield sẽ tăng {0} Sát Thương Heavy Attack và giảm {1} Sát Thương nhận vào trong {3} giây, có thể tích lũy tối đa {2} lần.</t>
+Nhận Khiên sẽ tăng {0} Sát Thương Đòn Tấn Công Mạnh và giảm {1} Sát Thương nhận vào trong {3} giây, có thể tích lũy tối đa {2} lần.</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
       <c r="M124" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Electro DMG tăng lên. Khi Năng Lượng Thăng Hoa đầy, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack trên không để tiêu hao toàn bộ Năng Lượng Thăng Hoa và thi triển Resonance Skill - Ánh Dương Bất Tử: Lao Xuống.</t>
+DMG Electro tăng lên. Khi Năng Lượng Thăng Hoa đầy, {Cus: Ipt,Touch=tap PC=press Gamepad=press} Normal Attack in mid-air to consume all Ascendancy and cast Resonance Skill - Undying Sunlight: Plunge.</t>
         </is>
       </c>
     </row>
@@ -8585,7 +8585,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
 - Thực hiện Basic Attack với Moonring sẽ hồi phục &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm Resonance Energy P=điểm Resonance Energy SapTag=0}.
-- Khi tiêu hao Sentience, Basic Attack với Moonbow bắn thêm {1} Mũi Tên Ánh Trăng. Mỗi mũi tên gây Aero DMG bằng {2} Attack và được tính là sát thương Resonance Liberation.</t>
+- Khi tiêu hao Sentience, Basic Attack với Moonbow bắn thêm {1} Mũi Tên Ánh Trăng. Mỗi mũi tên gây DMG Aero bằng {2} ATK và được tính là DMG Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -8652,7 +8652,7 @@
       <c r="M126" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Trong Lãnh Địa Full Moon, Crit. DMG của tất cả Resonators trong đội tăng {0}. Trong {3} giây, họ cũng nhận được Shield mỗi {1} giây bằng {2} Tấn Công của Iuno.</t>
+Trong Lãnh Địa Trăng Tròn, Crit. DMG của tất cả Resonator trong đội tăng {0}. Trong {3} giây, họ cũng nhận được Khiên mỗi {1} giây bằng {2} ATK của Iuno.</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
 - Thực hiện Basic Attack với Moonring sẽ hồi phục thêm {0} điểm Resonance Energy.
-- Khi tiêu hao Sentience, Basic Attack với Moonbow bắn thêm {1} Mũi Tên Ánh Trăng. Mỗi mũi tên gây Aero DMG bằng {2} Attack và được tính là sát thương Resonance Liberation.</t>
+- Khi tiêu hao Sentience, Basic Attack với Moonbow bắn thêm {1} Mũi Tên Ánh Trăng. Mỗi mũi tên gây DMG Aero bằng {2} ATK và được tính là DMG Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -8788,7 +8788,7 @@
       <c r="M128" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Trong Lãnh Địa Full Moon, Crit. DMG của tất cả Resonators trong đội được tăng cường, và họ định kỳ nhận được Shield.</t>
+Trong Lãnh Địa Trăng Tròn, Crit. DMG của tất cả Resonator trong đội được tăng cường, và họ định kỳ nhận được Khiên.</t>
         </is>
       </c>
     </row>
@@ -8855,7 +8855,7 @@
       <c r="M129" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Resonance Skill - Ác Quỷ Thức Tỉnh giảm Fusion RES của kẻ địch {0} trong {1} giây khi trúng đòn.</t>
+Resonance Skill - Ác Quỷ Thức Tỉnh giảm Kháng Fusion của kẻ địch {0} trong {1} giây khi trúng đòn.</t>
         </is>
       </c>
     </row>
@@ -8989,7 +8989,7 @@
       <c r="M131" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Tổng sát thương của Basic Attack - Cú Bắn Tử Thần tăng thêm {0}. Thi triển chiêu này sẽ hồi phục {1} Resonance Energy, kích hoạt &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3} mỗi {2} giây. Nếu Basic Attack này trúng kẻ địch bị Havoc Bane, tăng Crit. Rate thêm {4} trong {5} giây.</t>
+Tổng DMG của Basic Attack - Cú Bắn Tử Thần tăng thêm {0}. Thi triển chiêu này sẽ hồi phục {1} Resonance Energy, kích hoạt &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3} mỗi {2} giây. Nếu Basic Attack này trúng kẻ địch bị Havoc Bane, tăng Crit. Rate thêm {4} trong {5} giây.</t>
         </is>
       </c>
     </row>
@@ -9056,7 +9056,7 @@
       <c r="M132" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Tổng sát thương của Basic Attack - Cú Bắn Tử Thần được tăng lên. Thi triển chiêu này sẽ hồi phục Resonance Energy. Nếu Basic Attack này trúng kẻ địch bị Havoc Bane, tăng Crit. Rate.</t>
+Tổng DMG của Basic Attack - Cú Bắn Tử Thần được tăng lên. Thi triển chiêu này sẽ hồi phục Resonance Energy. Nếu Basic Attack này trúng kẻ địch bị Havoc Bane, tăng Crit. Rate.</t>
         </is>
       </c>
     </row>
@@ -9123,7 +9123,7 @@
       <c r="M133" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; 
-Tăng tái tạo Năng Lượng. Kích hoạt Resonance Liberation sẽ tăng cường Heavy Attack, liên tục gây Sát Thương diện rộng.</t>
+Tăng tái tạo Năng Lượng. Kích hoạt Resonance Liberation sẽ tăng cường Đòn Tấn Công Mạnh, liên tục gây Sát Thương diện rộng.</t>
         </is>
       </c>
     </row>
@@ -9190,7 +9190,7 @@
       <c r="M134" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt;
-Heavy Attack - Mountain Over Thunder và Heavy Attack - Thunder Over Mountain được tăng cường, gây hiệu ứng Electro Flare lên mục tiêu và tăng Electro DMG của Buling.</t>
+Heavy Attack - Mountain Over Thunder và Heavy Attack - Thunder Over Mountain được tăng cường, gây hiệu ứng Electro Flare lên mục tiêu và tăng DMG Electro của Buling.</t>
         </is>
       </c>
     </row>
@@ -9256,8 +9256,8 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Healing]&lt;/color&gt; 
-Khi nhận hồi phục, Buling tạo ra một Bùa tại vị trí của mình, gây sát thương diện rộng.</t>
+          <t>&lt;color=#c49e55&gt;[Hồi Phục]&lt;/color&gt; 
+Khi nhận hồi phục, Buling tạo ra một Bùa tại vị trí của mình, gây DMG diện rộng.</t>
         </is>
       </c>
     </row>
@@ -9324,7 +9324,7 @@
       <c r="M136" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt;
-Heavy Attack - Twin Mountains và Heavy Attack - Twin Thunders được tăng cường, đóng băng kẻ địch và gây Electro DMG đồng thời giảm Electro RES của chúng.</t>
+Heavy Attack - Twin Mountains và Heavy Attack - Twin Thunders được tăng cường, đóng băng kẻ địch và gây DMG Electro đồng thời giảm Kháng Electro của chúng.</t>
         </is>
       </c>
     </row>
@@ -9392,7 +9392,7 @@
       <c r="M137" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-- Basic Attack nhận được tăng cường đặc biệt. Basic Attack Stage 4 có thể tiếp nối bằng Basic Attack Stage 3, tạo ra Trigram - Sơn.
+- Basic Attack nhận được tăng cường đặc biệt. Basic Attack Giai Đoạn 4 có thể tiếp nối bằng Basic Attack Giai Đoạn 3, tạo ra Quẻ - Sơn.
 - Sát Thương Điện Quang được tăng lên.</t>
         </is>
       </c>
@@ -9462,9 +9462,9 @@
       <c r="M138" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-- Nhận {0} Energy Regen. Trong vòng {1} giây sau khi kích hoạt Resonance Liberation - Phép Thuật Sấm Chớp: Hòa Âm, bước vào trạng thái Thiên Sứ Trảm. Thực hiện Heavy Attack trong trạng thái này sẽ tiêu hao {2} HP để tạo ra {3} Mảng Sấm trong {4} giây, gây Electro DMG bằng {6} Attack mỗi {5} giây, được tính là Sát Thương Resonance Liberation. Mảng Sấm liên tục hút mục tiêu xung quanh.
-- Mảng Sấm tạo ra các tia sét ngẫu nhiên gây Electro DMG bằng {7} Attack khi trúng, được tính là Sát Thương Resonance Liberation.
-- Cooldown chiêu của Thiên Sứ Trảm là {8} giây. Hiệu ứng này không tiêu hao HP khi Buling chỉ còn {9} HP.</t>
+- Nhận {0} Hồi Năng Lượng. Trong vòng {1} giây sau khi kích hoạt Resonance Liberation - Phép Thuật Sấm Chớp: Hòa Âm, bước vào trạng thái Thiên Sứ Trảm. Thực hiện Đòn Heavy Attack trong trạng thái này sẽ tiêu hao {2} HP để tạo ra {3} Mảng Sấm trong {4} giây, gây Sát Thương Electro bằng {6} ATK mỗi {5} giây, được tính là Sát Thương Resonance Liberation. Mảng Sấm liên tục hút mục tiêu xung quanh.
+- Mảng Sấm tạo ra các tia sét ngẫu nhiên gây Sát Thương Electro bằng {7} ATK khi trúng, được tính là Sát Thương Resonance Liberation.
+- Thời gian hồi chiêu của Thiên Sứ Trảm là {8} giây. Hiệu ứng này không tiêu hao HP khi Buling chỉ còn {9} HP.</t>
         </is>
       </c>
     </row>
@@ -9531,7 +9531,7 @@
       <c r="M139" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt;
-Heavy Attack - Mountain Over Thunder và Heavy Attack - Thunder Over Mountain có phạm vi hiệu quả lớn hơn, gây &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=0} Electro Flare khi trúng mục tiêu và tăng Electro DMG của Buling thêm {1} trong {3} giây. Hiệu ứng này có thể cộng dồn tối đa {2} lần.</t>
+Heavy Attack - Mountain Over Thunder và Heavy Attack - Thunder Over Mountain có phạm vi hiệu quả lớn hơn, gây &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=0} Electro Flare khi trúng mục tiêu và tăng DMG Electro của Buling thêm {1} trong {3} giây. Hiệu ứng này có thể cộng dồn tối đa {2} lần.</t>
         </is>
       </c>
     </row>
@@ -9598,8 +9598,8 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Healing]&lt;/color&gt; 
-- Khi nhận hồi phục, Buling tạo ra một Bùa Sấm tại vị trí của mình, sau một lúc sẽ gây Electro DMG bằng {0} Tấn Công cho kẻ địch trong phạm vi, được tính là sát thương Năng Lượng Resonance. 
+          <t>&lt;color=#c49e55&gt;[Hồi Phục]&lt;/color&gt; 
+- Khi nhận hồi phục, Buling tạo ra một Bùa Sấm tại vị trí của mình, sau một lúc sẽ gây DMG Electro bằng {0} ATK cho kẻ địch trong phạm vi, được tính là DMG Năng Lượng Cộng Hưởng. 
 - Hiệu ứng này có thể kích hoạt mỗi giây một lần.</t>
         </is>
       </c>
@@ -9667,7 +9667,7 @@
       <c r="M141" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt;
-Thực hiện Heavy Attack - Twin Mountains hoặc Heavy Attack - Twin Thunders sẽ gây hiệu ứng Shock một lần, đóng băng kẻ địch trong phạm vi và gây Electro DMG bằng {0} Attack một lần. Sát thương này được tính là sát thương Heavy Attack và giảm Electro RES của kẻ địch đi {1} trong {3} giây, có thể cộng dồn tối đa {2} lần.</t>
+Thực hiện Heavy Attack - Twin Mountains hoặc Heavy Attack - Twin Thunders sẽ gây hiệu ứng Shock một lần, đóng băng kẻ địch trong phạm vi và gây DMG Electro bằng {0} ATK một lần. DMG này được tính là DMG Heavy Attack và giảm Kháng Electro của kẻ địch đi {1} trong {3} giây, có thể cộng dồn tối đa {2} lần.</t>
         </is>
       </c>
     </row>
@@ -9735,8 +9735,8 @@
       <c r="M142" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-- Sau khi thực hiện Basic Attack - Hexagram Calls, Stage 4 của Lightning Falls, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack để thực hiện Stage 3 của Basic Attack và nhận được một Trigram - Núi.
-- Electro DMG Flare tăng thêm {0}%.</t>
+- Sau khi thực hiện Basic Attack - Hexagram Calls, Giai Đoạn 4 của Lightning Falls, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack để thực hiện Giai Đoạn 3 của Basic Attack và nhận được một Quẻ - Núi.
+- DMG Electro Flare tăng thêm {0}%.</t>
         </is>
       </c>
     </row>
@@ -9803,9 +9803,9 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Plunging Attack]&lt;/color&gt;
-- Thực hiện Đòn Lao Xuống sau Basic Attack - Polychrome Leap, Basic Attack - Iridescent Splash và Basic Attack - Visual Impact sẽ tạo ra Neon Sprays.
-- Sau khi Neon Sprays phát nổ, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack để thực hiện Basic Attack - To a Vivid Tomorrow với hệ số sát thương tăng lên.</t>
+          <t>&lt;color=#c49e55&gt;[Tấn Công Lao Xuống]&lt;/color&gt;
+- Thực hiện Tấn Công Lao Xuống sau Basic Attack - Polychrome Leap, Basic Attack - Iridescent Splash và Basic Attack - Visual Impact sẽ tạo ra Neon Sprays.
+- Sau khi Neon Sprays phát nổ, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack để thực hiện Basic Attack - To a Vivid Tomorrow với hệ số DMG tăng lên.</t>
         </is>
       </c>
     </row>
@@ -9872,7 +9872,7 @@
       <c r="M144" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Sử dụng Resonance Liberation sẽ tạo ra Cyber City - Domain of Yesterday, tăng tốc độ tích lũy Off-Tune của Lynae và giảm Spectro RES của kẻ địch.</t>
+Sử dụng Resonance Liberation sẽ tạo ra Cyber City - Domain of Yesterday, tăng tốc độ tích lũy Off-Tune của Lynae và giảm Kháng Spectro của kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -10140,9 +10140,9 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Plunging Attack]&lt;/color&gt;
-- Thực hiện Đòn Lao Xuống sau Basic Attack - Polychrome Leap, Basic Attack - Iridescent Splash và Basic Attack - Visual Impact sẽ tạo ra {0} Neon Sprays theo ba hướng khác nhau, mỗi hướng gây Spectro DMG bằng {1} Attack, được tính là sát thương Basic Attack.
-- Sau khi Neon Sprays phát nổ, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack để thực hiện Basic Attack - To a Vivid Tomorrow với hệ số sát thương là {2}.</t>
+          <t>&lt;color=#c49e55&gt;[ATK Lao Xuống]&lt;/color&gt;
+- Thực hiện ATK Lao Xuống sau Basic Attack - Polychrome Leap, Basic Attack - Iridescent Splash và Basic Attack - Visual Impact sẽ tạo ra {0} Neon Sprays theo ba hướng khác nhau, mỗi hướng gây Sát Thương Spectro bằng {1} ATK, được tính là DMG Basic Attack.
+- Sau khi Neon Sprays phát nổ, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack để thực hiện Basic Attack - To a Vivid Tomorrow với hệ số DMG là {2}.</t>
         </is>
       </c>
     </row>
@@ -10209,7 +10209,7 @@
       <c r="M149" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Sử dụng Resonance Liberation sẽ tạo ra Cyber City - Domain of Yesterday. Trong phạm vi này, tốc độ tích lũy Off-Tune của Lynae tăng thêm {0} và Spectro RES của kẻ địch giảm {1}.</t>
+Sử dụng Resonance Liberation sẽ tạo ra Cyber City - Domain of Yesterday. Trong phạm vi này, tốc độ tích lũy Off-Tune của Lynae tăng thêm {0} và Kháng Spectro của kẻ địch giảm {1}.</t>
         </is>
       </c>
     </row>
@@ -10276,7 +10276,7 @@
       <c r="M150" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Mỗi đòn Basic Attack - Polychrome Leap tạo ra {0} Cầu Vồng. Mỗi cầu vồng liên tục gây hiệu ứng Dyeing lên kẻ địch gần đó, gây Spectro DMG mỗi giây bằng {1} Attack của Lynae, được tính là Sát Thương Basic Attack. Cầu Vồng tồn tại trong {2} giây và có thể xuất hiện đồng thời.</t>
+Mỗi đòn Basic Attack - Polychrome Leap tạo ra {0} Cầu Vồng. Mỗi cầu vồng liên tục gây hiệu ứng Dyeing lên kẻ địch gần đó, gây Sát Thương Spectro mỗi giây bằng {1} ATK của Lynae, được tính là Sát Thương Basic Attack. Cầu Vồng tồn tại trong {2} giây và có thể xuất hiện đồng thời.</t>
         </is>
       </c>
     </row>
@@ -10410,7 +10410,7 @@
       <c r="M152" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Mỗi {0} điểm Tăng Cường Giai Tune của Lynae sẽ tăng Crit. DMG của cô thêm {1}, tối đa {2}.</t>
+Mỗi {0} điểm Tăng Cường Giai Điệu của Lynae sẽ tăng Crit. DMG của cô thêm {1}, tối đa {2}.</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10544,7 @@
       <c r="M154" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; 
-Trong Wide Field Observation Mode, Mornye triệu hồi Quỹ Tinh tấn công kẻ địch.</t>
+Trong Chế Độ Quan Sát Trường Rộng, Mornye triệu hồi Quỹ Tinh tấn công kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -10612,8 +10612,8 @@
       <c r="M155" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-- Cooldown chiêu của Resonance Liberation được rút ngắn. Nhận Resonance Energy mỗi giây.
-- Sử dụng Resonance Liberation sẽ tạo ra High Syntony Field gây Sát Thương liên tục lên kẻ địch trong phạm vi.</t>
+- Thời gian hồi chiêu của Resonance Liberation được rút ngắn. Nhận Resonance Energy mỗi giây.
+- Sử dụng Resonance Liberation sẽ tạo ra Trường Cộng Hưởng Cao gây Sát Thương liên tục lên kẻ địch trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -10680,7 +10680,7 @@
       <c r="M156" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; 
-Trong Wide Field Observation Mode, DEF của Mornye tăng tương ứng với chỉ số Tấn Công.</t>
+Trong Chế Độ Quan Sát Trường Rộng, DEF của Mornye tăng tương ứng với chỉ số ATK.</t>
         </is>
       </c>
     </row>
@@ -10748,7 +10748,7 @@
       <c r="M157" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-- Resonance Skill và Basic Attack của Mornye gây hiệu ứng Tune Rupture - Shifting lên kẻ địch.
+- Resonance Skill và Đòn Basic Attack của Mornye gây hiệu ứng Tune Rupture - Shifting lên kẻ địch.
 - Tái Tạo Năng Lượng của Mornye tăng Tune Break Boost theo tỷ lệ tương ứng.</t>
         </is>
       </c>
@@ -10817,8 +10817,8 @@
       <c r="M158" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-- Khi Resonance Skill - Expectation Error ở trạng thái Dodge, triệu hồi Pháo Nổi để bắn kẻ địch {0} times, mỗi lần gây Fusion DMG bằng {1} DEF của Mornye, được tính là sát thương Resonance Liberation.
-- Cooldown chiêu của Resonance Skill - Distributed Array giảm {2} giây. Sử dụng kỹ năng này sẽ bổ sung {3} đường Pháo Nổi bắn về phía trước, mỗi lần trúng mục tiêu gây Fusion DMG bằng {4} DEF của Mornye, được tính là sát thương Resonance Liberation.</t>
+- Khi Resonance Skill - Expectation Error ở trạng thái Né Tránh, triệu hồi Pháo Nổi để bắn kẻ địch {0} lần, mỗi lần gây DMG Fusion bằng {1} DEF của Mornye, được tính là DMG Resonance Liberation.
+- Thời gian hồi chiêu của Resonance Skill - Distributed Array giảm {2} giây. Sử dụng kỹ năng này sẽ bổ sung {3} đường Pháo Nổi bắn về phía trước, mỗi lần trúng mục tiêu gây DMG Fusion bằng {4} DEF của Mornye, được tính là DMG Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -10885,7 +10885,7 @@
       <c r="M159" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; 
-Trong Wide Field Observation Mode, Mornye triệu hồi &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; Quỹ Tinh {Cus:Sap,S=Star P=Stars SapTag=1} mỗi {0} giây để tấn công mục tiêu, mỗi lần gây Fusion DMG bằng {2} DEF của Mornye, được tính là Sát Thương Resonance Liberation.</t>
+Trong Chế Độ Quan Sát Trường Rộng, Mornye triệu hồi &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; Quỹ Tinh {Cus:Sap,S=Star P=Stars SapTag=1} mỗi {0} giây để tấn công mục tiêu, mỗi lần gây Sát Thương Fusion bằng {2} DEF của Mornye, được tính là Sát Thương Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -10953,8 +10953,8 @@
       <c r="M160" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-- Cooldown chiêu của Resonance Liberation giảm {0} giây. Nhận &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=1} Resonance Energy mỗi giây.
-- Sử dụng Resonance Liberation sẽ tạo ra High Syntony Field. Kẻ địch trong trường này sẽ bị ảnh hưởng bởi hiệu ứng Sóng Xung Kích, chịu Fusion DMG tương đương {2} Phòng Ngự của Mornye mỗi giây, được tính là Sát Thương Resonance Liberation. Khi tấn công kẻ địch chịu hiệu ứng Sóng Xung Kích, Mornye gây thêm {3} tổng Sát Thương.</t>
+- Thời gian hồi chiêu của Resonance Liberation giảm {0} giây. Nhận &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=1} Resonance Energy mỗi giây.
+- Sử dụng Resonance Liberation sẽ tạo ra Trường Cộng Hưởng Cao. Kẻ địch trong trường này sẽ bị ảnh hưởng bởi hiệu ứng Sóng Xung Kích, chịu Sát Thương Fusion tương đương {2} Phòng Ngự của Mornye mỗi giây, được tính là Sát Thương Resonance Liberation. Khi tấn công kẻ địch chịu hiệu ứng Sóng Xung Kích, Mornye gây thêm {3} tổng Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       <c r="M161" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; 
-Trong Wide Field Observation Mode, mỗi &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=0} DEF của Mornye tăng &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=1} Tấn Công.</t>
+Trong Chế Độ Quan Sát Trường Rộng, mỗi &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=0} DEF của Mornye tăng &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=1} ATK.</t>
         </is>
       </c>
     </row>
@@ -11089,7 +11089,7 @@
       <c r="M162" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-- Resonance Skill và Basic Attack Giai đoạn 4 của Mornye gây hiệu ứng Tune Rupture - Shifting lên kẻ địch.
+- Resonance Skill và Đòn Basic Attack Giai đoạn 4 của Mornye gây hiệu ứng Tune Rupture - Shifting lên kẻ địch.
 - Mỗi {0} Tái Tạo Năng Lượng của Mornye tăng Tune Break Boost lên {1}, tối đa {2}.</t>
         </is>
       </c>
@@ -11157,7 +11157,7 @@
       <c r="M163" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt;
-Basic Attack, Dodge Counter hoặc Sync Strike khi trúng mục tiêu sẽ cộng thêm Synchronization Rate, từ đó nhận Starlight theo tỷ lệ. Tiêu hao lượng Starlight để sử dụng Starlight Resonance hoặc Starlight Ember, không thể bị gián đoạn và tăng Resonance Rate.</t>
+Basic Attack, Dodge Counter Tránh hoặc Sync Strike khi trúng mục tiêu sẽ cộng thêm Tỷ Lệ Đồng Bộ, từ đó nhận Starlight theo tỷ lệ. Tiêu hao lượng Starlight để sử dụng Starlight Resonance hoặc Starlight Ember, không thể bị gián đoạn và tăng Resonance Rate.</t>
         </is>
       </c>
     </row>
@@ -11224,7 +11224,7 @@
       <c r="M164" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Nhận được Tần Số Resonance sẽ giảm Cooldown chiêu Resonance Liberation và tăng thưởng Fusion DMG cùng Sát Thương Resonance Liberation.</t>
+Nhận được Tần Số Cộng Hưởng sẽ giảm Thời gian hồi chiêu Resonance Liberation và tăng thưởng Sát Thương Fusion cùng Sát Thương Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -11358,7 +11358,7 @@
       <c r="M166" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Resonance Skill - Sát thương Duet Thiên Thần được khuếch đại, nhưng tiêu hao gấp đôi Synchronization Rate.</t>
+Resonance Skill - DMG Duet Thiên Thần được khuếch đại, nhưng tiêu hao gấp đôi Tỷ Lệ Đồng Bộ.</t>
         </is>
       </c>
     </row>
@@ -11425,7 +11425,7 @@
       <c r="M167" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Sát thương Đồng Bộ Attack được khuếch đại. Sau khi thực hiện Đồng Bộ Attack, sát thương của Basic Attack, Dodge Counter, Resonance Sao và Than Hồng Sao được khuếch đại.</t>
+DMG Đồng Bộ Tấn Công được khuếch đại. Sau khi thực hiện Đồng Bộ Tấn Công, DMG của Đòn Basic Attack, Dodge Counter Tránh, Cộng Hưởng Sao và Than Hồng Sao được khuếch đại.</t>
         </is>
       </c>
     </row>
@@ -11494,11 +11494,11 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt;
-- Basic Attack, Dodge Counter hoặc Sync Strike trúng mục tiêu sẽ cộng thêm Synchronization Rate. Mỗi {0} điểm Synchronization Rate nhận được sẽ cộng &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm} Sao Quang.
-- Ở Dạng Aemeath, Đòn Trọng được thay thế bằng Resonance Sao Quang. Tiêu hao {2} điểm Sao Quang để sử dụng Resonance Sao Quang và nhận {3} điểm Resonance Rate, gây Fusion DMG bằng {4} Attack, được tính là sát thương Năng Lượng Resonance.
-- Ở Dạng Cơ Khí, Đòn Trọng được thay thế bằng Than Hồng Sao Quang. Tiêu hao {5} điểm Sao Quang để sử dụng Than Hồng Sao Quang và nhận {6} điểm Resonance Rate, gây Fusion DMG bằng {7} Attack, được tính là sát thương Năng Lượng Resonance.
-- Khi Đòn Trọng đang tích năng, Resonance Sao Quang và Than Hồng Sao Quang không bị gián đoạn. Sao Quang có thể tích lũy tối đa {8} lần. Nếu nhận được Sao Quang trong trạng thái Phản Ứng Tức Thì, Phản Ứng Tức Thì sẽ được ưu tiên hơn Sao Quang.</t>
+          <t>&lt;color=#c49e55&gt;[Đòn Trọng]&lt;/color&gt;
+- Đòn Cơ Bản, Dodge Counter Tránh hoặc Đòn Đồng Bộ trúng mục tiêu sẽ cộng thêm Tỷ Lệ Đồng Bộ. Mỗi {0} điểm Tỷ Lệ Đồng Bộ nhận được sẽ cộng &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm} Sao Quang.
+- Ở Dạng Aemeath, Đòn Trọng được thay thế bằng Cộng Hưởng Sao Quang. Tiêu hao {2} điểm Sao Quang để sử dụng Cộng Hưởng Sao Quang và nhận {3} điểm Tỷ Lệ Cộng Hưởng, gây DMG Fusion bằng {4} ATK, được tính là DMG Năng Lượng Cộng Hưởng.
+- Ở Dạng Cơ Khí, Đòn Trọng được thay thế bằng Than Hồng Sao Quang. Tiêu hao {5} điểm Sao Quang để sử dụng Than Hồng Sao Quang và nhận {6} điểm Tỷ Lệ Cộng Hưởng, gây DMG Fusion bằng {7} ATK, được tính là DMG Năng Lượng Cộng Hưởng.
+- Khi Đòn Trọng đang tích năng, Cộng Hưởng Sao Quang và Than Hồng Sao Quang không bị gián đoạn. Sao Quang có thể tích lũy tối đa {8} lần. Nếu nhận được Sao Quang trong trạng thái Phản Ứng Tức Thì, Phản Ứng Tức Thì sẽ được ưu tiên hơn Sao Quang.</t>
         </is>
       </c>
     </row>
@@ -11565,7 +11565,7 @@
       <c r="M169" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Mỗi lần nhận được Tần Số Resonance, Cooldown chiêu của Resonance Liberation - Thiên Lệnh Phán Quyết: Quá Tải sẽ giảm {0} giây. Đồng thời nhận được Lời Nguyện Ước Tốt Đẹp, tăng {1} Fusion DMG và {2} Sát Thương Resonance Liberation, có thể chồng chất lên đến {3} lần. Sử dụng Thiên Lệnh Phán Quyết: Đoạn Kết sẽ loại bỏ hiệu ứng này.</t>
+Mỗi lần nhận được Tần Số Cộng Hưởng, Thời gian hồi chiêu của Resonance Liberation - Thiên Lệnh Phán Quyết: Overdrive is reduced by {0}s. Additionally, obtain Good Wish, which grants {1} Fusion DMG Bonus and {2} Resonance Liberation DMG Bonus, stacking up to {3} times. Casting Heavenfall Edict: Finale removes this effect.</t>
         </is>
       </c>
     </row>
@@ -11635,8 +11635,8 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; 
 Cộng hưởng Sao và Than Sao được tăng cường.
-- Ở dạng Aemeath: Sử dụng Cộng hưởng Sao sẽ triệu hồi Mech tấn công, gây Fusion DMG bằng {0} Attack.
-- Ở dạng Mech: Sử dụng Than Sao sẽ triệu hồi Aemeath tấn công, gây Fusion DMG bằng {1} Attack.</t>
+- Ở dạng Aemeath: Sử dụng Cộng hưởng Sao sẽ triệu hồi Mech tấn công, gây Sát Thương Fusion bằng {0} ATK.
+- Ở dạng Mech: Sử dụng Than Sao sẽ triệu hồi Aemeath tấn công, gây Sát Thương Fusion bằng {1} ATK.</t>
         </is>
       </c>
     </row>
@@ -11703,7 +11703,7 @@
       <c r="M171" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Resonance Skill - Sát thương Duet Thiên Thần được khuếch đại thêm {0}, nhưng tiêu hao gấp đôi Synchronization Rate.</t>
+Resonance Skill - DMG Duet Thiên Thần được khuếch đại thêm {0}, nhưng tiêu hao gấp đôi Tỷ Lệ Đồng Bộ.</t>
         </is>
       </c>
     </row>
@@ -11770,7 +11770,7 @@
       <c r="M172" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Sát thương Đồng Bộ Tấn Công được khuếch đại thêm {0}. Sau khi Aemeath hoặc Mech thực hiện Đồng Bộ Tấn Công, sát thương của Basic Attack, Dodge Counter, Resonance Sao và Than Hồng Sao được khuếch đại thêm {1} trong {2} giây.</t>
+DMG Đồng Bộ Tấn Công được khuếch đại thêm {0}. Sau khi Aemeath hoặc Mech thực hiện Đồng Bộ Tấn Công, DMG của Đòn Basic Attack, Dodge Counter Tránh, Cộng Hưởng Sao và Than Hồng Sao được khuếch đại thêm {1} trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -11837,9 +11837,9 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Mid-air Attack]&lt;/color&gt;
+          <t>&lt;color=#c49e55&gt;[Đòn Tấn Công Giữa Không]&lt;/color&gt;
 - Luuk Herrsen không tiêu hao thể lực khi thực hiện bất kỳ hành động nào.
-- Sau khi thực hiện Giai đoạn 3 của Đòn Mid-air Attack, tiếp tục thực hiện Giai đoạn 1. Đòn Mid-air Attack - Gavel of Earthshaker gây sát thương tăng thêm dựa trên thời gian ở trên không.</t>
+- Sau khi thực hiện Giai đoạn 3 của Đòn Tấn Công Giữa Không, tiếp tục thực hiện Giai đoạn 1. Đòn Tấn Công Giữa Không - Gavel of Earthshaker gây DMG tăng thêm dựa trên thời gian ở trên không.</t>
         </is>
       </c>
     </row>
@@ -11973,7 +11973,7 @@
       <c r="M175" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Chịu sát thương không làm tiêu hao tầng Bình Minh Giữ Lại. Nhận hiệu ứng khuếch đại Sát Thương Basic Attack dựa trên số tầng Bình Minh Giữ Lại đang có. Lưỡi Kiếm Ichor tạo ra từ Dodge Giữa Không giờ đây có thể kích hoạt Dodge Counter.</t>
+Chịu DMG không làm tiêu hao tầng Bình Minh Giữ Lại. Nhận hiệu ứng khuếch đại Sát Thương Đòn Basic Attack dựa trên số tầng Bình Minh Giữ Lại đang có. Lưỡi Kiếm Ichor tạo ra từ Né Tránh Giữa Không giờ đây có thể kích hoạt Dodge Counter Tránh.</t>
         </is>
       </c>
     </row>
@@ -12039,8 +12039,8 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Mid-air Attack]&lt;/color&gt; 
-Mid-air Attack bắt đầu từ Stage 2. Sử dụng các lưỡi hái khác nhau sẽ tăng Spectro DMG.</t>
+          <t>&lt;color=#c49e55&gt;[Tấn Công Giữa Không]&lt;/color&gt; 
+Tấn Công Giữa Không bắt đầu từ Giai Đoạn 2. Sử dụng các lưỡi hái khác nhau sẽ tăng Sát Thương Spectro.</t>
         </is>
       </c>
     </row>
@@ -12109,7 +12109,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
 - Nhận hồi năng lượng.
-- Kích hoạt Vòng Hào Quang Hành Quyết sẽ khuếch đại sát thương của Resonance Liberation - Viết Lại Trong Biên Giới Mùa Đông.</t>
+- Kích hoạt Vòng Hào Quang Hành Quyết sẽ khuếch đại DMG của Resonance Liberation - Viết Lại Trong Biên Giới Mùa Đông.</t>
         </is>
       </c>
     </row>
@@ -12177,10 +12177,10 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Mid-air Attack]&lt;/color&gt;
+          <t>&lt;color=#c49e55&gt;[Đòn Tấn Công Giữa Không]&lt;/color&gt;
 - Luuk Herrsen không tiêu hao thể lực khi thực hiện bất kỳ hành động nào.
-- Sau khi thực hiện Stage {0} của Đòn Mid-air Attack, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack để thực hiện Giai đoạn {1}.
-- Luuk Herrsen nhận hiệu ứng Golden Proof khi ở trên không. Khi hiệu ứng này còn hiệu lực, Đòn Mid-air Attack - Gavel of Earthshaker gây thêm {3} sát thương sau mỗi {2} giây trên không, tối đa {4} lần cộng dồn. Hạ cánh hoặc sử dụng Đòn Mid-air Attack - Gavel of Earthshaker sẽ loại bỏ hiệu ứng này.</t>
+- Sau khi thực hiện Giai đoạn {0} của Đòn Tấn Công Giữa Không, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Đòn Normal Attack để thực hiện Giai đoạn {1}.
+- Luuk Herrsen nhận hiệu ứng Golden Proof khi ở trên không. Khi hiệu ứng này còn hiệu lực, Đòn Tấn Công Giữa Không - Gavel of Earthshaker gây thêm {3} DMG sau mỗi {2} giây trên không, tối đa {4} lần cộng dồn. Hạ cánh hoặc sử dụng Đòn Tấn Công Giữa Không - Gavel of Earthshaker sẽ loại bỏ hiệu ứng này.</t>
         </is>
       </c>
     </row>
@@ -12249,9 +12249,9 @@
       <c r="M179" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-- Trạng thái Thẩm Phán Hoàng Kim được kích hoạt vĩnh viễn. Trong trạng thái này, Vòng Trừng Phạt: Chuông sẽ hút mục tiêu xung quanh, và Vòng Trừng Phạt: Đột Phá được thay thế bằng một đòn xoay tấn công phạm vi rộng, có thể đánh trúng tối đa {0} times, mỗi lần gây Spectro DMG bằng {1} sức tấn công. Luuk Herssen có thể di chuyển tự do trong đòn tấn công này, nhưng Kiếm Ichor sẽ không còn được phóng đi.
-- Vòng Trừng Phạt: Ánh Sáng có thể sử dụng tối đa {2} lần, mỗi lần gây Spectro DMG bằng {3} sức tấn công. Kiếm Ichor Rắn Chắc khi phóng đi có thể kích nổ Kho Ichor, gây Spectro DMG bằng {4} sức tấn công.
-- Thực hiện Đòn Mid-air Attack - Búa Địa Chấn sẽ thiết lập lại chuỗi kỹ năng Vòng Trừng Phạt.</t>
+- Trạng thái Thẩm Phán Hoàng Kim được kích hoạt vĩnh viễn. Trong trạng thái này, Vòng Trừng Phạt: Chuông sẽ hút mục tiêu xung quanh, và Vòng Trừng Phạt: Đột Phá được thay thế bằng một đòn xoay tấn công phạm vi rộng, có thể đánh trúng tối đa {0} lần, mỗi lần gây DMG Spectro bằng {1} sức tấn công. Luuk Herssen có thể di chuyển tự do trong đòn tấn công này, nhưng Kiếm Ichor sẽ không còn được phóng đi.
+- Vòng Trừng Phạt: Ánh Sáng có thể sử dụng tối đa {2} lần, mỗi lần gây DMG Spectro bằng {3} sức tấn công. Kiếm Ichor Rắn Chắc khi phóng đi có thể kích nổ Kho Ichor, gây DMG Spectro bằng {4} sức tấn công.
+- Thực hiện Đòn ATK Giữa Không - Búa Địa Chấn sẽ thiết lập lại chuỗi kỹ năng Vòng Trừng Phạt.</t>
         </is>
       </c>
     </row>
@@ -12318,7 +12318,7 @@
       <c r="M180" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Chịu sát thương không làm tiêu hao tầng Dawn Giữ Lại. Mỗi &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=tầng P=tầng SapTag=0} Dawn Giữ Lại sẽ cấp &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=tầng P=tầng SapTag=1} Dawn Lại, khuếch đại Sát Thương Basic Attack lên {2}. Lưỡi Kiếm Ichor tạo ra từ Dodge Giữa Không giờ đây có thể kích hoạt Dodge Counter.</t>
+Chịu DMG không làm tiêu hao tầng Bình Minh Giữ Lại. Mỗi &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=tầng P=tầng SapTag=0} Bình Minh Giữ Lại sẽ cấp &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=tầng P=tầng SapTag=1} Bình Minh Lại, khuếch đại Sát Thương Đòn Basic Attack lên {2}. Lưỡi Kiếm Ichor tạo ra từ Né Tránh Giữa Không giờ đây có thể kích hoạt Dodge Counter Tránh.</t>
         </is>
       </c>
     </row>
@@ -12384,8 +12384,8 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Mid-air Attack]&lt;/color&gt; 
-Mid-air Attack bắt đầu từ Giai Đoạn {0}. Sử dụng các lưỡi hái khác nhau giữa Giai Đoạn {1} và Giai Đoạn {2} sẽ tăng {3} Spectro DMG trong {4} giây, có thể cộng dồn tối đa {5} lần.</t>
+          <t>&lt;color=#c49e55&gt;[Tấn Công Giữa Không]&lt;/color&gt; 
+Tấn Công Giữa Không bắt đầu từ Giai Đoạn {0}. Sử dụng các lưỡi hái khác nhau giữa Giai Đoạn {1} và Giai Đoạn {2} sẽ tăng {3} Sát Thương Spectro trong {4} giây, có thể cộng dồn tối đa {5} lần.</t>
         </is>
       </c>
     </row>
@@ -12454,7 +12454,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
 - Nhận hồi {0} năng lượng.
-- Kích hoạt bất kỳ hình thức Vòng Hào Quang Hành Quyết nào sẽ nhận 1 tầng Ánh Sáng Ban Ngày, khuếch đại sát thương của Resonance Liberation - Viết Lại Trong Biên Giới Mùa Đông thêm {1}, tối đa {2} tầng. Kích hoạt Resonance Liberation - Viết Lại Trong Biên Giới Mùa Đông sẽ xóa hiệu ứng này.</t>
+- Kích hoạt bất kỳ hình thức Vòng Hào Quang Hành Quyết nào sẽ nhận 1 tầng Ánh Sáng Ban Ngày, khuếch đại DMG của Resonance Liberation - Viết Lại Trong Biên Giới Mùa Đông thêm {1}, tối đa {2} tầng. Kích hoạt Resonance Liberation - Viết Lại Trong Biên Giới Mùa Đông sẽ xóa hiệu ứng này.</t>
         </is>
       </c>
     </row>
@@ -12584,7 +12584,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Mở Thiết bị đầu cuối Resonance ở Hồng Trấn</t>
+          <t>Mở Thiết bị đầu cuối Cộng Hưởng ở Hongzhen</t>
         </is>
       </c>
     </row>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Mở khóa Đèn Hiệu Cộng Hưởng Nhỏ tại đầu rồng của Loong's Crest.</t>
+          <t>Mở khóa Đèn Cộng Hưởng Nhỏ tại đầu rồng của Loong's Crest.</t>
         </is>
       </c>
     </row>
@@ -12844,7 +12844,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Sử dụng bất kỳ Bình Thuốc nào 20 lần.</t>
+          <t>Dùng 20 Lọ Thuốc bất kỳ.</t>
         </is>
       </c>
     </row>
@@ -12909,7 +12909,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Sử dụng bất kỳ Bình Thuốc nào 50 lần.</t>
+          <t>Dùng 50 Lọ Thuốc bất kỳ.</t>
         </is>
       </c>
     </row>
@@ -12974,7 +12974,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Sử dụng bất kỳ Bình Thuốc nào 100 lần.</t>
+          <t>Dùng 100 Lọ Thuốc bất kỳ.</t>
         </is>
       </c>
     </row>
@@ -13039,7 +13039,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Dùng Dishes 20 lần.</t>
+          <t>Dùng Món Ăn 20 lần.</t>
         </is>
       </c>
     </row>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Dùng Dishes 50 lần.</t>
+          <t>Dùng Món Ăn 50 lần.</t>
         </is>
       </c>
     </row>
@@ -13169,7 +13169,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Dùng Dishes 100 lần.</t>
+          <t>Dùng Món Ăn 100 lần.</t>
         </is>
       </c>
     </row>
@@ -13234,7 +13234,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Trigger Tài Năng Hỗ Trợ Nấu Ăn 10 lần.</t>
+          <t>Kích hoạt Tài Năng Hỗ Trợ Nấu Ăn 10 lần.</t>
         </is>
       </c>
     </row>
@@ -13299,7 +13299,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Trigger Tài Năng Hỗ Trợ Synthesis 10 lần.</t>
+          <t>Kích hoạt Tài Năng Hỗ Trợ Tổng Hợp 10 lần.</t>
         </is>
       </c>
     </row>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Kích hoạt tất cả Resonance Beacon ở Jinzhou.</t>
+          <t>Kích hoạt tất cả Đèn Cộng Hưởng ở Jinzhou.</t>
         </is>
       </c>
     </row>
@@ -13429,7 +13429,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Kích hoạt tất cả Resonance Beacon ở Ragunna.</t>
+          <t>Kích hoạt tất cả Đèn Cộng Hưởng ở Ragunna.</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Hoàn thành "First Resonance."</t>
+          <t>Hoàn thành "Cộng Hưởng Đầu Tiên."</t>
         </is>
       </c>
     </row>
@@ -13624,7 +13624,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Phoebe 100 lần</t>
+          <t>Sử dụng Kỹ Năng Outro của Phoebe 100 lần</t>
         </is>
       </c>
     </row>
@@ -13689,7 +13689,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Sử dụng Kỹ Năng Kết Thúc của Brant 100 lần.</t>
+          <t>Sử dụng Outro Skill của Brant 100 lần.</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Zani 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Zani 100 lần.</t>
         </is>
       </c>
     </row>
@@ -13819,7 +13819,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Ciaccona 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Ciaccona 100 lần.</t>
         </is>
       </c>
     </row>
@@ -13884,7 +13884,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Augusta 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Augusta 100 lần.</t>
         </is>
       </c>
     </row>
@@ -13949,7 +13949,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Sử dụng Kỹ Năng Kết Thúc của Iuno 100 lần.</t>
+          <t>Sử dụng Outro Skill của Iuno 100 lần.</t>
         </is>
       </c>
     </row>
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Galbrena 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Galbrena 100 lần.</t>
         </is>
       </c>
     </row>
@@ -14079,7 +14079,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Qiuyuan 100 lần.</t>
+          <t>Sử dụng Kỹ năng Outro của Qiuyuan 100 lần.</t>
         </is>
       </c>
     </row>
@@ -14144,7 +14144,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Chisa 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Chisa 100 lần.</t>
         </is>
       </c>
     </row>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Sử dụng Kỹ Năng Kết Thúc của Buling 100 lần.</t>
+          <t>Sử dụng Outro Skill của Buling 100 lần.</t>
         </is>
       </c>
     </row>
@@ -14274,7 +14274,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Phrolova 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Phrolova 100 lần.</t>
         </is>
       </c>
     </row>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Cartethyia 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Cartethyia 100 lần.</t>
         </is>
       </c>
     </row>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Lupa 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Lupa 100 lần.</t>
         </is>
       </c>
     </row>
@@ -14469,7 +14469,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Rover: Aero 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Rover: Aero 100 lần.</t>
         </is>
       </c>
     </row>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Cantarella 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Cantarella 100 lần.</t>
         </is>
       </c>
     </row>
@@ -14599,7 +14599,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Trigger Intro Skill 20 lần.</t>
+          <t>Kích hoạt Kỹ Năng Khởi Động 20 lần.</t>
         </is>
       </c>
     </row>
@@ -14664,7 +14664,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Dùng Kỹ Năng Echo của Bell-Borne Geochelone để giáng đòn chí mạng vào hắn.</t>
+          <t>Dùng Kỹ Năng Tiếng Vọng của Bell-Borne Geochelone để giáng đòn chí mạng vào hắn.</t>
         </is>
       </c>
     </row>
@@ -14729,7 +14729,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Dùng Kỹ Năng Echo của Inferno Rider để hạ gục hắn.</t>
+          <t>Dùng Kỹ Năng Tiếng Vọng của Inferno Rider để hạ gục hắn.</t>
         </is>
       </c>
     </row>
@@ -14794,7 +14794,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Dùng Kỹ Năng Echo của Mourning Aix để kết liễu con quái vật này.</t>
+          <t>Dùng Kỹ Năng Tiếng Vọng của Mourning Aix để kết liễu con quái vật này.</t>
         </is>
       </c>
     </row>
@@ -14859,7 +14859,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Dùng Kỹ Năng Echo của Crownless để kết liễu hắn.</t>
+          <t>Dùng Kỹ Năng Tiếng Vọng của Crownless để kết liễu hắn.</t>
         </is>
       </c>
     </row>
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Dùng Kỹ Năng Echo của Thundering Mephis để giáng đòn chí mạng vào hắn.</t>
+          <t>Dùng Kỹ Năng Tiếng Vọng của Thundering Mephis để giáng đòn chí mạng vào hắn.</t>
         </is>
       </c>
     </row>
@@ -15119,7 +15119,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Thực hiện Kỹ Năng Kết của Rover: Spectro 10 lần.</t>
+          <t>Thực hiện Kỹ Năng Kết của Vận Mệnh Giả: Spectro 10 lần.</t>
         </is>
       </c>
     </row>
@@ -15184,7 +15184,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Kích hoạt Outro Skill của Camellya 10 lần.</t>
+          <t>Kích hoạt Kỹ Năng Outro của Camellya 10 lần.</t>
         </is>
       </c>
     </row>
@@ -15249,7 +15249,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Thực hiện Kỹ Năng Kết của Rover: Havoc 10 lần.</t>
+          <t>Thực hiện Kỹ Năng Kết của Vận Mệnh Giả: Havoc 10 lần.</t>
         </is>
       </c>
     </row>
@@ -15314,7 +15314,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Thực hiện Outro Skill của Jianxin 10 lần.</t>
+          <t>Thực hiện Kỹ Năng Outro của Jianxin 10 lần.</t>
         </is>
       </c>
     </row>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Thực hiện Outro Skill của Jinhsi 10 lần.</t>
+          <t>Thực hiện Kỹ Năng Outro của Jinhsi 10 lần.</t>
         </is>
       </c>
     </row>
@@ -15444,7 +15444,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Kích hoạt Outro Skill của Chixia 10 lần.</t>
+          <t>Kích hoạt Kỹ Năng Outro của Chixia 10 lần.</t>
         </is>
       </c>
     </row>
@@ -15509,7 +15509,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Thực hiện Outro Skill của Danjin 10 lần.</t>
+          <t>Thực hiện Kỹ Năng Outro của Danjin 10 lần.</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Kích hoạt Outro Skill của Sanhua 10 lần.</t>
+          <t>Kích hoạt Kỹ Năng Outro của Sanhua 10 lần.</t>
         </is>
       </c>
     </row>
@@ -15639,7 +15639,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Kích hoạt Outro Skill của Taoqi 10 lần.</t>
+          <t>Kích hoạt Kỹ Năng Outro của Taoqi 10 lần.</t>
         </is>
       </c>
     </row>
@@ -15704,7 +15704,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Kích hoạt Outro Skill của Yangyang 10 lần.</t>
+          <t>Kích hoạt Kỹ Năng Outro của Yangyang 10 lần.</t>
         </is>
       </c>
     </row>
@@ -15769,7 +15769,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Kích hoạt Outro Skill của Yinlin 10 lần.</t>
+          <t>Kích hoạt Kỹ Năng Outro của Yinlin 10 lần.</t>
         </is>
       </c>
     </row>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Kích hoạt Outro Skill của Verina 10 lần.</t>
+          <t>Kích hoạt Kỹ Năng Outro của Verina 10 lần.</t>
         </is>
       </c>
     </row>
@@ -15899,7 +15899,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Thực hiện Outro Skill của Encore 10 lần.</t>
+          <t>Thực hiện Kỹ Năng Outro của Encore 10 lần.</t>
         </is>
       </c>
     </row>
@@ -15964,7 +15964,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Kích hoạt Outro Skill của Baizhi 10 lần.</t>
+          <t>Kích hoạt Kỹ Năng Outro của Baizhi 10 lần.</t>
         </is>
       </c>
     </row>
@@ -16029,7 +16029,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Thực hiện Outro Skill của Lingyang 10 lần.</t>
+          <t>Thực hiện Kỹ Năng Outro của Lingyang 10 lần.</t>
         </is>
       </c>
     </row>
@@ -16094,7 +16094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Thực hiện Outro Skill của Mortefi 10 lần.</t>
+          <t>Thực hiện Kỹ Năng Outro của Mortefi 10 lần.</t>
         </is>
       </c>
     </row>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Kích hoạt Outro Skill của Yuanwu 10 lần.</t>
+          <t>Kích hoạt Kỹ Năng Outro của Yuanwu 10 lần.</t>
         </is>
       </c>
     </row>
@@ -16224,7 +16224,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Thực hiện Outro Skill của Jiyan 10 lần.</t>
+          <t>Thực hiện Kỹ Năng Outro của Jiyan 10 lần.</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Kích hoạt Outro Skill của Aalto 10 lần.</t>
+          <t>Kích hoạt Kỹ Năng Outro của Aalto 10 lần.</t>
         </is>
       </c>
     </row>
@@ -16354,7 +16354,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Kích hoạt Outro Skill của Calcharo 10 lần.</t>
+          <t>Kích hoạt Kỹ Năng Outro của Calcharo 10 lần.</t>
         </is>
       </c>
     </row>
@@ -16419,7 +16419,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Rover: Spectro 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Rover: Spectro 100 lần.</t>
         </is>
       </c>
     </row>
@@ -16484,7 +16484,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Rover: Havoc 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Rover: Havoc 100 lần.</t>
         </is>
       </c>
     </row>
@@ -16549,7 +16549,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Sử dụng Kỹ Năng Kết Thúc của Jianxin 100 lần.</t>
+          <t>Sử dụng Outro Skill của Jianxin 100 lần.</t>
         </is>
       </c>
     </row>
@@ -16614,7 +16614,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Sử dụng Kỹ Năng Kết Thúc của Jinhsi 100 lần.</t>
+          <t>Sử dụng Outro Skill của Jinhsi 100 lần.</t>
         </is>
       </c>
     </row>
@@ -16679,7 +16679,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Chixia 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Chixia 100 lần.</t>
         </is>
       </c>
     </row>
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Danjin 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Danjin 100 lần.</t>
         </is>
       </c>
     </row>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Sanhua 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Sanhua 100 lần.</t>
         </is>
       </c>
     </row>
@@ -16874,7 +16874,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Taoqi 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Taoqi 100 lần.</t>
         </is>
       </c>
     </row>
@@ -16939,7 +16939,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Yangyang 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Yangyang 100 lần.</t>
         </is>
       </c>
     </row>
@@ -17004,7 +17004,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Yinlin 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Yinlin 100 lần.</t>
         </is>
       </c>
     </row>
@@ -17069,7 +17069,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Verina 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Verina 100 lần.</t>
         </is>
       </c>
     </row>
@@ -17134,7 +17134,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Encore 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Encore 100 lần.</t>
         </is>
       </c>
     </row>
@@ -17199,7 +17199,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Baizhi 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Baizhi 100 lần.</t>
         </is>
       </c>
     </row>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Lingyang 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Lingyang 100 lần.</t>
         </is>
       </c>
     </row>
@@ -17329,7 +17329,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Mortefi 100 lần</t>
+          <t>Sử dụng Kỹ Năng Outro của Mortefi 100 lần</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Yuanwu 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Yuanwu 100 lần.</t>
         </is>
       </c>
     </row>
@@ -17459,7 +17459,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Sử dụng Kỹ Năng Kết Thúc của Jiyan 100 lần.</t>
+          <t>Sử dụng Outro Skill của Jiyan 100 lần.</t>
         </is>
       </c>
     </row>
@@ -17524,7 +17524,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Aalto 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Aalto 100 lần.</t>
         </is>
       </c>
     </row>
@@ -17589,7 +17589,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Sử dụng Kỹ Năng Kết Thúc của Calcharo 100 lần.</t>
+          <t>Sử dụng Outro Skill của Calcharo 100 lần.</t>
         </is>
       </c>
     </row>
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Changli 10 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Changli 10 lần.</t>
         </is>
       </c>
     </row>
@@ -17719,7 +17719,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Changli 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Changli 100 lần.</t>
         </is>
       </c>
     </row>
@@ -17784,7 +17784,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Xiangli Yao 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Xiangli Yao 100 lần.</t>
         </is>
       </c>
     </row>
@@ -17849,7 +17849,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Zhezhi 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Zhezhi 100 lần.</t>
         </is>
       </c>
     </row>
@@ -17914,7 +17914,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Shorekeeper 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Shorekeeper 100 lần.</t>
         </is>
       </c>
     </row>
@@ -17979,7 +17979,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Youhu 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Youhu 100 lần.</t>
         </is>
       </c>
     </row>
@@ -18044,7 +18044,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Camellya 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Camellya 100 lần.</t>
         </is>
       </c>
     </row>
@@ -18109,7 +18109,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Lumi 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Lumi 100 lần.</t>
         </is>
       </c>
     </row>
@@ -18174,7 +18174,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Gây 1.000 sát thương bằng một đòn tấn công vào kẻ địch.</t>
+          <t>Gây 1.000 DMG bằng một đòn tấn công vào kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -18304,7 +18304,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Gây tổng cộng 10.000 DMG.</t>
+          <t>Gây tổng cộng 10.000 Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -18369,7 +18369,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Gây tổng cộng 100.000 DMG.</t>
+          <t>Gây tổng cộng 100.000 Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -18499,7 +18499,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Gây tổng cộng 10.000.000 DMG.</t>
+          <t>Gây tổng cộng 10.000.000 Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -18694,7 +18694,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Gây 30.000 sát thương bằng một đòn tấn công vào kẻ địch.</t>
+          <t>Gây 30.000 DMG bằng một đòn tấn công vào kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -18759,7 +18759,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Gây 40.000 sát thương bằng một đòn tấn công vào kẻ địch.</t>
+          <t>Gây 40.000 DMG bằng một đòn tấn công vào kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -18824,7 +18824,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Gây 50.000 sát thương bằng một đòn tấn công vào kẻ địch.</t>
+          <t>Gây 50.000 DMG bằng một đòn tấn công vào kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -18954,7 +18954,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Gây 200.000 sát thương bằng một đòn tấn công vào kẻ địch.</t>
+          <t>Gây 200.000 DMG bằng một đòn tấn công vào kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -19019,7 +19019,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Gây 300.000 sát thương bằng một đòn tấn công vào kẻ địch.</t>
+          <t>Gây 300.000 DMG bằng một đòn tấn công vào kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -19084,7 +19084,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Gây 400.000 sát thương bằng một đòn tấn công vào kẻ địch.</t>
+          <t>Gây 400.000 DMG bằng một đòn tấn công vào kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -19149,7 +19149,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Gây 500.000 sát thương bằng một đòn tấn công vào kẻ địch.</t>
+          <t>Gây 500.000 DMG bằng một đòn tấn công vào kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -19409,7 +19409,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Carlotta 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Carlotta 100 lần.</t>
         </is>
       </c>
     </row>
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Roccia 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Roccia 100 lần.</t>
         </is>
       </c>
     </row>
@@ -19539,7 +19539,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Dùng Heavy Attack của Chixia tiêu diệt kẻ địch 10 lần từ khoảng cách 7m.</t>
+          <t>Dùng Đòn Heavy Attack của Chixia tiêu diệt kẻ địch 10 lần từ khoảng cách 7m.</t>
         </is>
       </c>
     </row>
@@ -19604,7 +19604,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Dùng Heavy Attack của Chixia tiêu diệt kẻ địch 10 lần từ khoảng cách 1m.</t>
+          <t>Dùng Đòn Heavy Attack của Chixia tiêu diệt kẻ địch 10 lần từ khoảng cách 1m.</t>
         </is>
       </c>
     </row>
@@ -19669,7 +19669,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Dùng Kỹ Năng Echo của Fusion Dreadmane để đánh bại Havoc Dreadmane 10 lần.</t>
+          <t>Dùng Kỹ Năng Tiếng Vọng của Fusion Dreadmane để đánh bại Havoc Dreadmane 10 lần.</t>
         </is>
       </c>
     </row>
@@ -19799,7 +19799,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Resonator bị hạ gục bởi đòn chí mạng của Glacio DMG khi HP vẫn còn trên 50%.</t>
+          <t>Resonator bị hạ gục bởi đòn chí mạng của DMG Glacio khi HP vẫn còn trên 50%.</t>
         </is>
       </c>
     </row>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Resonator bị hạ gục bởi đòn chí mạng của Spectro DMG khi HP vẫn còn trên 50%.</t>
+          <t>Resonator bị hạ gục bởi đòn chí mạng của DMG Spectro khi HP vẫn còn trên 50%.</t>
         </is>
       </c>
     </row>
@@ -20124,7 +20124,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Resonator bị hạ gục bởi đòn chí mạng của Havoc DMG khi HP vẫn còn trên 50%.</t>
+          <t>Resonator bị hạ gục bởi đòn chí mạng của DMG Havoc khi HP vẫn còn trên 50%.</t>
         </is>
       </c>
     </row>
@@ -20189,7 +20189,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Vượt qua tầng cuối của bất kỳ tháp nào trong Hazard Zone mà không chịu sát thương nào.</t>
+          <t>Vượt qua tầng cuối của bất kỳ tháp nào trong Khu Nguy Hiểm mà không chịu sát thương nào.</t>
         </is>
       </c>
     </row>
@@ -20254,7 +20254,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Lynae 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Lynae 100 lần.</t>
         </is>
       </c>
     </row>
@@ -20319,7 +20319,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Mornye 100 lần</t>
+          <t>Sử dụng Kỹ Năng Outro của Mornye 100 lần</t>
         </is>
       </c>
     </row>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Aemeath 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Aemeath 100 lần.</t>
         </is>
       </c>
     </row>
@@ -20449,7 +20449,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Luuk Herssen 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Luuk Herssen 100 lần.</t>
         </is>
       </c>
     </row>
@@ -20579,7 +20579,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Dùng Resonance Beacon hoặc Nexus để hồi sinh Resonator 10 lần.</t>
+          <t>Dùng Đèn Cộng Hưởng hoặc Nexus để hồi sinh Resonator 10 lần.</t>
         </is>
       </c>
     </row>
@@ -20644,7 +20644,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Hoàn thành 5 Hướng Dẫn Kỹ Năng của Resonators.</t>
+          <t>Hoàn thành 5 Hướng Dẫn Kỹ Năng của Resonator.</t>
         </is>
       </c>
     </row>
@@ -20709,7 +20709,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Hoàn thành Echo "Độ Sâu Ảo Ảnh" ở bất kỳ độ khó nào với HP đầy đủ.</t>
+          <t>Hoàn thành Tổ Tacet "Độ Sâu Ảo Ảnh" ở bất kỳ độ khó nào với HP đầy đủ.</t>
         </is>
       </c>
     </row>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Hoàn thành Depths of Illusive Realm với Concerto: Mortefi 1 lần.</t>
+          <t>Hoàn thành Vực Sâu Ảo Cảnh với Concerto: Mortefi 1 lần.</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Hoàn thành Depths of Illusive Realm với Concerto: Aalto 1 lần.</t>
+          <t>Hoàn thành Vực Sâu Ảo Cảnh với Concerto: Aalto 1 lần.</t>
         </is>
       </c>
     </row>
@@ -21099,7 +21099,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Hoàn thành Depths of Illusive Realm với Concerto: Danjin 1 lần.</t>
+          <t>Hoàn thành Vực Sâu Ảo Cảnh với Concerto: Danjin 1 lần.</t>
         </is>
       </c>
     </row>
@@ -21164,7 +21164,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Tham Gia Carnival Giấc Mơ Cùng Concerto: Baizhi 1 Lần</t>
+          <t>Tham Gia Lễ Hội Giấc Mơ Cùng Concerto: Baizhi 1 Lần</t>
         </is>
       </c>
     </row>
@@ -21229,7 +21229,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Tham gia Carnival Thách Đấu ở Slumberland cùng Concerto: Yinlin 1 lần.</t>
+          <t>Tham gia Lễ Hội Thách Đấu ở Slumberland cùng Concerto: Yinlin 1 lần.</t>
         </is>
       </c>
     </row>
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Tham gia Carnival Thách Đấu ở Slumberland cùng Concerto: Jianxin 1 lần.</t>
+          <t>Tham gia Lễ Hội Thách Đấu ở Slumberland cùng Concerto: Jianxin 1 lần.</t>
         </is>
       </c>
     </row>
@@ -21359,7 +21359,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Tham Gia Carnival Giấc Mơ Cùng Concerto: Danjin 1 Lần</t>
+          <t>Tham Gia Lễ Hội Giấc Mơ Cùng Concerto: Danjin 1 Lần</t>
         </is>
       </c>
     </row>
@@ -21424,7 +21424,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Tham gia Carnival Thách Đấu ở Slumberland cùng Concerto: Verina 1 lần.</t>
+          <t>Tham gia Lễ Hội Thách Đấu ở Slumberland cùng Concerto: Verina 1 lần.</t>
         </is>
       </c>
     </row>
@@ -21489,7 +21489,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Tham gia Carnival Thách Đấu ở Slumberland cùng Concerto: Mortefi 1 lần.</t>
+          <t>Tham gia Lễ Hội Thách Đấu ở Slumberland cùng Concerto: Mortefi 1 lần.</t>
         </is>
       </c>
     </row>
@@ -21554,7 +21554,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Tham gia Carnival Thách Đấu ở Slumberland cùng Concerto: Sanhua 1 lần.</t>
+          <t>Tham gia Lễ Hội Thách Đấu ở Slumberland cùng Concerto: Sanhua 1 lần.</t>
         </is>
       </c>
     </row>
@@ -21619,7 +21619,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Tham gia Carnival Thách Đấu ở Slumberland cùng Concerto: Yuanwu 1 lần.</t>
+          <t>Tham gia Lễ Hội Thách Đấu ở Slumberland cùng Concerto: Yuanwu 1 lần.</t>
         </is>
       </c>
     </row>
@@ -21684,7 +21684,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Tham Gia Carnival Giấc Mơ Cùng Concerto: Aalto 1 Lần</t>
+          <t>Tham Gia Lễ Hội Giấc Mơ Cùng Concerto: Aalto 1 Lần</t>
         </is>
       </c>
     </row>
@@ -21749,7 +21749,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Thách đấu bất kỳ độ khó nào của Phantasm Amass một lần bằng 4 Concerto Resonators khác nhau.</t>
+          <t>Thách đấu bất kỳ độ khó nào của Phantasm Amass một lần bằng 4 Concerto Resonator khác nhau.</t>
         </is>
       </c>
     </row>
@@ -21882,10 +21882,10 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Chiếc Lock Trường Thọ bí ẩn mà Lingyang đeo khi lần đầu gặp gỡ những người trong &lt;te href=850130&gt;Liondance Troupe&lt;/te&gt;.
-Sau khi đến thành phố &lt;te href=850091&gt;Jinzhou&lt;/te&gt;, Liondance Troupe đã đi khắp các con phố và giúp Lingyang tìm gặp một số thương nhân để hỏi về nguồn gốc chiếc mặt dây chuyền, nhưng vô vọng. Tất cả những gì họ nói chỉ là: "Đây là một thiết kế cổ mà tôi chưa từng thấy."
+          <t>Chiếc Khóa Trường Thọ bí ẩn mà Lingyang đeo khi lần đầu gặp gỡ những người trong &lt;te href=850130&gt;Đoàn Múa Lân&lt;/te&gt;.
+Sau khi đến thành phố &lt;te href=850091&gt;Jinzhou&lt;/te&gt;, Đoàn Múa Lân đã đi khắp các con phố và giúp Lingyang tìm gặp một số thương nhân để hỏi về nguồn gốc chiếc mặt dây chuyền, nhưng vô vọng. Tất cả những gì họ nói chỉ là: "Đây là một thiết kế cổ mà tôi chưa từng thấy."
 Vì những động tác múa lân mạnh mẽ chắc chắn sẽ làm hỏng nó, Lingyang đã cất giữ chiếc khóa trong một chiếc hộp gỗ an toàn.
-Dù ai là người tạo ra nó, chiếc Lock Trường Thọ vẫn mang theo những lời chúc sức khỏe và hạnh phúc. Khi trao nó cho ngươi, Lingyang cũng gửi gắm những mong ước chân thành cho sự bình an của ngươi.</t>
+Dù ai là người tạo ra nó, chiếc Khóa Trường Thọ vẫn mang theo những lời chúc sức khỏe và hạnh phúc. Khi trao nó cho ngươi, Lingyang cũng gửi gắm những mong ước chân thành cho sự bình an của ngươi.</t>
         </is>
       </c>
     </row>
@@ -21953,7 +21953,7 @@
       <c r="M328" t="inlineStr">
         <is>
           <t>Một đôi lông vũ được tạo thành từ ngọn lửa của Changli. Một chiếc đã được tặng cho một vị khách danh giá của &lt;te href=850091&gt;Jinzhou&lt;/te&gt;, còn chiếc kia Changli giữ bên mình.
-Dù rực cháy, đôi lông vũ chỉ tỏa ra hơi ấm dịu dàng khi nằm trong lòng bàn tay, phản ánh khả năng điều khiển Forte gần như hoàn hảo của Changli. Like bộ trang phục của cô, chiếc lông vũ hoàn toàn được tạo nên từ lửa.
+Dù rực cháy, đôi lông vũ chỉ tỏa ra hơi ấm dịu dàng khi nằm trong lòng bàn tay, phản ánh khả năng điều khiển Forte gần như hoàn hảo của Changli. Giống như bộ trang phục của cô, chiếc lông vũ hoàn toàn được tạo nên từ lửa.
 Trong những câu chuyện kể trước giờ đi ngủ của một cô bé, phượng hoàng sinh ra từ lửa sẽ trao chiếc lông đuôi quý giá nhất cho người mà nó yêu thương nhất.</t>
         </is>
       </c>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Từng chỉ là một con rối đơn sơ, giờ đây đã trở thành vũ khí sắc bén nhờ khả năng Resonance của Yinlin. Dù cô có phủ nhận, tình yêu của cô dành cho con búp bê vẫn hiện rõ trong từng chi tiết, dù nó đã sờn rách sau bao năm tháng chiến đấu. Nó từng chỉ là một mẫu thử của người làm búp bê, nhưng giờ đây đã trở thành đồng minh đáng tin cậy của Yinlin trên chiến trường.</t>
+          <t>Từng chỉ là một con rối đơn sơ, giờ đây đã trở thành vũ khí sắc bén nhờ khả năng Cộng Hưởng của Yinlin. Dù cô có phủ nhận, tình yêu của cô dành cho con búp bê vẫn hiện rõ trong từng chi tiết, dù nó đã sờn rách sau bao năm tháng chiến đấu. Nó từng chỉ là một mẫu thử của người làm búp bê, nhưng giờ đây đã trở thành đồng minh đáng tin cậy của Yinlin trên chiến trường.</t>
         </is>
       </c>
     </row>
@@ -22159,7 +22159,7 @@
       <c r="M331" t="inlineStr">
         <is>
           <t>Một con búp bê gỗ chạm khắc tinh xảo, được tạo hình theo dáng vẻ của {PlayerName} và chế tác từ rễ cây do Forte của Camellya tạo ra. Nó phản ánh gu thẩm mỹ độc đáo của cô.
-Trước khi tái ngộ ở &lt;te href=850091&gt;Jinzhou&lt;/te&gt;, Camellya đã thử vô số lần để khắc họa gương mặt búp bê, nhưng mỗi lần đều khiến cô nản lòng vì không thể hoàn thiện Dodget cuối cùng.
+Trước khi tái ngộ ở &lt;te href=850091&gt;Jinzhou&lt;/te&gt;, Camellya đã thử vô số lần để khắc họa gương mặt búp bê, nhưng mỗi lần đều khiến cô nản lòng vì không thể hoàn thiện nét cuối cùng.
 Giờ đây, sau bao lần thử mò mẫm và thất vọng, tầm nhìn của cô cuối cùng cũng thành hiện thực.
 Nhìn tác phẩm của mình, cô không nhịn được cười khúc khích.
 "Thì ra nó phải như thế này," cô nghĩ.
@@ -22233,10 +22233,10 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Biểu đồ dạng sóng của Resonator Sanhua cho thấy dao động hình elip. Mô hình miền thời gian ổn định, không có dạng sóng bất thường. Kết quả kiểm tra nằm trong giới hạn bình thường. Tuy nhiên, nguy cơ &lt;te href=850073&gt;Overclocking&lt;/te&gt; của Sanhua vẫn còn.
-Mức Độ Resonance Tới Hạn: Rất ổn định. Nhưng liên tục tiến sát ngưỡng Tới Hạn. Nguy cơ Quá Tải vẫn ở mức cao.
+          <t>Biểu đồ dạng sóng của Resonator Sanhua cho thấy dao động hình elip. Mô hình miền thời gian ổn định, không có dạng sóng bất thường. Kết quả kiểm tra nằm trong giới hạn bình thường. Tuy nhiên, nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; của Sanhua vẫn còn.
+Mức Độ Cộng Hưởng Tới Hạn: Rất ổn định. Nhưng liên tục tiến sát ngưỡng Tới Hạn. Nguy cơ Quá Tải vẫn ở mức cao.
 Sanhua có tiền sử Quá Tải. Mức Quá Tải tối đa: Trung bình.
-Những lần Quá Tải trước đây của Sanhua đã gây ra bão tuyết cấp 2 do cô duy trì trạng thái tiến sát ngưỡng Resonance Tới Hạn và phản ứng dao động Tần số cực đoan trong thời gian dài. Không có thương vong dân sự trong các sự cố này. Chuỗi sự kiện này hiện được ghi nhận dưới mã EX01521, phân loại là sự kiện nguy hiểm cấp 3.
+Những lần Quá Tải trước đây của Sanhua đã gây ra bão tuyết cấp 2 do cô duy trì trạng thái tiến sát ngưỡng Cộng Hưởng Tới Hạn và phản ứng dao động Tần số cực đoan trong thời gian dài. Không có thương vong dân sự trong các sự cố này. Chuỗi sự kiện này hiện được ghi nhận dưới mã EX01521, phân loại là sự kiện nguy hiểm cấp 3.
 Tần số của Sanhua dao động do sự xói mòn, gây ra những vụ bùng nổ năng lượng và làm thay đổi nhận thức. Quá Tải khiến sự xói mòn lan nhanh hơn và biến đồng tử trái của cô từ màu xám sang đỏ.
 Do khuynh hướng Quá Tải trong quá khứ của Sanhua, cần theo dõi sát sao tình trạng tâm lý và thể chất của cô. Tư vấn và kiểm tra định kỳ là bắt buộc.</t>
         </is>
@@ -22309,11 +22309,11 @@
       <c r="M333" t="inlineStr">
         <is>
           <t>Cơ sở Đánh giá: [Đánh giá Cộng hưởng 2105-G] 
-Theo báo cáo của Resonator Sanhua, cô sinh ra đã có cấu trúc mắt bất thường dẫn đến mù lòa. Sau đó, việc tiếp xúc với Discord trong một trận bão tuyết do &lt;te href=850080&gt;Waveworn Phenomenon&lt;/te&gt; gây ra đã làm xói mòn tần số ở mắt phải, khiến thị lực của Sanhua trở nên bất thường và dẫn đến sự thức tỉnh của Forte. 
-&lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của Resonator Sanhua nằm ở đồng tử mắt phải, chỉ hiện rõ khi cô sử dụng Forte. Sau khi phân tích lời khai của Sanhua và kết quả test y tế, chúng tôi đã xác định được những thay đổi về thể chất sau khi thức tỉnh. Những thay đổi này bao gồm phản ứng tần số hỗn loạn ở đồng tử phải gần Tacet Mark, khiến nó chuyển sang màu đỏ. Sự xói mòn cũng đang tiến triển, thể hiện qua việc đồng tử trái chuyển từ màu xám sang đỏ. 
+Theo báo cáo của Resonator Sanhua, cô sinh ra đã có cấu trúc mắt bất thường dẫn đến mù lòa. Sau đó, việc tiếp xúc với Tacet Discord trong một trận bão tuyết do &lt;te href=850080&gt;Hiện tượng Waveworn&lt;/te&gt; gây ra đã làm xói mòn tần số ở mắt phải, khiến thị lực của Sanhua trở nên bất thường và dẫn đến sự thức tỉnh của Forte. 
+&lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của Resonator Sanhua nằm ở đồng tử mắt phải, chỉ hiện rõ khi cô sử dụng Forte. Sau khi phân tích lời khai của Sanhua và kết quả kiểm tra y tế, chúng tôi đã xác định được những thay đổi về thể chất sau khi thức tỉnh. Những thay đổi này bao gồm phản ứng tần số hỗn loạn ở đồng tử phải gần Dấu Tacet, khiến nó chuyển sang màu đỏ. Sự xói mòn cũng đang tiến triển, thể hiện qua việc đồng tử trái chuyển từ màu xám sang đỏ. 
 Sanhua đã có được thị lực bất thường và khả năng kiểm soát tuyết thông qua Forte, sức mạnh của nó phụ thuộc vào sự tập trung của cô. Sau khi phân tích lời giải thích của cô, kết luận ban đầu của chúng tôi là thị lực của cô khác biệt so với bình thường, cho phép cô cảm nhận trực tiếp tần số của vật thể. Các thử nghiệm tần số cho thấy độ chính xác 99,64% trong khả năng hình dung của cô. 
 Mô hình Phổ Cộng hưởng của Sanhua giống hệt với phổ của tuyết. Ngoài ra, phổ tần số của đồng tử cô cũng trùng khớp với khoảng dao động tần số của các TD đã biết. Cả hai thử nghiệm đều cho thấy phản ứng Đồng điệu mạnh mẽ, và nguyên nhân chính xác dẫn đến sự thức tỉnh của cô vẫn chưa rõ ràng. 
-Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; không hội tụ với đoạn tăng đột biến ở phần giữa. Do đó, Sanhua được xếp vào loại &lt;te href=850069&gt;Mutant Resonator&lt;/te&gt;.</t>
+Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Đường cong Rabelle&lt;/te&gt; không hội tụ với đoạn tăng đột biến ở phần giữa. Do đó, Sanhua được xếp vào loại &lt;te href=850069&gt;Resonator Đột biến&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -22384,13 +22384,13 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Tiêu chí đánh giá: [Đánh Giá Resonance 2190-G]
-Resonator Baizhi trải qua Sự Thức Tỉnh cách đây bốn năm, sau khi tiếp xúc với nguồn &lt;te href=850076&gt;Remnant Energy&lt;/te&gt; mạnh một năm trước đó. Sự tiếp xúc này đã kích hoạt các tần số Tàn Dư tương ứng bên trong cô. Theo lời kể của Baizhi, trong quá trình Thức Tỉnh, cô cảm thấy một xung động mãnh liệt muốn hồi sinh đồng đội. Kết quả là, các tần số trên đã hiện thân thành một Sinh Vật Tàn Dư, giờ đây trở thành người bạn đồng hành của cô.
-&lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của Resonator Baizhi nằm ở mặt trước đùi phải. Không có thay đổi vật lý đáng kể nào sau Thức Tỉnh được ghi nhận.
-Tuy nhiên, khi sử dụng Forte, Tacet Mark phát ra ánh sáng trắng mờ nhạt cùng với sự xuất hiện của Sinh Vật Tàn Dư trên. Sinh vật này có màu trắng trong suốt, hình dáng giống cánh hoa Epiphyllum. Nó không thể phát ra tiếng người, nhưng có thể giao tiếp với Baizhi bằng thần giao cách cảm.
+          <t>Tiêu chí đánh giá: [Đánh Giá Cộng Hưởng 2190-G]
+Resonator Baizhi trải qua Sự Thức Tỉnh cách đây bốn năm, sau khi tiếp xúc với nguồn &lt;te href=850076&gt;Năng Lượng Tàn Dư&lt;/te&gt; mạnh một năm trước đó. Sự tiếp xúc này đã kích hoạt các tần số Tàn Dư tương ứng bên trong cô. Theo lời kể của Baizhi, trong quá trình Thức Tỉnh, cô cảm thấy một xung động mãnh liệt muốn hồi sinh đồng đội. Kết quả là, các tần số trên đã hiện thân thành một Sinh Vật Tàn Dư, giờ đây trở thành người bạn đồng hành của cô.
+&lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của Resonator Baizhi nằm ở mặt trước đùi phải. Không có thay đổi vật lý đáng kể nào sau Thức Tỉnh được ghi nhận.
+Tuy nhiên, khi sử dụng Forte, Dấu Tacet phát ra ánh sáng trắng mờ nhạt cùng với sự xuất hiện của Sinh Vật Tàn Dư trên. Sinh vật này có màu trắng trong suốt, hình dáng giống cánh hoa Epiphyllum. Nó không thể phát ra tiếng người, nhưng có thể giao tiếp với Baizhi bằng thần giao cách cảm.
 Resonator Baizhi không thể trực tiếp sử dụng Forte của mình, nhưng cô có thể tận dụng nhiệt độ cực thấp và khả năng chữa lành của Sinh Vật Tàn Dư để điều trị vết thương trong phạm vi gần.
-Mô hình Phổ Resonance của Baizhi không giống bất kỳ tần số nào đã biết. Tuy nhiên, nó cho thấy mức độ tương đồng nhất định với sự dao động của Năng Lượng Tàn Dư, và có Phản Ứng Đồng Điệu mạnh với "&lt;te href=850140&gt;You'tan&lt;/te&gt;", Sinh Vật Tàn Dư của cô. Dù có những mối liên hệ này, nguyên nhân Thức Tỉnh của Baizhi vẫn chưa rõ ràng do thiếu bằng chứng lý thuyết đầy đủ.
-Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; không hội tụ, với sự tăng dần rồi đột ngột tăng mạnh ở đoạn giữa. Do đó, Resonator Baizhi được phân loại là &lt;te href=850069&gt;Mutant Resonator&lt;/te&gt; với Giai Đoạn Tiềm Tàng.</t>
+Mô hình Phổ Cộng Hưởng của Baizhi không giống bất kỳ tần số nào đã biết. Tuy nhiên, nó cho thấy mức độ tương đồng nhất định với sự dao động của Năng Lượng Tàn Dư, và có Phản Ứng Đồng Điệu mạnh với "&lt;te href=850140&gt;You'tan&lt;/te&gt;", Sinh Vật Tàn Dư của cô. Dù có những mối liên hệ này, nguyên nhân Thức Tỉnh của Baizhi vẫn chưa rõ ràng do thiếu bằng chứng lý thuyết đầy đủ.
+Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Đường Cong Rabelle&lt;/te&gt; không hội tụ, với sự tăng dần rồi đột ngột tăng mạnh ở đoạn giữa. Do đó, Resonator Baizhi được phân loại là &lt;te href=850069&gt;Resonator Đột Biến&lt;/te&gt; với Giai Đoạn Tiềm Tàng.</t>
         </is>
       </c>
     </row>
@@ -22458,7 +22458,7 @@
       <c r="M335" t="inlineStr">
         <is>
           <t>Biểu đồ dạng sóng của Resonator Lingyang cho thấy dao động hình elip. Mô hình miền thời gian đều đặn với giá trị đỉnh ổn định, không phát hiện sóng bất thường.
-Độ Ổn Định Cộng Hưởng: Rất ổn định. Lingyang sở hữu mức Độ Ổn Định khá cao. Nguy cơ &lt;te href=850073&gt;Overclocking&lt;/te&gt; rất thấp.
+Độ Ổn Định Cộng Hưởng: Rất ổn định. Lingyang sở hữu mức Độ Ổn Định khá cao. Nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; rất thấp.
 Lingyang chưa từng có tiền sử Quá Tải. Cậu thể hiện khả năng kiểm soát Forte thành thạo, luôn duy trì trạng thái cảm xúc ổn định. Khi sử dụng kỹ năng "Truyền Ý Chí", trường nhiệt độ thấp tạo ra chủ yếu mang lại lợi ích cho đồng đội. Trong đội hình, điều này giúp giảm nguy cơ Quá Tải tổng thể cho Lingyang. Khuyến nghị giữ mức rủi ro của Lingyang ở mức thấp và theo dõi tiến trình thường xuyên. Nên tiếp tục quan sát.</t>
         </is>
       </c>
@@ -22531,13 +22531,13 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Cơ sở đánh giá: [Đánh Giá Resonance 1888-G]
+          <t>Cơ sở đánh giá: [Đánh Giá Cộng Hưởng 1888-G]
 Tuổi tác và thời điểm thức tỉnh của Resonator Lingyang vẫn chưa xác định, và có vẻ cậu đã thức tỉnh từ rất lâu. Lingyang đã trải qua thời gian dài tiếp xúc với điều kiện môi trường khắc nghiệt và có thể đã kích hoạt Forte một cách tự nhiên trong chiến đấu.
-Lingyang mang &lt;te href=850072&gt;Tacet Mark&lt;/te&gt; trên cánh tay phải. Không ghi nhận đột biến sau thức tỉnh.
+Lingyang mang &lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; trên cánh tay phải. Không ghi nhận đột biến sau thức tỉnh.
 Sức bền và thể lực của cậu vượt trội, có thể do tiếp xúc với môi trường cực đoan. Cậu thể hiện kỹ năng chiến đấu và sinh tồn điêu luyện, nhưng thiếu kinh nghiệm sử dụng Forte do không thường xuyên vận dụng. Cần đánh giá thêm để xác định liệu có cần hướng dẫn sử dụng Forte đúng cách hay không.
 Dưới tác động của Forte, giác quan của Lingyang trở nên nhạy bén hơn và cậu có thể tạo ra một trường Gusto băng giá vô hình trong phạm vi giới hạn. Điều này cũng tạo ra một trường nhiệt độ thấp gây áp lực lên kẻ địch xung quanh. Ngoài ra, Lingyang có thể tác động và khích lệ tinh thần của những người gần đó thông qua ý chí truyền đạt.
-Chưa ghi nhận trường hợp nào có Mô hình Phổ Resonance tương tự Lingyang. Nguyên nhân thức tỉnh của cậu vẫn chưa được xác định.
-Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; không hội tụ với đoạn tăng dần. Do đó, Lingyang được xác định là &lt;te href=850070&gt;Natural Resonator&lt;/te&gt;.
+Chưa ghi nhận trường hợp nào có Mô hình Phổ Cộng Hưởng tương tự Lingyang. Nguyên nhân thức tỉnh của cậu vẫn chưa được xác định.
+Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Đường cong Rabelle&lt;/te&gt; không hội tụ với đoạn tăng dần. Do đó, Lingyang được xác định là &lt;te href=850070&gt;Resonator Tự Nhiên&lt;/te&gt;.
 &lt;i&gt;"Gì cơ? Vậy ngoại hình 'hoang dã' của cậu ta không phải do Forte à? Rốt cuộc đây là cái gì..."&lt;/i&gt;</t>
         </is>
       </c>
@@ -22613,13 +22613,13 @@
         <is>
           <t>Cơ sở Đánh giá: [Đánh giá Cộng hưởng 1231-G]
 Thời điểm chính xác của Sự Thức tỉnh Resonator Zhezhi vẫn chưa rõ. Dấu hiệu "hoạt họa" đã xuất hiện trong các bức vẽ từ nhỏ, và khả năng kiểm soát Forte của cô cải thiện song song với kỹ năng hội họa.
-&lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của Zhezhi nằm ở mu bàn tay phải. Quan sát sau Sự Thức tỉnh không phát hiện thay đổi thể chất đáng kể. Test cho thấy Zhezhi có thể "hoạt họa" các bức vẽ, ảnh hưởng đến nhận thức và phán đoán thị giác của người quan sát (hiệu quả với cả sinh vật sống và &lt;te href=850081&gt;Tacet Discords&lt;/te&gt;).
+&lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của Zhezhi nằm ở mu bàn tay phải. Quan sát sau Sự Thức tỉnh không phát hiện thay đổi thể chất đáng kể. Kiểm tra cho thấy Zhezhi có thể "hoạt họa" các bức vẽ, ảnh hưởng đến nhận thức và phán đoán thị giác của người quan sát (hiệu quả với cả sinh vật sống và &lt;te href=850081&gt;Tacet Discord&lt;/te&gt;).
 "Hoạt họa" có hai cấp độ:
 Vừa: Gây chuyển động nhẹ trong hình ảnh hai chiều.
 Nghiêm trọng: Mô phỏng hình khối ba chiều, kéo dài đến 30 phút 28 giây, phủ sóng lên đến 274,5 mét vuông.
 Cả hai cấp độ đều tạo ra ảo giác, không phải vật thể thực. Không phát hiện khoảng thời gian ổn định.
 Không xác định được Mô hình Phổ Cộng hưởng tương tự, nguyên nhân Sự Thức tỉnh của Zhezhi vẫn chưa rõ.
-Ngoài ra, phân tích mẫu thử cho thấy &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; có dạng sóng tuần hoàn rõ rệt. Do đó, Zhezhi được xác định là &lt;te href=850068&gt;Congenital Resonator&lt;/te&gt;.</t>
+Ngoài ra, phân tích mẫu thử cho thấy &lt;te href=850067&gt;Đường cong Rabelle&lt;/te&gt; có dạng sóng tuần hoàn rõ rệt. Do đó, Zhezhi được xác định là &lt;te href=850068&gt;Resonator Bẩm sinh&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -22687,7 +22687,7 @@
       <c r="M338" t="inlineStr">
         <is>
           <t>Biểu đồ dạng sóng của Resonator Youhu từng xuất hiện dao động xung vuông không tuần hoàn, với giá trị đỉnh duy trì trong những khoảng thời gian nhất định trước khi giảm dần. Hiện tại, dạng sóng đang thể hiện dao động hình sin rõ rệt. Cả giá trị đỉnh trên và dưới đều thấp.
-Độ Phản Ứng Cộng Hưởng: Tương đối cao. Tần số của Youhu có độ ổn định cao, nguy cơ &lt;te href=850073&gt;Overclocking&lt;/te&gt; thấp.
+Độ Phản Ứng Cộng Hưởng: Tương đối cao. Tần số của Youhu có độ ổn định cao, nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; thấp.
 Nên tiến hành kiểm tra sức khỏe định kỳ, nhưng tư vấn tâm lý hiện không cần thiết.</t>
         </is>
       </c>
@@ -22758,7 +22758,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Tiêu chí đánh giá: [Báo cáo Resonance RA1013-G]</t>
+          <t>Tiêu chí đánh giá: [Báo cáo Cộng Hưởng RA1013-G]</t>
         </is>
       </c>
     </row>
@@ -22834,8 +22834,8 @@
 Thành viên này đã Thức Tỉnh hơn một thập kỷ trước và sở hữu khả năng kiểm soát Forte cực kỳ xuất sắc.
 Dấu &lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của thành viên nằm ở vùng thắt lưng, không phát hiện thay đổi vật lý đáng kể sau khi Thức Tỉnh. Cô có thể tạo ra vô số tinh thể lấp lánh giống như ngọc opal, tái cấu trúc thành súng và đạn dược khi cần. Khi sử dụng Forte, mái tóc của Opal cũng xuất hiện hiệu ứng kết tinh. Kẻ địch trúng phải tinh thể sẽ bị kết tinh theo.
 &lt;i&gt;Đáng nói là có kẻ đã cố thu gom những "viên ngọc" này để kiếm lời, chỉ để phát hiện chúng không thể bán hay lưu thông. Nhìn bề ngoài, chúng giống như đá quý, nhưng bản chất lại là một loại môi trường kích hoạt tái cấu trúc cấu trúc, có thể khiến tần số của mục tiêu sụp đổ và phân rã cho đến khi biến mất hoàn toàn.&lt;/i&gt;
-Mô hình Phổ Resonance của thành viên này có Dodget tương đồng nhất định với đồ trang trí kính màu và bông tuyết tự nhiên. Có khả năng điều này liên quan đến hành vi chủ động phá vỡ truyền thống của cô khi lần đầu sử dụng đồ trang trí làm vũ khí lúc Forte vừa Thức Tỉnh.
-Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; không hội tụ, do đó thành viên này được phân loại là &lt;te href=850069&gt;Mutant Resonator&lt;/te&gt; có thời kỳ ủ bệnh.</t>
+Mô hình Phổ Cộng Hưởng của thành viên này có nét tương đồng nhất định với đồ trang trí kính màu và bông tuyết tự nhiên. Có khả năng điều này liên quan đến hành vi chủ động phá vỡ truyền thống của cô khi lần đầu sử dụng đồ trang trí làm vũ khí lúc Forte vừa Thức Tỉnh.
+Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Đường Cong Rabelle&lt;/te&gt; không hội tụ, do đó thành viên này được phân loại là &lt;te href=850069&gt;Resonator Đột Biến&lt;/te&gt; có thời kỳ ủ bệnh.</t>
         </is>
       </c>
     </row>
@@ -22907,10 +22907,10 @@
         <is>
           <t>Cơ sở đánh giá: [Đánh giá Cộng hưởng 2893-G]
 Resonator Chixia đã trải qua Sự Thức Tỉnh cách đây 6 năm sau khi tiếp xúc với nhiệt độ cực hạn và ngọn lửa rực cháy.
-&lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của Resonator Chixia nằm ở vùng bụng dưới bên trái. Sau Sự Thức Tỉnh, quan sát ghi nhận tóc cô chuyển sang màu đỏ và thân nhiệt tăng đáng kể.
+&lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của Resonator Chixia nằm ở vùng bụng dưới bên trái. Sau Sự Thức Tỉnh, quan sát ghi nhận tóc cô chuyển sang màu đỏ và thân nhiệt tăng đáng kể.
 Cô có khả năng chuyển đổi tần số của các chất ở nhiệt độ cao thành đạn lửa hữu hình.
-Mô hình Phổ Resonance của Chixia được ghi nhận có sự tương đồng cao với phổ của ngọn lửa. Phản ứng Resonance mạnh mẽ đã được quan sát, song nguyên nhân dẫn đến Sự Thức Tỉnh của Chixia vẫn chưa rõ ràng.
-Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; không hội tụ với đoạn tăng đột biến ở giữa. Do đó, Resonator Chixia được phân loại là &lt;te href=850069&gt;Mutant Resonator&lt;/te&gt;.</t>
+Mô hình Phổ Cộng Hưởng của Chixia được ghi nhận có sự tương đồng cao với phổ của ngọn lửa. Phản ứng Cộng Hưởng mạnh mẽ đã được quan sát, song nguyên nhân dẫn đến Sự Thức Tỉnh của Chixia vẫn chưa rõ ràng.
+Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Đường cong Rabelle&lt;/te&gt; không hội tụ với đoạn tăng đột biến ở giữa. Do đó, Resonator Chixia được phân loại là &lt;te href=850069&gt;Resonator Đột Biến&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -22979,11 +22979,11 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Cơ sở đánh giá: [Đánh Giá Resonance 1631-G]
-Thời điểm chính xác của sự Kích Hoạt của Resonator Encore vẫn chưa được xác định. Theo báo cáo của Encore và kết quả test cộng hưởng, những thực thể giống cừu đi theo cô được cho là biểu hiện của trí tưởng tượng và trạng thái tâm lý của cô. Chúng được tin là đại diện cho khả năng Forte của cô.
-Đánh giá Resonance của Encore chịu ảnh hưởng bởi cảm xúc tập thể trong môi trường thử nghiệm, thể hiện phản ứng Đồng Điệu mạnh mẽ. Nguyên nhân dẫn đến sự Kích Hoạt của cô vẫn chưa được xác nhận.
-Encore mang &lt;te href=850072&gt;Tacet Mark&lt;/te&gt; trên lưng trên, và các test sau Kích Hoạt đã phát hiện một số đột biến vật lý nhỏ, bao gồm phần tóc giống như len. Khi cảm xúc lên cao, cô có thể mọc ra sừng giống cừu, yêu cầu nhân viên thử nghiệm phải thận trọng.
-Phân tích mẫu thử cho thấy một &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; không hội tụ với dạng sóng tuần hoàn rõ rệt, qua đó xếp Encore vào loại &lt;te href=850068&gt;Congenital Resonator&lt;/te&gt;.</t>
+          <t>Cơ sở đánh giá: [Đánh Giá Cộng Hưởng 1631-G]
+Thời điểm chính xác của sự Kích Hoạt của Resonator Encore vẫn chưa được xác định. Theo báo cáo của Encore và kết quả kiểm tra cộng hưởng, những thực thể giống cừu đi theo cô được cho là biểu hiện của trí tưởng tượng và trạng thái tâm lý của cô. Chúng được tin là đại diện cho khả năng Forte của cô.
+Đánh giá Cộng Hưởng của Encore chịu ảnh hưởng bởi cảm xúc tập thể trong môi trường thử nghiệm, thể hiện phản ứng Đồng Điệu mạnh mẽ. Nguyên nhân dẫn đến sự Kích Hoạt của cô vẫn chưa được xác nhận.
+Encore mang &lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; trên lưng trên, và các kiểm tra sau Kích Hoạt đã phát hiện một số đột biến vật lý nhỏ, bao gồm phần tóc giống như len. Khi cảm xúc lên cao, cô có thể mọc ra sừng giống cừu, yêu cầu nhân viên thử nghiệm phải thận trọng.
+Phân tích mẫu thử cho thấy một &lt;te href=850067&gt;Đường Cong Rabelle&lt;/te&gt; không hội tụ với dạng sóng tuần hoàn rõ rệt, qua đó xếp Encore vào loại &lt;te href=850068&gt;Resonator Bẩm Sinh&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -23053,7 +23053,7 @@
       <c r="M343" t="inlineStr">
         <is>
           <t>Biểu đồ dạng sóng của Resonator Mortefi cho thấy dao động hình zigzag. Mô hình miền thời gian đều đặn, nhưng giá trị đỉnh có xu hướng tăng. Giá trị đỉnh hiện dưới mức Độ Ổn Định, chưa phát hiện sóng bất thường.
-Độ Ổn Định Cộng Hưởng: High nhưng kém ổn định. Nguy cơ &lt;te href=850073&gt;Overclocking&lt;/te&gt; rất cao.
+Độ Ổn Định Cộng Hưởng: Cao nhưng kém ổn định. Nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; rất cao.
 Mortefi có tiền sử Quá Tải. Mức Quá Tải tối đa: Trung bình.
 Khi Quá Tải, các tinh thể đỏ hình vảy trên ngực Mortefi liên tục mở rộng, bao phủ diện tích da lớn hơn. Quá trình này đi kèm với sự tăng nhiệt độ cơ thể đáng kể, gây ra dao động Tần số mạnh mẽ. Đặc biệt, một ảo ảnh rồng lửa xuất hiện phía sau Mortefi trong giai đoạn này.
 Mortefi là nguyên nhân gây ra vụ hỏa hoạn lớn tại Desorock Highland. Sự cố được phân loại mã EX67891 là nguy hiểm cấp 3. May mắn không có thương vong. Forte và lịch sử Quá Tải của Mortefi cho thấy cảm xúc tiêu cực là tác nhân chính gây Quá Tải, do đó nguy cơ Quá Tải cao hơn. Khuyến nghị theo dõi sát tình trạng tâm lý của Resonator Mortefi và tiến hành tư vấn, kiểm tra định kỳ.</t>
@@ -23126,12 +23126,12 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Cơ sở đánh giá: [Đánh Giá Resonance 2183-G]
+          <t>Cơ sở đánh giá: [Đánh Giá Cộng Hưởng 2183-G]
 Theo báo cáo của Resonator Mortefi, dấu hiệu Thức Tỉnh của hắn bắt đầu xuất hiện từ thời niên thiếu. Quá trình Thức Tỉnh thực sự đi kèm với cơn thịnh nộ dữ dội.
-&lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của Mortefi nằm ở ngực phải. Khi Năng Lực của Mortefi được kích hoạt, các tinh thể hình vảy rồng xuất hiện quanh Tacet Mark, bốc cháy dữ dội khi hắn vận dụng sức mạnh.
+&lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của Mortefi nằm ở ngực phải. Khi Năng Lực của Mortefi được kích hoạt, các tinh thể hình vảy rồng xuất hiện quanh Dấu Tacet, bốc cháy dữ dội khi hắn vận dụng sức mạnh.
 Resonator Mortefi thể hiện khả năng tạo ra và điều khiển lửa thông qua sự tập trung nhiệt lượng. Cường độ ngọn lửa sinh ra gắn liền với trạng thái cảm xúc của Mortefi. Thử nghiệm sâu rộng cho thấy ngọn lửa là biểu hiện hữu hình của những cảm xúc tiêu cực tích tụ vượt ngưỡng nhất định.
-Mô hình Phổ Resonance của Mortefi có sự tương đồng cao với loài Dragon, một chủng tộc hiện đã tuyệt chủng. Do không còn cá thể Dragon sống để tiến hành thử nghiệm Đồng Điệu, hiện chưa thể xác nhận nguyên nhân Thức Tỉnh của Mortefi bằng thực nghiệm.
-Phân tích mẫu thử cho thấy một &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; không hội tụ, với đoạn giữa tăng đột biến. Resonator Mortefi do đó được phân loại là &lt;te href=850069&gt;Mutant Resonator&lt;/te&gt;.</t>
+Mô hình Phổ Cộng Hưởng của Mortefi có sự tương đồng cao với loài Rồng, một chủng tộc hiện đã tuyệt chủng. Do không còn cá thể Rồng sống để tiến hành thử nghiệm Đồng Điệu, hiện chưa thể xác nhận nguyên nhân Thức Tỉnh của Mortefi bằng thực nghiệm.
+Phân tích mẫu thử cho thấy một &lt;te href=850067&gt;Đường Cong Rabelle&lt;/te&gt; không hội tụ, với đoạn giữa tăng đột biến. Resonator Mortefi do đó được phân loại là &lt;te href=850069&gt;Resonator Đột Biến&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -23203,7 +23203,7 @@
       <c r="M345" t="inlineStr">
         <is>
           <t>Biểu đồ dạng sóng của Resonator Changli cho thấy dao động hình elip. Mô hình miền thời gian ổn định, không có dạng sóng bất thường.
-Mức Độ Cộng Hưởng Tới Hạn: High. Tần số của Changli thể hiện độ ổn định cao, rủi ro &lt;te href=850073&gt;Overclocking&lt;/te&gt; là rất thấp.
+Mức Độ Cộng Hưởng Tới Hạn: Cao. Tần số của Changli thể hiện độ ổn định cao, rủi ro &lt;te href=850073&gt;Quá Tải&lt;/te&gt; là rất thấp.
 Changli có tiền sử Quá Tải được ghi nhận.
 Mức Quá Tải tối đa: Không đáng kể.
 Theo báo cáo của Changli, cô từng trải qua Quá Tải từ nhỏ do tiếp xúc lâu dài với môi trường nguy hiểm. Điều này khiến Forte của cô bùng nổ nhiều lần để tự vệ hoặc bảo vệ người khác, để lại vết bỏng vĩnh viễn trên cánh tay trái.
@@ -23280,10 +23280,10 @@
         <is>
           <t>Cơ sở đánh giá: [Đánh giá Cộng hưởng 2326-G]
 Thời điểm chính xác Resonator Changli thức tỉnh vẫn chưa được xác định. Các báo cáo cho thấy Changli đã biểu hiện khả năng điều khiển lửa từ nhỏ, nhưng thường không kiểm soát được. Tuy nhiên, khi trưởng thành, tần suất và sự ổn định của những biểu hiện này đã cải thiện đáng kể.
-&lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của Resonator Changli nằm ở vùng ngực dưới. Các test sau thức tỉnh đã phát hiện những thay đổi đặc biệt trên cơ thể cô, bao gồm sự phai màu dần ở đuôi tóc và những vết cháy hình lông vũ trên cánh tay trái, phát sáng rực lửa dưới ảnh hưởng của Forte.
+&lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của Resonator Changli nằm ở vùng ngực dưới. Các kiểm tra sau thức tỉnh đã phát hiện những thay đổi đặc biệt trên cơ thể cô, bao gồm sự phai màu dần ở đuôi tóc và những vết cháy hình lông vũ trên cánh tay trái, phát sáng rực lửa dưới ảnh hưởng của Forte.
 Mô hình Phổ Cộng hưởng của Changli phản ánh đặc tính của lửa, cho thấy phản ứng Cộng hưởng mạnh mẽ trong thử nghiệm. Dù nguyên nhân thức tỉnh vẫn chưa rõ ràng, chưa có mẫu nào có độ tương đồng Phổ Cộng hưởng vượt quá 60%. Forte của Changli gần gũi với loài chim thần thoại trong truyền thuyết &lt;te href=850093&gt;Huanglong&lt;/te&gt;, có thể do ảnh hưởng từ những câu chuyện cô nghe từ nhỏ về sinh vật huyền thoại này.
-Changli sở hữu khả năng đặc biệt Dodgen lửa thành những viên đạn hình lông vũ mỏng manh. Khi Forte của cô được giải phóng, nó có thể tạo ra những ngọn lửa thiêu đốt với sức nóng khủng khiếp, đủ sức tàn phá một vùng rộng lớn. Dấu hiệu cho thấy Forte của cô đang hoạt động là sự xuất hiện của một chiếc lông vũ lửa đơn độc với họa tiết giống con mắt trên trán, mà cô gọi là "Con Mắt Tâm Linh".
-Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; không hội tụ với xu hướng tăng ổn định. Đôi khi có những dao động trong phạm vi bình thường. Do đó, Changli được xác định là &lt;te href=850070&gt;Natural Resonator&lt;/te&gt;.</t>
+Changli sở hữu khả năng đặc biệt nén lửa thành những viên đạn hình lông vũ mỏng manh. Khi Forte của cô được giải phóng, nó có thể tạo ra những ngọn lửa thiêu đốt với sức nóng khủng khiếp, đủ sức tàn phá một vùng rộng lớn. Dấu hiệu cho thấy Forte của cô đang hoạt động là sự xuất hiện của một chiếc lông vũ lửa đơn độc với họa tiết giống con mắt trên trán, mà cô gọi là "Con Mắt Tâm Linh".
+Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Đường cong Rabelle&lt;/te&gt; không hội tụ với xu hướng tăng ổn định. Đôi khi có những dao động trong phạm vi bình thường. Do đó, Changli được xác định là &lt;te href=850070&gt;Resonator Tự nhiên&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -23421,9 +23421,9 @@
       <c r="M348" t="inlineStr">
         <is>
           <t>Biểu đồ sóng của Resonator Calcharo dao động gấp khúc. Mô hình miền Thời Gian bất thường, cả đỉnh trên và dưới đều cao, gần mức Giới Hạn Tới Hạn. Một số đoạn sóng bị mờ nhòe và xuất hiện dạng sóng dị thường.
-Mức Độ Tới Hạn Cộng Hưởng: Tương đối cao, kết hợp với độ ổn định cực thấp. Nguy cơ &lt;te href=850073&gt;Overclocking&lt;/te&gt; rất lớn.
+Mức Độ Tới Hạn Cộng Hưởng: Tương đối cao, kết hợp với độ ổn định cực thấp. Nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; rất lớn.
 Calcharo có tiền sử Quá Tải. Mức Quá Tải cao nhất ghi nhận: Nghiêm trọng.
-Khi Quá Tải, dấu hiệu xói mòn &lt;te href=850081&gt;Tacet Discord&lt;/te&gt; lan trên cơ thể Calcharo, và Core Tacet vàng trên ngực hắn nhấp nháy. Tần số dao động của hắn tăng mạnh, tạo ra nhiều thực thể ảo.
+Khi Quá Tải, dấu hiệu xói mòn &lt;te href=850081&gt;Tacet Discord&lt;/te&gt; lan trên cơ thể Calcharo, và Lõi Tacet vàng trên ngực hắn nhấp nháy. Tần số dao động của hắn tăng mạnh, tạo ra nhiều thực thể ảo.
 Chưa ghi nhận thiệt hại về người hay tài sản do Quá Tải của Calcharo.
 Calcharo có nguy cơ Quá Tải cực cao với nguyên nhân kích hoạt chưa xác định. Khuyến nghị nâng mức đánh giá rủi ro và theo dõi sát tình trạng của hắn.</t>
         </is>
@@ -23497,14 +23497,14 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Tiêu chí đánh giá: [Đánh Giá Resonance 2300-G]
+          <t>Tiêu chí đánh giá: [Đánh Giá Cộng Hưởng 2300-G]
 Thời điểm Thức Tỉnh của Resonator Calcharo vẫn chưa rõ ràng. Theo báo cáo của Calcharo, hắn đã trải qua thời gian dài trong môi trường khắc nghiệt và đối mặt với vô số tình huống đe dọa tính mạng. Kết quả là, Forte của hắn tự thức tỉnh như một phương thức tự vệ.
-&lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của Resonator Calcharo nằm trên trán. Khi Calcharo kích hoạt Forte, một lõi vàng xuất hiện trên ngực hắn. Đồng thời, nhiều bộ phận trên cơ thể hắn hiện lên đặc điểm của &lt;te href=850081&gt;Tacet Discords&lt;/te&gt;, quấn quýt với những gai bóng tối.
+&lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của Resonator Calcharo nằm trên trán. Khi Calcharo kích hoạt Forte, một lõi vàng xuất hiện trên ngực hắn. Đồng thời, nhiều bộ phận trên cơ thể hắn hiện lên đặc điểm của &lt;te href=850081&gt;Tacet Discord&lt;/te&gt;, quấn quýt với những gai bóng tối.
 Đáng chú ý, cơ thể Calcharo chứa lượng năng lượng sinh học điện cao hơn nhiều so với người bình thường. Hắn thể hiện khả năng nhận thức và kiểm soát dòng điện cũng như lực từ trường vượt trội.
 Nguyên nhân chính xác dẫn đến Sự Thức Tỉnh của Resonator Calcharo hiện chưa thể xác định, do Mô Hình Phổ của hắn không giống bất kỳ mẫu nào đã biết.
-Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; không hội tụ, với sự tăng dần đều. Do đó, Resonator Calcharo được phân loại là &lt;te href=850070&gt;Natural Resonator&lt;/te&gt;.
+Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Đường Cong Rabelle&lt;/te&gt; không hội tụ, với sự tăng dần đều. Do đó, Resonator Calcharo được phân loại là &lt;te href=850070&gt;Resonator Tự Nhiên&lt;/te&gt;.
 &lt;i&gt;"Thực ra... có một Mô Hình Phổ cực kỳ tương đồng mà chúng ta dường như đã bỏ sót, hay đúng hơn, là ngần ngại không dám nghĩ tới."&lt;/i&gt;
-&lt;i&gt;"Yes... Đó là Tacet Discord."&lt;/i&gt;</t>
+&lt;i&gt;"Đúng vậy... Đó là Tacet Discord."&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -23574,12 +23574,12 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Cơ sở đánh giá: [Đánh giá Cộng hưởng 2917-G]
-&lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của Resonator Yinlin nằm ở mặt ngoài đùi trái. Không có thay đổi thể chất đáng kể nào được ghi nhận trên cơ thể Yinlin sau Sự Thức Tỉnh. Một dòng điện nhẹ đã được phát hiện trên bề mặt da cô, nhưng không gây ra bất kỳ tác động tiêu cực nào có thể phát hiện được.
-Yinlin sở hữu khả năng hội tụ dòng điện thành những sợi tơ mảnh. Khả năng điều khiển những sợi tơ này của cô vô cùng điêu luyện.
-Mô hình Phổ Resonance của cô được phát hiện có sự tương đồng với phổ của các vật liệu dẫn điện đã biết. Các thử nghiệm cho thấy phản ứng Resonance mạnh mẽ.
-Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Đường cong Rabelle&lt;/n&gt; không hội tụ với dạng sóng tuần hoàn rõ rệt, qua đó phân loại Yinlin là &lt;te href=850068&gt;Resonator Bẩm Sinh&lt;/te&gt;.
-GHI CHÚ PHỤ: Yinlin có tiền sử rối loạn nhịp tim, có thể liên quan hoặc không liên quan đến Forte của cô. Việc phong tỏa Forte có thể làm tăng nguy cơ rung nhĩ.</t>
+          <t>Cơ sở đánh giá: [Resonance Assessment 2917-G]
+Resonator Yinlin's &lt;te href=850072&gt;Tacet Mark&lt;/te&gt; is located on the exterior side of her left thigh. No significant physical changes have been observed in Yinlin's body after her Awakening. A mild electrical current has been detected on the surface of her skin, but it has not resulted in any detectable adverse effects on her body.
+Yinlin possesses the power to converge electric currents into thin threads. Her manipulation of these threads is extraordinarily proficient.
+Her Resonance Spectrum Pattern is found to be similar to the Spectrum Pattern of known conductive materials. Tests have found strong Syntony.
+Analysis of test samples has revealed a non-convergent &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; with a noticeable periodic waveform, which classifies Yinlin as a &lt;te href=850068&gt;Congenital Resonator&lt;/te&gt;.
+SIDENOTES: Yinlin has a preexisting arrhythmia that may or may not be related to her Forte. Blocking of her Forte could potentially increase the risk of atrial fibrillation.</t>
         </is>
       </c>
     </row>
@@ -23649,8 +23649,8 @@
       <c r="M351" t="inlineStr">
         <is>
           <t>Biểu đồ dạng sóng của Resonator Yuanwu có dao động hình elip. Mô hình miền Thời Gian ổn định, không phát hiện sóng bất thường.
-Mức Độ Resonance Tới Hạn: Tương đối cao. Tần số của Yuanwu thể hiện độ ổn định cao, nguy cơ &lt;te href=850073&gt;Overclocking&lt;/te&gt; rất thấp.
-Hồ sơ trước đây không ghi nhận tiền sử Quá Tải; tuy nhiên, trong thời niên thiếu, khi lần đầu sử dụng Năng Lực Resonance, Yuanwu từng suýt Quá Tải, gây ra dao động tần số dữ dội và hành vi mất kiểm soát. Sự cố được xếp loại nguy hiểm cấp 2 và lưu trữ dưới mã EX42978.
+Mức Độ Cộng Hưởng Tới Hạn: Tương đối cao. Tần số của Yuanwu thể hiện độ ổn định cao, nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; rất thấp.
+Hồ sơ trước đây không ghi nhận tiền sử Quá Tải; tuy nhiên, trong thời niên thiếu, khi lần đầu sử dụng Năng Lực Cộng Hưởng, Yuanwu từng suýt Quá Tải, gây ra dao động tần số dữ dội và hành vi mất kiểm soát. Sự cố được xếp loại nguy hiểm cấp 2 và lưu trữ dưới mã EX42978.
 Các kiểm tra sau đó cho thấy sự cố này xuất phát từ căng thẳng tinh thần. Không ghi nhận di chứng Quá Tải.
 Hiện tại, trạng thái tâm lý của Yuanwu được đánh giá là ổn định và khỏe mạnh. Khuyến nghị kiểm tra định kỳ để ngăn ngừa Quá Tải trong tương lai.</t>
         </is>
@@ -23722,12 +23722,12 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Cơ sở đánh giá: [Đánh Giá Resonance 1425-G]
+          <t>Cơ sở đánh giá: [Đánh Giá Cộng Hưởng 1425-G]
 Thời điểm chính xác Resonator Yuanwu thức tỉnh vẫn chưa rõ. Yuanwu kể lại rằng anh đã tiếp xúc với năng lượng điện cực mạnh trong thời gian dài trước khi thức tỉnh.
-&lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của Resonator Yuanwu nằm ở bên phải cổ. Sau khi thức tỉnh, các cấu trúc tinh thể màu xanh dương xuất hiện trên chi trước, cùng với những vết sẹo trên tay và cổ tay. Những thay đổi này đã ổn định kể từ đó.
+&lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của Resonator Yuanwu nằm ở bên phải cổ. Sau khi thức tỉnh, các cấu trúc tinh thể màu xanh dương xuất hiện trên chi trước, cùng với những vết sẹo trên tay và cổ tay. Những thay đổi này đã ổn định kể từ đó.
 Yuanwu có khả năng kiểm soát phi thường đối với sự dao động tần số trong cơ thể. Anh có thể điều chỉnh biên độ và phạm vi tần số trong nháy mắt mà không gây tổn hại cho bản thân. Các thử nghiệm kết luận rằng anh thành thạo trong việc thao túng tần số hơn 82,58% so với Resonator trung bình.
-Mô hình Phổ Resonance của Yuanwu được quan sát có sự tương đồng cao với sấm sét. Một phản ứng Đồng Điệu mạnh đã được ghi nhận, nhưng nguyên nhân thức tỉnh của Yuanwu vẫn chưa rõ.
-Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; không hội tụ với xu hướng tăng dần. Do đó, Yuanwu được phân loại là &lt;te href=850070&gt;Natural Resonator&lt;/te&gt;.</t>
+Mô hình Phổ Cộng Hưởng của Yuanwu được quan sát có sự tương đồng cao với sấm sét. Một phản ứng Đồng Điệu mạnh đã được ghi nhận, nhưng nguyên nhân thức tỉnh của Yuanwu vẫn chưa rõ.
+Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Đường cong Rabelle&lt;/te&gt; không hội tụ với xu hướng tăng dần. Do đó, Yuanwu được phân loại là &lt;te href=850070&gt;Resonator Tự Nhiên&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -23800,11 +23800,11 @@
         <is>
           <t>Cơ sở Đánh giá: [Đánh giá Cộng hưởng 2100-G] 
 Thời điểm chính xác Resonator Jinhsi thức tỉnh vẫn chưa được xác định. Dấu hiệu thức tỉnh của cô xuất hiện từ sớm, thiết lập một sự cộng hưởng sâu sắc với &lt;te href=850116&gt;Sentinel Jué&lt;/te&gt;. 
-&lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của Jinhsi nằm ở giữa lưng, là một đặc điểm nổi bật. Khi kích hoạt Năng lực Cộng hưởng, những cấu trúc tinh thể giống sừng Loong hiện ra trên đầu cô. 
+&lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của Jinhsi nằm ở giữa lưng, là một đặc điểm nổi bật. Khi kích hoạt Năng lực Cộng hưởng, những cấu trúc tinh thể giống sừng Loong hiện ra trên đầu cô. 
 Nhờ năng lực đặc biệt, Jinhsi có thể thao túng ánh sáng để tạo ra những hình chiếu hologram phản chiếu Sentinel Jué, thể hiện sức mạnh tương đương với khả năng của chính &lt;te href=850083&gt;Sentinel&lt;/te&gt;. 
 Dữ liệu quan sát cho thấy tiềm năng phát triển vượt trội của Năng lực Cộng hưởng của đối tượng. Đỉnh cao của khả năng này gợi mở viễn cảnh đáng kinh ngạc về việc dịch chuyển thời gian. 
 Phân tích chi tiết Mô hình Phổ Cộng hưởng của Jinhsi đã tiết lộ sự tương đồng đáng kinh ngạc với Mô hình của Sentinel Jué. Các thử nghiệm nghiêm ngặt đã phát hiện phản ứng Đồng điệu mạnh mẽ. Tuy nhiên, nguyên nhân chính xác dẫn đến sự thức tỉnh của Jinhsi vẫn còn là bí ẩn do vị trí đặc biệt của Sentinel. 
-Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; không hội tụ với dạng sóng tuần hoàn rõ rệt, qua đó xếp Jinhsi vào loại &lt;te href=850068&gt;Congenital Resonator&lt;/te&gt;.</t>
+Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Đường cong Rabelle&lt;/te&gt; không hội tụ với dạng sóng tuần hoàn rõ rệt, qua đó xếp Jinhsi vào loại &lt;te href=850068&gt;Resonator Bẩm sinh&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -23875,9 +23875,9 @@
         <is>
           <t>Cơ sở đánh giá: [Đánh giá Cộng hưởng 2603-G]
 Resonator Xiangli Yao thức tỉnh cách đây hai năm, sau một sự cố tại Court of Savantae Ruins, nơi anh mất cánh tay phải và tiếp xúc với một loại kim loại lạ.
-&lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của Xiangli Yao nằm trên cánh tay giả bên phải. Quan sát sau thức tỉnh cho thấy anh có khả năng Metalmorph bằng cách thay đổi hình dạng và tích trữ năng lượng trong cánh tay giả.
+&lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của Xiangli Yao nằm trên cánh tay giả bên phải. Quan sát sau thức tỉnh cho thấy anh có khả năng Metalmorph bằng cách thay đổi hình dạng và tích trữ năng lượng trong cánh tay giả.
 Mô hình Phổ Cộng hưởng của Xiangli Yao gần như trùng khớp với sấm sét. Phản ứng Cộng hưởng mạnh mẽ đã được ghi nhận, nhưng nguyên nhân thức tỉnh của anh vẫn chưa rõ do không thể thu hồi mẫu kim loại lạ.
-Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; ổn định, bằng phẳng trước khi tăng vọt và ổn định trở lại. Do đó, Xiangli Yao được xác định là &lt;te href=850069&gt;Mutant Resonator&lt;/te&gt;.</t>
+Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Đường cong Rabelle&lt;/te&gt; ổn định, bằng phẳng trước khi tăng vọt và ổn định trở lại. Do đó, Xiangli Yao được xác định là &lt;te href=850069&gt;Resonator Đột biến&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -23947,7 +23947,7 @@
       <c r="M355" t="inlineStr">
         <is>
           <t>Biểu đồ dạng sóng của Resonator Yangyang cho thấy dao động elip ổn định trong miền Thời Gian, không có dấu hiệu bất thường. Sau kiểm tra, tất cả kết quả đều nằm trong ngưỡng bình thường.
-Về mức Độ Phản Ứng Cộng Hưởng, Yangyang ở mức tương đối thấp nhưng có độ ổn định cao. Kết quả kiểm tra đều nằm trong ngưỡng bình thường, không có nguy cơ &lt;te href=850073&gt;Overclocking&lt;/te&gt;.
+Về mức Độ Phản Ứng Cộng Hưởng, Yangyang ở mức tương đối thấp nhưng có độ ổn định cao. Kết quả kiểm tra đều nằm trong ngưỡng bình thường, không có nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt;.
 Yangyang từng có tiền sử Quá Tải.
 Mức Quá Tải tối đa: Không đáng kể.
 Trong sự cố, Yangyang trải qua tình trạng tràn trề cảm xúc và mất kiểm soát tạm thời đối với Forte. May mắn là không có thương vong hay nguy hiểm nào được ghi nhận, dù cô đã phải chịu vài cơn hôn mê do kích thích quá mức. Kiểm tra sâu hơn cho thấy khả năng cảm nhận nhạy bén của Yangyang đang gây tổn hại cho cơ thể thông qua Forte. Hậu quả đã ổn định, nhưng những sợi tóc biến dạng như lông vũ ở đuôi tóc vẫn không thể phục hồi. Tình trạng quá tải giác quan của Yangyang đã được kiểm soát, tâm trạng ổn định, tiên lượng tích cực. Nên tiến hành kiểm tra định kỳ để theo dõi.</t>
@@ -24022,10 +24022,10 @@
         <is>
           <t>Cơ sở Đánh giá: [Đánh giá Cộng hưởng 1011-G]
 Thời điểm và nguyên nhân chính xác của Sự Thức tỉnh Resonator Yangyang vẫn chưa rõ ràng. Yangyang cho biết cô có độ nhạy cảm cao với môi trường xung quanh từ nhỏ.
-&lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của Yangyang nằm ở trung tâm trán. Quan sát sau Sự Thức tỉnh không phát hiện thay đổi thể chất đáng kể. Khi dao động tần số tái xuất hiện, những biến đổi giống như lông vũ đã được ghi nhận ở đuôi tóc.
+&lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của Yangyang nằm ở trung tâm trán. Quan sát sau Sự Thức tỉnh không phát hiện thay đổi thể chất đáng kể. Khi dao động tần số tái xuất hiện, những biến đổi giống như lông vũ đã được ghi nhận ở đuôi tóc.
 Yangyang đồng bộ với không khí xung quanh bằng cách phát hiện thông tin trong luồng gió và tạo ra trường năng lượng từ luồng khí hội tụ.
 Mô hình Phổ Cộng hưởng của Yangyang có hơn 20% tương đồng với đặc tính của luồng không khí và các loài chim nhỏ. Mặc dù phản ứng Đồng điệu mạnh mẽ, mô hình này cũng có hơn 5% tương đồng với nhiều mẫu hiện có khác, cho thấy khả năng có nhiều nguyên nhân hoặc tạp nhiễm trong Sự Thức tỉnh.
-Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; không hội tụ với đà tăng ổn định. Đôi khi xuất hiện dao động trong phạm vi bình thường. Do đó, Yangyang được xác định là &lt;te href=850070&gt;Natural Resonator&lt;/te&gt;.</t>
+Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Đường cong Rabelle&lt;/te&gt; không hội tụ với đà tăng ổn định. Đôi khi xuất hiện dao động trong phạm vi bình thường. Do đó, Yangyang được xác định là &lt;te href=850070&gt;Resonator Tự nhiên&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -24096,11 +24096,11 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Cơ sở đánh giá: [Đánh Giá Resonance 1617-G]
-Theo báo cáo của Resonator Aalto, vào ngày anh ta ra đời, đã xuất hiện một hiện tượng hiếm gặp: sương mù dày đặc. &lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của Aalto nằm ở bên trái cổ. Ngoài khả năng biến hình ngắn hạn thành dạng sương mù, không có thay đổi vật lý đáng kể nào được ghi nhận trên cơ thể Aalto sau khi Kích Hoạt.
+          <t>Cơ sở đánh giá: [Đánh Giá Cộng Hưởng 1617-G]
+Theo báo cáo của Resonator Aalto, vào ngày anh ta ra đời, đã xuất hiện một hiện tượng hiếm gặp: sương mù dày đặc. &lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của Aalto nằm ở bên trái cổ. Ngoài khả năng biến hình ngắn hạn thành dạng sương mù, không có thay đổi vật lý đáng kể nào được ghi nhận trên cơ thể Aalto sau khi Kích Hoạt.
 Resonator Aalto rất xuất sắc trong nghệ thuật ngụy trang và biến hóa, thường xuyên duy trì trạng thái vật lý khó nắm bắt và biến đổi, giống như đặc tính của sương mù. Các thử nghiệm tiếp theo nhằm xác định tính chất của màn sương do anh ta tạo ra đều không đưa ra kết quả rõ ràng.
-Mô hình Phổ Resonance của Aalto trùng khớp với các Mô hình Phổ đã biết của sương mù. Phản ứng Đồng Điệu mạnh mẽ đã được ghi nhận trong quá trình thử nghiệm, xác nhận mối liên hệ giữa sương mù và sự Kích Hoạt của Aalto.
-Ngoài ra, phân tích mẫu thử cho thấy một &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; không hội tụ với dạng sóng tuần hoàn rõ rệt, qua đó xếp Aalto vào loại &lt;te href=850068&gt;Congenital Resonator&lt;/te&gt;.
+Mô hình Phổ Cộng Hưởng của Aalto trùng khớp với các Mô hình Phổ đã biết của sương mù. Phản ứng Đồng Điệu mạnh mẽ đã được ghi nhận trong quá trình thử nghiệm, xác nhận mối liên hệ giữa sương mù và sự Kích Hoạt của Aalto.
+Ngoài ra, phân tích mẫu thử cho thấy một &lt;te href=850067&gt;Đường Cong Rabelle&lt;/te&gt; không hội tụ với dạng sóng tuần hoàn rõ rệt, qua đó xếp Aalto vào loại &lt;te href=850068&gt;Resonator Bẩm Sinh&lt;/te&gt;.
 &lt;i&gt;Ghi chú của Nhà nghiên cứu: Như đã nêu trong báo cáo, Resonator này rất xảo quyệt và là bậc thầy ngụy trang, do đó độ tin cậy trong lời kể của hắn rất đáng ngờ.&lt;/i&gt;
 &lt;i&gt;Ghi chú cho ghi chú: Là một người môi giới trọng danh dự, ta, Aalto, xin thề rằng lời kể ta trình bày là sự thật 100%. Không thêm, không bớt.&lt;/i&gt;</t>
         </is>
@@ -24172,12 +24172,12 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Cơ sở đánh giá: [Đánh Giá Resonance 2141-G]
+          <t>Cơ sở đánh giá: [Đánh Giá Cộng Hưởng 2141-G]
 Sự Thức Tỉnh Năng Lực của Resonator Jiyan được ghi nhận tại Trại Viễn Thám, vùng Desorock Highland. Sự kiện này đặc trưng bởi sự tích tụ luồng gió quanh cơ thể hắn, hình thành nên một ngọn giáo đặc trưng.
-Jiyan mang một &lt;te href=850072&gt;Tacet Mark&lt;/te&gt; đặc biệt nằm trên sống lưng. Sau khi Thức Tỉnh, quan sát thấy một số mảng vảy giống vảy Loong mọc lên ở hàm trái. Chưa phát hiện dấu hiệu mở rộng tiến triển.
+Jiyan mang một &lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; đặc biệt nằm trên sống lưng. Sau khi Thức Tỉnh, quan sát thấy một số mảng vảy giống vảy Loong mọc lên ở hàm trái. Chưa phát hiện dấu hiệu mở rộng tiến triển.
 Resonator Jiyan sở hữu khả năng điều khiển năng lượng gió, có thể tập trung thành &lt;ano=Teal Dragon&gt;"Qingloong"&lt;/ano&gt; hỗ trợ trong chiến đấu. Ngoài ra, hắn còn có khả năng nhận thức và lãnh đạo xuất sắc, tận dụng kết nối với gió để thu thập và phân tích thông tin chiến trường với độ chính xác đáng kinh ngạc. Kiểm chứng thực nghiệm cho thấy tỷ lệ chính xác trong đánh giá tình huống động lên tới 99,12%.
-Mô hình Phổ Resonance của Jiyan không hề giống với bất kỳ mẫu đã biết. Nguyên nhân Thức Tỉnh của hắn vẫn chưa rõ.
-Phân tích mẫu thử cho thấy một &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; không hội tụ, với đoạn giữa tăng đột biến. Resonator Jiyan do đó được phân loại là &lt;te href=850069&gt;Mutant Resonator&lt;/te&gt;.</t>
+Mô hình Phổ Cộng Hưởng của Jiyan không hề giống với bất kỳ mẫu đã biết. Nguyên nhân Thức Tỉnh của hắn vẫn chưa rõ.
+Phân tích mẫu thử cho thấy một &lt;te href=850067&gt;Đường Cong Rabelle&lt;/te&gt; không hội tụ, với đoạn giữa tăng đột biến. Resonator Jiyan do đó được phân loại là &lt;te href=850069&gt;Resonator Đột Biến&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -24247,12 +24247,12 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Cơ sở đánh giá: [Đánh Giá Resonance 1541-G]
+          <t>Cơ sở đánh giá: [Đánh Giá Cộng Hưởng 1541-G]
 Resonator Jianxin thức tỉnh cách đây 3 năm. Quá trình thức tỉnh không do bất kỳ sự kiện nào kích hoạt, do đó được xem là Thức Tỉnh Tự Nhiên.
-&lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của Jianxin nằm ở vai trái. Quan sát sau thức tỉnh không ghi nhận thay đổi thể chất đáng kể.
-Khả năng của Jianxin cho phép cô tăng cường đòn tấn công bằng cách thao túng luồng không khí và tạo ra trường lực. Đánh giá cho thấy tốc độ tấn công đạt 340m/s. Details về trường lực vẫn chưa thể kết luận. Nhìn chung, khả năng của Jianxin có tiềm năng phát triển hơn nữa.
-Mô hình Phổ Resonance của Jianxin có 5% tương đồng với hơn 10 đối tượng và không có sự tương đồng đáng kể nào trên 20%. Nguồn gốc thức tỉnh hiện chưa thể xác định.
-Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; không hội tụ với xu hướng tăng ổn định. Đôi khi xuất hiện dao động trong phạm vi bình thường. Do đó, Jianxin được xác định là &lt;te href=850070&gt;Natural Resonator&lt;/te&gt;.</t>
+&lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của Jianxin nằm ở vai trái. Quan sát sau thức tỉnh không ghi nhận thay đổi thể chất đáng kể.
+Khả năng của Jianxin cho phép cô tăng cường đòn tấn công bằng cách thao túng luồng không khí và tạo ra trường lực. Đánh giá cho thấy tốc độ tấn công đạt 340m/s. Chi tiết về trường lực vẫn chưa thể kết luận. Nhìn chung, khả năng của Jianxin có tiềm năng phát triển hơn nữa.
+Mô hình Phổ Cộng Hưởng của Jianxin có 5% tương đồng với hơn 10 đối tượng và không có sự tương đồng đáng kể nào trên 20%. Nguồn gốc thức tỉnh hiện chưa thể xác định.
+Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Đường cong Rabelle&lt;/te&gt; không hội tụ với xu hướng tăng ổn định. Đôi khi xuất hiện dao động trong phạm vi bình thường. Do đó, Jianxin được xác định là &lt;te href=850070&gt;Resonator Tự Nhiên&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -24323,10 +24323,10 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Journal của Veron Toccata—Trưởng gia tộc Toccata
-Hội đã không thể tránh khỏi việc biết đến năng lực của Ciaccona. Họ cho rằng số phận của cô là trở thành ca sĩ sáng chói nhất của gia tộc Toccata. Theo quy trình, họ đã tiến hành test Forte đối với cô. Đây là kết quả:
-Biểu đồ dạng sóng của thành viên này cho thấy dao động hình elip với miền Thời gian ổn định. Không phát hiện dấu hiệu dao động bất thường. Kết quả test được đánh giá là trong giai đoạn bình thường.
-Độ Tới Hạn Cộng Hưởng: High. Thành viên này sở hữu độ ổn định cao với rủi ro &lt;te href=850073&gt;Overclocking&lt;/te&gt; cực thấp.
+          <t>Nhật ký của Veron Toccata—Trưởng gia tộc Toccata
+Hội đã không thể tránh khỏi việc biết đến năng lực của Ciaccona. Họ cho rằng số phận của cô là trở thành ca sĩ sáng chói nhất của gia tộc Toccata. Theo quy trình, họ đã tiến hành kiểm tra Forte đối với cô. Đây là kết quả:
+Biểu đồ dạng sóng của thành viên này cho thấy dao động hình elip với miền Thời gian ổn định. Không phát hiện dấu hiệu dao động bất thường. Kết quả kiểm tra được đánh giá là trong giai đoạn bình thường.
+Độ Tới Hạn Cộng Hưởng: Cao. Thành viên này sở hữu độ ổn định cao với rủi ro &lt;te href=850073&gt;Quá Tải&lt;/te&gt; cực thấp.
 Hồ sơ ghi nhận không có tiền sử Quá Tải.
 Hiện không cần tư vấn tâm lý.
 &lt;i&gt;Mọi dữ liệu đều có vẻ bình thường, có lẽ vì cô bé cảm nhận giai điệu tràn đầy điều kỳ diệu và hy vọng. Khi lớn lên, đôi lúc tôi ước gì con bé có thể mãi hạnh phúc như thế... Nhưng tôi biết điều đó đã trở nên bất khả thi từ khi con bé cầm chiếc chìa khóa ấy.&lt;/i&gt;</t>
@@ -24400,13 +24400,13 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Cơ sở đánh giá: [Đánh Giá Resonance 1916-G]
+          <t>Cơ sở đánh giá: [Đánh Giá Cộng Hưởng 1916-G]
 Theo báo cáo của Resonator Verina, từ nhỏ cô đã tiếp xúc nhiều với các mẫu thực vật và có khả năng nghe thấy tần số của chúng. Thời điểm thức tỉnh của cô vẫn chưa xác định được.
 Tần số cộng hưởng của Verina có xu hướng tăng dần theo thời gian, dẫn đến suy đoán rằng khả năng Forte của cô cũng sẽ tiếp tục mạnh lên theo tuổi tác. Mức độ phát triển này vẫn đang được theo dõi.
-Resonator Verina mang &lt;te href=850072&gt;Tacet Mark&lt;/te&gt; dưới xương đòn. Sau khi thức tỉnh, cơ thể cô đã xuất hiện những thay đổi rõ rệt, như sự mọc lên của những dây leo trên hai tai và cột sống.
+Resonator Verina mang &lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; dưới xương đòn. Sau khi thức tỉnh, cơ thể cô đã xuất hiện những thay đổi rõ rệt, như sự mọc lên của những dây leo trên hai tai và cột sống.
 Những dây leo này hình thành mối quan hệ cộng sinh với Verina, hỗ trợ chuyển đổi tần số cộng hưởng của cô thành năng lượng Spectro để lưu trữ và giải phóng hiệu quả khi sử dụng Forte.
-Ngoài ra, Mô Hình Phổ Resonance của Verina trùng khớp với các mẫu phổ đã biết của sinh vật thực vật. Các phản ứng Đồng Điệu mạnh đã được ghi nhận trong quá trình thử nghiệm, song nguyên nhân chính xác dẫn đến sự thức tỉnh của Verina vẫn chưa được làm rõ.
-Phân tích mẫu thử cho thấy một &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; không hội tụ với dạng sóng tuần hoàn rõ rệt. Do đó, Verina được phân loại là &lt;te href=850068&gt;Congenital Resonator&lt;/te&gt;.</t>
+Ngoài ra, Mô Hình Phổ Cộng Hưởng của Verina trùng khớp với các mẫu phổ đã biết của sinh vật thực vật. Các phản ứng Đồng Điệu mạnh đã được ghi nhận trong quá trình thử nghiệm, song nguyên nhân chính xác dẫn đến sự thức tỉnh của Verina vẫn chưa được làm rõ.
+Phân tích mẫu thử cho thấy một &lt;te href=850067&gt;Đường Cong Rabelle&lt;/te&gt; không hội tụ với dạng sóng tuần hoàn rõ rệt. Do đó, Verina được phân loại là &lt;te href=850068&gt;Resonator Bẩm Sinh&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -24477,9 +24477,9 @@
         <is>
           <t>Cơ sở Đánh giá: [Đánh giá Cộng hưởng 1159-G]
 Thời điểm chính xác của Sự Thức tỉnh Resonator Lumi vẫn chưa rõ. Hiện tượng phát quang tự phát đã được quan sát từ nhỏ, và cô dần kiểm soát được ánh sáng.
-&lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của Lumi nằm ở chân phải. Quan sát sau Sự Thức tỉnh không phát hiện thay đổi thể chất đáng kể.
+&lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của Lumi nằm ở chân phải. Quan sát sau Sự Thức tỉnh không phát hiện thay đổi thể chất đáng kể.
 Mô hình Phổ Cộng hưởng của Lumi phản ánh đặc tính của ánh sáng. Khi sử dụng Forte, cô có thể chuyển hóa ánh sáng thành năng lượng Electro và cung cấp cho các vật liệu cụ thể.
-Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; không hội tụ với dạng sóng tuần hoàn rõ rệt. Do đó, Lumi được xếp loại là &lt;te href=850068&gt;Congenital Resonator&lt;/te&gt;.</t>
+Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Đường cong Rabelle&lt;/te&gt; không hội tụ với dạng sóng tuần hoàn rõ rệt. Do đó, Lumi được xếp loại là &lt;te href=850068&gt;Resonator Bẩm sinh&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -24550,7 +24550,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>[Bản Ghi Archive Trích Xuất - A.A1001]</t>
+          <t>[Bản Ghi Lưu Trữ Trích Xuất - A.A1001]</t>
         </is>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>[Bản Ghi Archive Trích Xuất - A.A1001]</t>
+          <t>[Bản Ghi Lưu Trữ Trích Xuất - A.A1001]</t>
         </is>
       </c>
     </row>
@@ -24694,12 +24694,12 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>[&lt;te href=850099&gt;Order of the Deep&lt;/te&gt; - Ministry of Holy Rituals Records] 
-Biểu đồ dạng sóng của Resonator Phoebe hiển thị dao động hình elip. Mẫu miền Thời gian ổn định và không có dấu hiệu dao động bất thường. Kết quả test nằm trong phạm vi pha bình thường.
-Độ nguy cấp cộng hưởng: Tương đối cao. Tần số của Resonator Phoebe thể hiện tính ổn định cao với nguy cơ &lt;te href=850073&gt;Overclocking&lt;/te&gt; thấp.
-Hồ sơ không ghi nhận tiền sử Overclocking.
-&lt;i&gt;&lt;te href=850100&gt;Acolyte&lt;/te&gt; Phoebe luôn tuân thủ nghiêm ngặt giáo lý "tĩnh lặng" và "tự kiềm chế", khiến sự ổn định của cô vượt trội so với đồng nghiệp. Quan sát cho thấy khả năng Resonance của Acolyte Phoebe tạo ra tần số ổn định, ảnh hưởng mạnh mẽ đến Echoes và sinh vật &lt;te href=850076&gt;Remnant&lt;/te&gt;. Humans cũng có thể bị ảnh hưởng ở một mức độ nhất định, trải qua sự "hàn gắn" về mặt tinh thần. Điều này khiến cô đặc biệt phù hợp với các vai trò đòi hỏi sự xoa dịu và hòa giải.&lt;/i&gt;
-*Ghi chú mới nhất: Một dao động hình răng cưa ngắn đã được phát hiện trong dạng sóng thông thường của Acolyte Phoebe. Hiện chưa ghi nhận bất thường, nhưng vẫn cần tiếp tục theo dõi, tăng cường chú ý nếu cần thiết.*</t>
+          <t>["Tổ Tacet - Hồ Sơ Bộ Thánh Nghi Lễ"] 
+Biểu đồ sóng cộng hưởng của Resonator Phoebe cho thấy dao động hình elip. Mẫu miền thời gian ổn định, không phát hiện dấu hiệu dao động bất thường. Kết quả kiểm tra nằm trong phạm vi pha bình thường.
+Độ Tới Hạn Cộng Hưởng: Tương đối cao. Tần số của Phoebe thể hiện sự ổn định cao với rủi ro &lt;te href=850073&gt;Quá Tải&lt;/te&gt; thấp.
+Hồ sơ không ghi nhận tiền sử Quá Tải.
+&lt;i&gt;&lt;te href=850100&gt;Tín Đồ&lt;/te&gt; Phoebe luôn tuân thủ nghiêm ngặt giáo lý "tĩnh lặng" và "kiềm chế bản thân", khiến sự ổn định của cô vượt trội so với đồng môn. Quan sát cho thấy khả năng Cộng Hưởng của Tín Đồ Phoebe tạo ra tần số ổn định, tác động mạnh mẽ đến Tiếng Vọng và Sinh Vật &lt;te href=850076&gt;Tàn Dư&lt;/te&gt;. Con người cũng chịu ảnh hưởng ở một mức độ nhất định, trải qua "sự chữa lành" về mặt tinh thần. Điều này khiến cô đặc biệt phù hợp với các vai trò đòi hỏi sự xoa dịu và hòa giải.&lt;/i&gt;
+*Ghi chú mới nhất: Phát hiện dao động hình răng cưa ngắn trong biểu đồ sóng thông thường của Tín Đồ Phoebe. Hiện chưa ghi nhận bất thường, nhưng khuyến nghị tiếp tục theo dõi, tăng cường chú ý nếu cần thiết.</t>
         </is>
       </c>
     </row>
@@ -24770,13 +24770,13 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>[Trích đoạn Thư Giới Thiệu từ Trại Trẻ Mồ Côi của Order Orphanage]
-Ngay khi nhìn thấy &lt;te href=850072&gt;Tacet Mark&lt;/te&gt; phát sáng trên đùi trái phía trên của cô bé, tôi đã lập tức nhận ra đây là phước lành từ &lt;te href=850105&gt;Imperator&lt;/te&gt;.
-...Khả năng Resonance của cô cho phép cô tạo ra ánh sáng, khúc xạ nó thành nhiều dạng lăng kính khác nhau. Ngay cả trong những đêm tối tăm nhất, khi cơn bão đã dập tắt mọi nguồn sáng khác, cô vẫn lấp đầy mọi căn phòng bằng ánh sáng dịu dàng, rạng rỡ. Một thứ ánh sáng ấm áp đến mức truyền tải chính bản chất của hy vọng trong những thời khắc tăm tối nhất. Như đã viết trong &lt;i&gt;Tenets of the Deep&lt;/i&gt;, thứ ánh sáng ấy hẳn đã luôn tồn tại trong trái tim cô, một dấu hiệu cho thấy lòng thành kính không ngừng nghỉ của cô...
-*Bản ghi này đã được chuyển từ Orphanage sang kho lưu trữ của &lt;te href=850099&gt;Order of the Deep&lt;/te&gt;.
-&lt;i&gt;Chúng tôi có lý do để tin rằng khả năng Resonance vô song của &lt;te href=850100&gt;Acolyte&lt;/te&gt; Initiate Phoebe bắt nguồn từ niềm tin kiên định của cô vào Divinity.
-Điều này được thể hiện qua mối quan hệ giữa cô và &lt;ano=Divine Envoys&gt;&lt;te href=850082&gt;Echoes&lt;/te&gt;&lt;/ano&gt;, một sự kết nối đã củng cố niềm tin mà một số tín đồ của chúng ta dành cho cô. Sự tham gia tích cực của cô trong các hoạt động từ thiện đã giúp cô nhận được sự công nhận, do đó chúng tôi đã nhất trí trao cho cô danh hiệu Acolyte sau thời gian tập sự.
-Tuy nhiên, một số người trong Order cho rằng sự gần gũi của cô với Echoes vi phạm giáo lý của Order. Những phước lành từ Divine Envoys phải được chia sẻ một cách công bằng, bởi tình yêu của &lt;te href=850083&gt;Sentinel&lt;/te&gt; dành cho con dân là không thiên vị và không bị vấy bẩn bởi sự thiên vị. Việc quá gần gũi với Divine Envoys có thể dẫn đến những rủi ro không lường trước được. Vì lý do này, chúng tôi không đề xuất bổ nhiệm cô vào Servitude Hall, và tin rằng việc chuyển cô sang Ministry of Holy Rituals sẽ là thận trọng nhất...&lt;/i&gt;</t>
+          <t>["Trích đoạn Thư Giới Thiệu từ Trại Trẻ Mồ Côi Hội]
+Ngay khoảnh khắc tôi nhìn thấy &lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; phát sáng trên đùi trái của cô bé, tôi đã lập tức nhận ra đây là phước lành của &lt;te href=850105&gt;Imperator&lt;/te&gt;.
+...Khả năng Cộng Hưởng cho phép cô bé tạo ra ánh sáng, khúc xạ thành muôn hình vạn trạng. Ngay cả trong những đêm tối tăm nhất, khi bão tố dập tắt mọi nguồn sáng khác, cô vẫn thắp lên từng căn phòng bằng thứ ánh sáng dịu dàng, rực rỡ. Một thứ ánh sáng ấm áp đến mức truyền tải chính tinh thần của hy vọng trong những thời khắc tăm tối nhất. Như đã chép trong &lt;i&gt;Giáo Lý Của Vực Sâu&lt;/i&gt;, thứ ánh sáng ấy hẳn đã luôn tồn tại trong trái tim cô, dấu hiệu của lòng sùng kính không ngừng nghỉ...
+*Bản ghi này đã được chuyển từ Trại Trẻ Mồ Côi sang kho lưu trữ của &lt;te href=850099&gt;Hội Vực Sâu&lt;/te&gt;.
+&lt;i&gt;Chúng tôi có lý do để tin rằng khả năng Cộng Hưởng vô song của Tín Đồ Tập Sự Phoebe bắt nguồn từ niềm tin kiên định vào Thánh Thần.
+Điều này được chứng minh qua mối liên hệ giữa cô và &lt;ano=Thiên Sứ Thần Linh&gt;&lt;te href=850082&gt;Echoes&lt;/te&gt;&lt;/ano&gt;, một sự kết nối đã củng cố niềm tin của một số tín đồ vào cô. Những hoạt động từ thiện tích cực của cô đã giúp cô giành được sự công nhận, do đó chúng tôi đã nhất trí trao cho cô danh hiệu Tín Đồ sau thời gian tập sự.
+Tuy nhiên, một số người trong Hội cho rằng sự gần gũi của cô với Echoes vi phạm giáo lý của Hội. Phước lành của Thiên Sứ Thần Linh phải được chia sẻ công bằng, bởi tình yêu của &lt;te href=850083&gt;Sentinel&lt;/te&gt; dành cho con dân là vô tư và không thiên vị. Quá gần gũi với Thiên Sứ Thần Linh có thể dẫn đến những rủi ro khó lường. Vì lý do này, chúng tôi không khuyến nghị bổ nhiệm cô vào Đại Sảnh Phục Vụ, và cho rằng việc chuyển cô sang Bộ Nghi Lễ Thánh sẽ là thận trọng nhất...&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -24847,12 +24847,12 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Profile Nhân viên Kho Averardo - Quyền truy cập xác nhận
-Name nhân viên: Zani
+          <t>Hồ sơ Nhân viên Kho Averardo - Quyền truy cập xác nhận
+Tên nhân viên: Zani
 Lịch sử Thức tỉnh của nhân viên Zani vẫn còn là ẩn số. Cả trình độ phát triển và tần suất sử dụng Forte của cô đều ở mức cao.
-&lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của Zani chạy chéo qua lưng. Sau khi Thức tỉnh, cơ thể cô đã trải qua những đột biến đáng kể, bao gồm sự xuất hiện của cặp sừng giống cừu đực và một chiếc đuôi mảnh khảnh kéo dài từ xương cụt. Khi Zani kích hoạt Forte, cô có thể tạm thời lưu trữ năng lượng động học dư thừa trong cơ thể để tăng cường khả năng thể chất. Năng lượng này hiện lên dưới dạng những dòng năng lượng sáng chói tràn ra từ sừng, đuôi và tóc. Ngoài ra, những vết dấu phát sáng cũng xuất hiện khắp phần thân trên của cô. Theo Zani, đó là những vết sẹo đã lành theo thời gian, chỉ còn lại những dấu vết mờ nhạt khó nhìn thấy bằng mắt thường. Người ta cho rằng cấu trúc tế nhị của làn da đã lành giúp tập trung năng lượng vào những vùng này.
-Zani kể lại một sự cố vài năm trước, khi cô bị thương nặng trong một vụ tấn công có tổ chức bởi ▇▇▇▇▇▇▇. Chính giữa cuộc tấn công đó, cô đã Thức tỉnh Forte và đẩy lùi kẻ tấn công bằng khả năng mới. Phân tích Mô hình Phổ Cộng hưởng không xác định được nguyên nhân Thức tỉnh của cô. Phân tích mẫu thử cho thấy một &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; không hội tụ. Do đó, Zani được xác định là một &lt;te href=850069&gt;Mutant Resonator&lt;/te&gt; với thời kỳ ủ bệnh.
-&lt;i&gt;"Những đặc điểm thể chất độc đáo sau khi Thức tỉnh của Zani khiến ta nhớ đến những truyền thuyết bị lãng quên mà gia tộc từng sưu tầm. Những câu chuyện ấy kể về những thực thể siêu nhiên kỳ bí, ẩn nấp trong bóng tối từ rất lâu trước &lt;te href=850075&gt;Lament&lt;/te&gt;. Liệu có mối liên hệ nào giữa những truyền thuyết đó và nguyên nhân Thức tỉnh của cô không? Hay chỉ là sự trùng hợp ngẫu nhiên?"&lt;/i&gt; 
+&lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của Zani chạy chéo qua lưng. Sau khi Thức tỉnh, cơ thể cô đã trải qua những đột biến đáng kể, bao gồm sự xuất hiện của cặp sừng giống cừu đực và một chiếc đuôi mảnh khảnh kéo dài từ xương cụt. Khi Zani kích hoạt Forte, cô có thể tạm thời lưu trữ năng lượng động học dư thừa trong cơ thể để tăng cường khả năng thể chất. Năng lượng này hiện lên dưới dạng những dòng năng lượng sáng chói tràn ra từ sừng, đuôi và tóc. Ngoài ra, những vết dấu phát sáng cũng xuất hiện khắp phần thân trên của cô. Theo Zani, đó là những vết sẹo đã lành theo thời gian, chỉ còn lại những dấu vết mờ nhạt khó nhìn thấy bằng mắt thường. Người ta cho rằng cấu trúc tế nhị của làn da đã lành giúp tập trung năng lượng vào những vùng này.
+Zani kể lại một sự cố vài năm trước, khi cô bị thương nặng trong một vụ tấn công có tổ chức bởi ▇▇▇▇▇▇▇. Chính giữa cuộc tấn công đó, cô đã Thức tỉnh Forte và đẩy lùi kẻ tấn công bằng khả năng mới. Phân tích Mô hình Phổ Cộng hưởng không xác định được nguyên nhân Thức tỉnh của cô. Phân tích mẫu thử cho thấy một &lt;te href=850067&gt;Đường cong Rabelle&lt;/te&gt; không hội tụ. Do đó, Zani được xác định là một &lt;te href=850069&gt;Resonator Đột biến&lt;/te&gt; với thời kỳ ủ bệnh.
+&lt;i&gt;"Những đặc điểm thể chất độc đáo sau khi Thức tỉnh của Zani khiến ta nhớ đến những truyền thuyết bị lãng quên mà gia tộc từng sưu tầm. Những câu chuyện ấy kể về những thực thể siêu nhiên kỳ bí, ẩn nấp trong bóng tối từ rất lâu trước &lt;te href=850075&gt;Lời Than Thở&lt;/te&gt;. Liệu có mối liên hệ nào giữa những truyền thuyết đó và nguyên nhân Thức tỉnh của cô không? Hay chỉ là sự trùng hợp ngẫu nhiên?"&lt;/i&gt; 
 &lt;i&gt;"Đừng suy nghĩ quá nhiều. Có khi cô ấy chỉ bị một con Tumbleyak hay con dê nào đó đánh thức thôi."&lt;/i&gt;</t>
         </is>
       </c>
@@ -24923,12 +24923,12 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Cơ sở đánh giá: [Đánh Giá Resonance 2083-G]
+          <t>Cơ sở đánh giá: [Đánh Giá Cộng Hưởng 2083-G]
 Resonator Taoqi đã thức tỉnh khả năng Forte cách đây 3 năm, nhưng không xác định được sự kiện kích hoạt.
-&lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của Taoqi nằm ở vùng giữa hai bả vai. Sau khi thức tỉnh, không ghi nhận thay đổi ngoại hình đáng kể nào. Các thử nghiệm cho thấy da cô có độ cứng vượt trội so với người bình thường.
+&lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của Taoqi nằm ở vùng giữa hai bả vai. Sau khi thức tỉnh, không ghi nhận thay đổi ngoại hình đáng kể nào. Các thử nghiệm cho thấy da cô có độ cứng vượt trội so với người bình thường.
 Cô sở hữu khả năng tạo ra một trường lực đặc biệt, hình thành lá chắn bảo vệ bản thân và đồng đội khỏi nguy hiểm.
-Mô Hình Phổ Resonance của Taoqi không giống bất kỳ mẫu phổ đã biết nào. Nguyên nhân thức tỉnh của cô vẫn còn là ẩn số.
-Phân tích mẫu thử cho thấy một &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; không hội tụ với xu hướng tăng ổn định. Đôi khi xuất hiện dao động trong phạm vi bình thường. Do đó, Taoqi được phân loại là &lt;te href=850070&gt;Natural Resonator&lt;/te&gt;.</t>
+Mô Hình Phổ Cộng Hưởng của Taoqi không giống bất kỳ mẫu phổ đã biết nào. Nguyên nhân thức tỉnh của cô vẫn còn là ẩn số.
+Phân tích mẫu thử cho thấy một &lt;te href=850067&gt;Đường Cong Rabelle&lt;/te&gt; không hội tụ với xu hướng tăng ổn định. Đôi khi xuất hiện dao động trong phạm vi bình thường. Do đó, Taoqi được phân loại là &lt;te href=850070&gt;Resonator Tự Nhiên&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -24999,13 +24999,13 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Cơ sở đánh giá: [Đánh Giá Resonance 1856-G]
+          <t>Cơ sở đánh giá: [Đánh Giá Cộng Hưởng 1856-G]
 Thời điểm chính xác Resonator Danjin thức tỉnh vẫn chưa xác định. Đáng chú ý, trong sự kiện thức tỉnh của Resonator Danjin, cô đã thể hiện trạng thái mất kiểm soát về mặt cảm xúc. Có giả thuyết cho rằng những cảm xúc mãnh liệt có thể là chất xúc tác cho sự thức tỉnh của cô.
-Một &lt;te href=850072&gt;Tacet Mark&lt;/te&gt; nằm trên cánh tay trên bên trái của Danjin. Quan sát cho thấy những thay đổi rõ rệt về đặc điểm thể chất sau khi thức tỉnh. Một thay đổi đáng chú ý là đồng tử của cô chuyển sang màu đỏ sau khi sử dụng Forte đến một ngưỡng nhất định.
+Một &lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; nằm trên cánh tay trên bên trái của Danjin. Quan sát cho thấy những thay đổi rõ rệt về đặc điểm thể chất sau khi thức tỉnh. Một thay đổi đáng chú ý là đồng tử của cô chuyển sang màu đỏ sau khi sử dụng Forte đến một ngưỡng nhất định.
 Biến động tần số của Resonator Danjin mạnh hơn bình thường, thể hiện những thay đổi tức thời bất thường có thể gây tổn hại vật lý đến môi trường xung quanh và bất kỳ sinh vật nào trong đó nếu không được kiểm soát.
-Test thực nghiệm cho thấy tiềm năng hủy diệt của Danjin vượt trội hơn người bình thường 78,94%.
-Mô hình Phổ Resonance của Resonator này trùng khớp với mẫu máu người. Các thử nghiệm cho thấy phản ứng Resonance mạnh mẽ, tuy nhiên nguyên nhân thức tỉnh của Danjin vẫn chưa rõ ràng.
-Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; không hội tụ với đoạn tăng đột ngột ở phần giữa. Do đó, Danjin được phân loại là &lt;te href=850069&gt;Mutant Resonator&lt;/te&gt;.</t>
+Kiểm tra thực nghiệm cho thấy tiềm năng hủy diệt của Danjin vượt trội hơn người bình thường 78,94%.
+Mô hình Phổ Cộng Hưởng của Resonator này trùng khớp với mẫu máu người. Các thử nghiệm cho thấy phản ứng Cộng Hưởng mạnh mẽ, tuy nhiên nguyên nhân thức tỉnh của Danjin vẫn chưa rõ ràng.
+Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Đường cong Rabelle&lt;/te&gt; không hội tụ với đoạn tăng đột ngột ở phần giữa. Do đó, Danjin được phân loại là &lt;te href=850069&gt;Resonator Đột Biến&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -25075,7 +25075,7 @@
       <c r="M370" t="inlineStr">
         <is>
           <t>Biểu đồ sóng của Resonator Camellya dao động như kim châm. Mô hình miền Thời Gian cho thấy hoạt động hỗn loạn với tần số cực cao. Trong quá trình kiểm tra, dữ liệu miền Thời Gian bị biến dạng nghiêm trọng, giá trị đỉnh không xác định được.
-Mức Độ Tới Hạn Cộng Hưởng: Low. Tần số của Camellya cực kỳ bất ổn, nguy cơ &lt;te href=850073&gt;Overclocking&lt;/te&gt; cao.
+Mức Độ Tới Hạn Cộng Hưởng: Thấp. Tần số của Camellya cực kỳ bất ổn, nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; cao.
 Camellya có tiền sử Quá Tải. Mức Quá Tải cao nhất ghi nhận: Nghiêm trọng.
 Theo báo cáo của Camellya, các đợt Quá Tải xảy ra sau khi Cô Tỉnh Thức, thường liên quan đến quá trình phục hồi rối loạn ███ và dao động cảm xúc. Ở giai đoạn sau, triệu chứng tiến triển thành toàn thân hóa thực vật, gây suy giảm ngôn ngữ, mất phương hướng nhận thức và cơn đau dữ dội. Nguyên nhân kích hoạt hiện tại vẫn chưa xác định.
 Bắt buộc kiểm tra sức khỏe định kỳ và can thiệp cưỡng chế theo lịch trình do hiệu quả tư vấn tâm lý rất hạn chế.</t>
@@ -25148,11 +25148,11 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Cơ sở đánh giá: [Đánh Giá Resonance RA2███-G]
+          <t>Cơ sở đánh giá: [Đánh Giá Cộng Hưởng RA2███-G]
 Thời điểm chính xác Resonator Camellya thức tỉnh không rõ ràng do chứng rối loạn ███ của cô. Từ sau khi thức tỉnh, cô đã có thể sử dụng Forte của mình.
-&lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của Resonator Camellya nằm ở ngực. Sau khi thức tỉnh, cơ thể cô đã xuất hiện những dấu hiệu rõ rệt của hiện tượng thực vật hóa cơ thể. Cả cánh tay phải và đầu đều có sự biến đổi, mức độ thay đổi tăng lên theo sự dao động của tần số.
-Mô hình Phổ Resonance của Camellya gần giống với hình dáng hoa trà, cho thấy phản ứng Đồng Điệu mạnh mẽ. Tuy nhiên, nguyên nhân dẫn đến sự thức tỉnh của Camellya vẫn chưa rõ ràng vì chưa tìm thấy vật thể nào phù hợp với những thay đổi trong Mô hình Phổ Resonance của cô.
-Giai đoạn đầu của &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; xuất hiện nhiều dao động bất thường. Khi Rabelle's Curve vượt quá ngưỡng tới hạn, █████████████████.
+&lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của Resonator Camellya nằm ở ngực. Sau khi thức tỉnh, cơ thể cô đã xuất hiện những dấu hiệu rõ rệt của hiện tượng thực vật hóa cơ thể. Cả cánh tay phải và đầu đều có sự biến đổi, mức độ thay đổi tăng lên theo sự dao động của tần số.
+Mô hình Phổ Cộng Hưởng của Camellya gần giống với hình dáng hoa trà, cho thấy phản ứng Đồng Điệu mạnh mẽ. Tuy nhiên, nguyên nhân dẫn đến sự thức tỉnh của Camellya vẫn chưa rõ ràng vì chưa tìm thấy vật thể nào phù hợp với những thay đổi trong Mô hình Phổ Cộng Hưởng của cô.
+Giai đoạn đầu của &lt;te href=850067&gt;Đường Cong Rabelle&lt;/te&gt; xuất hiện nhiều dao động bất thường. Khi Đường Cong Rabelle vượt quá ngưỡng tới hạn, █████████████████.
 &lt;i&gt;"Đối tượng này bị nghi ngờ là Resonator Nhân Tạo. Tuy nhiên, mô hình đường cong hiện tại không khớp với bất kỳ mẫu đã biết nào. Do đó, báo cáo này tạm thời được niêm phong."&lt;/i&gt;</t>
         </is>
       </c>
@@ -25229,9 +25229,9 @@
       <c r="M372" t="inlineStr">
         <is>
           <t>Cấp độ: Tuyệt Mật
-&lt;te href=850094&gt;Fisalia&lt;/te&gt; - Bản ghi của Butler Sebastian: Quản lý Sức khỏe Tâm thần của Gia chủ
-Những trải nghiệm thời thơ ấu, những thử thách, cùng việc sử dụng kéo dài Khả năng "&lt;te href=850119&gt;Illusory Dream&lt;/te&gt;" đã gây tổn thương không thể phục hồi cho cả tinh thần lẫn thể xác của Quý cô.
-Hiện tại, một phần tần số ghi lại của bà đã bị mất. Dựa vào sự gia tăng dạng sóng, phần bị thiếu có thể rất đột ngột, gần như chạm ngưỡng &lt;te href=850073&gt;Overclocking&lt;/te&gt;...
+&lt;te href=850094&gt;Fisalia&lt;/te&gt; - Bản ghi của Quản gia Sebastian: Quản lý Sức khỏe Tâm thần của Gia chủ
+Những trải nghiệm thời thơ ấu, những thử thách, cùng việc sử dụng kéo dài Khả năng "&lt;te href=850119&gt;Giấc Mộng Ảo Ảnh&lt;/te&gt;" đã gây tổn thương không thể phục hồi cho cả tinh thần lẫn thể xác của Quý cô.
+Hiện tại, một phần tần số ghi lại của bà đã bị mất. Dựa vào sự gia tăng dạng sóng, phần bị thiếu có thể rất đột ngột, gần như chạm ngưỡng &lt;te href=850073&gt;Quá Tải&lt;/te&gt;...
 Những dạng sóng còn lại thể hiện một dạng phân cực hiếm gặp, và ở mức tồi tệ nhất, nhiều dạng sóng riêng biệt dường như đã xuất hiện:
 * Dạng sóng α dao động dữ dội.
 * Dạng sóng β cực kỳ ổn định, không có dấu hiệu dao động bất thường.
@@ -25309,12 +25309,12 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Level: Công Khai
+          <t>Cấp: Công Khai
 &lt;te href=850094&gt;Fisalia&lt;/te&gt; Hồ sơ Khám bệnh của Dược sĩ Rosemary: Ấn bản Đặc biệt Được Gia chủ Phê duyệt
 Rõ ràng là người đứng đầu gia tộc Fisalia hiện nay, Quý bà Cantarella, đại diện cho đỉnh cao của Forte liên quan đến chất độc trong gia tộc. Thật vinh dự khi được mời đến lâu đài để kiểm tra sức khỏe cho bà, cũng như được phép tự do tiếp cận khu vườn của &lt;te href=850095&gt;Porto-Veno Castle&lt;/te&gt; cho mục đích nghiên cứu.
 Khả năng của Quý bà Cantarella là một dạng độc tố gây ảo giác hiếm có, khác biệt hoàn toàn với những loại độc gây chết người thường thấy trong gia tộc. Không giống như các loại độc thông thường, chất độc này không gây tử vong ngay lập tức. Khi đàn sứa xuất hiện từ chiếc dù của bà, một biển ảo ảnh tuyệt đẹp sẽ hình thành xung quanh. Người bị nhiễm độc sẽ trải qua ảo giác, có thể là những khát khao sâu thẳm nhất hoặc những ảo ảnh được tạo ra. Nếu họ ở lại quá lâu trong biển ảo ảnh này, tê liệt sẽ ập đến, sau đó là bất tỉnh, và cuối cùng, nếu tác động kéo dài, sẽ dẫn đến cái chết.
 Sự điều khiển khả năng của Quý bà Cantarella đạt đến trình độ điêu luyện. Ở mức độ tinh tế nhất, bà có thể gây ra ảo giác mà không gây tổn hại về thể chất.
-Dù sức mạnh này là con dao hai lưỡi, thường gây hại cho cả người sử dụng, nhưng phong thái duyên dáng và điềm tĩnh của Quý bà Cantarella cho thấy bà không bị ảnh hưởng quá nhiều bởi "&lt;te href=850119&gt;Illusory Dream&lt;/te&gt;". Hay ít nhất, có vẻ như vậy… phải không nhỉ?
+Dù sức mạnh này là con dao hai lưỡi, thường gây hại cho cả người sử dụng, nhưng phong thái duyên dáng và điềm tĩnh của Quý bà Cantarella cho thấy bà không bị ảnh hưởng quá nhiều bởi "&lt;te href=850119&gt;Giấc Mộng Ảo Ảnh&lt;/te&gt;". Hay ít nhất, có vẻ như vậy… phải không nhỉ?
 Ghi chú: Quý bà Cantarella hoàn toàn hiểu rõ khả năng của mình. Thật hiếm khi bà cho phép tôi khám cho bà. Thành thật mà nói, điều đó khiến tôi hơi lo lắng… Hy vọng là tôi không mắc sai lầm nào.</t>
         </is>
       </c>
@@ -25391,17 +25391,17 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Thay vì tên thật, Sanhua thường được gọi là "&lt;te href=850124&gt;Magistrate's Bodyguard&lt;/te&gt;."
+          <t>Thay vì tên thật, Sanhua thường được gọi là "&lt;te href=850124&gt;Vệ sĩ của Quan Phán&lt;/te&gt;."
 Sanhua luôn đứng lặng lẽ phía sau Jinhsi, giữ khoảng cách vừa đủ. Dáng đứng thẳng tắp, hiên ngang, ẩn mình trong góc khuất ánh nhìn của người khác, như một lưỡi kiếm sắc bén sẵn sàng tuốt ra bất cứ lúc nào.
-Dù phần lớn tiếng nói phản đối Jinhsi đã lắng xuống, vẫn còn một số kẻ dám thử thách quyền uy của nàng. Vì Jinhsi vẫn giữ chức &lt;te href=850084&gt;Jinzhou&lt;/te&gt; của &lt;te href=850091&gt;Magistrate&lt;/te&gt;, nên vệ sĩ có vẻ cứng nhắc và thô lỗ bên cạnh nàng trở thành mục tiêu dễ dàng hơn để gây sức ép. Ít nhất, họ nghĩ vậy.
+Dù phần lớn tiếng nói phản đối Jinhsi đã lắng xuống, vẫn còn một số kẻ dám thử thách quyền uy của nàng. Vì Jinhsi vẫn giữ chức &lt;te href=850084&gt;Quan Phán&lt;/te&gt; của &lt;te href=850091&gt;Jinzhou&lt;/te&gt;, nên vệ sĩ có vẻ cứng nhắc và thô lỗ bên cạnh nàng trở thành mục tiêu dễ dàng hơn để gây sức ép. Ít nhất, họ nghĩ vậy.
 Dù yêu cầu của họ có vô lý đến đâu, Sanhua vẫn luôn hoàn thành một cách hoàn hảo đến mức không thể chê vào đâu được.
 Với khả năng quản lý thời gian tuyệt vời, trí tuệ sắc bén, phong thái điềm tĩnh dưới áp lực và kỹ năng đàm phán khéo léo... ngay cả những kẻ chỉ trích gay gắt nhất cũng phải câm lặng.
 Là vệ sĩ của Quan Phán, Sanhua xử lý cả những vị khách ban ngày khó chịu lẫn những kẻ không mời mà đến lẩn khuất trong bóng tối.
 Là Quan Phán của Jinzhou, Jinhsi là mục tiêu hàng đầu với giá trị treo thưởng cao. Những vị khách không mời mà đến không chỉ muốn uống trà, nhưng họ sẽ sớm nhận ra sai lầm của mình: thay vì trà nóng, họ đối mặt với lưỡi kiếm sắc bén của vệ sĩ. Người vệ sĩ đôi mắt đỏ thẫm này dường như có khả năng phát hiện dối trá một cách kỳ lạ. Trong nháy mắt, cô biến thành một Asura đáng sợ sẵn sàng ra tay.
 Một nhát chém nhanh gọn khiến tay chân run rẩy, ống quần đứt lìa rơi xuống không trung lạnh lẽo. Chỉ thế thôi cũng đủ khiến hầu hết những kẻ không mời mà đến phải khiếp vía. Đương nhiên, khi lưỡi kiếm trở về vỏ, mọi bóng tối và âm mưu đen tối đều bị xóa sạch. Ánh hào quang của Jinhsi vẫn nguyên vẹn, không vướng chút bẩn nào.
 Nhưng đôi khi, ngay cả Sanhua cũng gặp phải những bất ngờ trong cuộc sống...
-"Hello. Chắc cô là vệ sĩ của Bà Quan Phán?"
-Đó là lời của một Resonator lạ mặt đứng trước mặt cô, mang cùng tần số hình người xinh đẹp như Jinhsi.
+"Xin chào. Chắc cô là vệ sĩ của Bà Quan Phán?"
+Đó là lời của một Cộng Hưởng Giả lạ mặt đứng trước mặt cô, mang cùng tần số hình người xinh đẹp như Jinhsi.
 Thế giới của cô bỗng dậy sóng với những gợn sóng mới.</t>
         </is>
       </c>
@@ -25489,7 +25489,7 @@
 Từ nhỏ, Sanhua đã trầm lặng và dè dặt, không giỏi giao tiếp với người khác. Một luồng khí lạnh luôn bao quanh cô, ngăn cách cô với thế giới. Những người qua đường đều e dè trước những vết bỏng lạnh bí ẩn mà nó gây ra.
 Cô cảnh giác, nguy hiểm và khó đoán. Có lẽ khó ai tưởng tượng được một người như Sanhua lại thường xuyên gặp ác mộng về tuyết.
 Trong giấc mơ, cô luôn lạc lõng trong bóng tối vô tận, tìm kiếm một cánh đồng tuyết hay một tia sáng le lói. Nhưng ngay khoảnh khắc sau, cô đã nằm trên mặt đất phủ tuyết, bao quanh là những con quái vật méo mó. Chúng gặm nhấm cô khi cô nằm giữa hàng trăm xác chết vỡ vụn. Khi chúng móc mắt cô, bóng tối ập xuống, chỉ còn lại những cái bóng chập chờn của chúng. Rồi cô giật mình tỉnh dậy.
-Khi trưởng thành, Forte của cô ngày càng mạnh mẽ. Con quỷ bất an ẩn náu trong người thúc giục cô nghe theo bản năng thèm khát của &lt;te href=850081&gt;TDs&lt;/te&gt;, muốn nuốt chửng tần số: sức mạnh của băng giá ngày càng khó kiểm soát, và ngay cả tần số giữa con người với Tacet Discord cũng dần trở nên khó phân biệt.
+Khi trưởng thành, Forte của cô ngày càng mạnh mẽ. Con quỷ bất an ẩn náu trong người thúc giục cô nghe theo bản năng thèm khát của &lt;te href=850081&gt;Tacet Discord&lt;/te&gt;, muốn nuốt chửng tần số: sức mạnh của băng giá ngày càng khó kiểm soát, và ngay cả tần số giữa con người với Tacet Discord cũng dần trở nên khó phân biệt.
 Đôi lúc, Sanhua tưởng mình đã thoát khỏi cơn ác mộng, nhưng rồi nhận ra mình vẫn đang mắc kẹt trong đó và đã biến thành một con quái vật. Phải chăng do cô thiếu lòng trắc ẩn, hay do sự khắc nghiệt của tuyết? Hay có lẽ, cô vốn dĩ đã là một phần của tuyết từ đầu.
 Đối mặt với số phận không thể tránh khỏi gắn liền với quỷ dữ, Sanhua bắt đầu cuộc hành trình tự lưu đày.
 Gần đây, Sanhua vẫn mơ về tuyết.
@@ -25497,12 +25497,12 @@
 "Xin lỗi tiểu thư..." Sanhua xin lỗi vì không hoàn thành nhiệm vụ.
 Một thiếu nữ đang say sưa viết dưới ánh đèn. Nhận thấy có động tĩnh, cô ngẩng đầu lên, "Ta đã bảo cô nghỉ ngơi mà, Sanhua. Không có cô, ta không thể hoàn thành nổi một nửa trước sáng mai. Cô thức cả đêm để sắp xếp chúng à."
 "Tiểu thư cần nghỉ ngơi. Hãy để tôi xử lý những thứ này."
-"Thôi nào, Sanhua. Ta có đành lòng để cô một mình xử lý đống giấy tờ nhàm chán này đâu. Not a chance." Jinhsi suy nghĩ một lát rồi nở nụ cười tinh nghịch, "Nếu cô muốn giúp, thì cứ ngồi lại trò chuyện với ta một lát. Ta sắp xong rồi."
+"Thôi nào, Sanhua. Ta có đành lòng để cô một mình xử lý đống giấy tờ nhàm chán này đâu. Không đời nào." Jinhsi suy nghĩ một lát rồi nở nụ cười tinh nghịch, "Nếu cô muốn giúp, thì cứ ngồi lại trò chuyện với ta một lát. Ta sắp xong rồi."
 "Vâng ạ. Tiểu thư muốn nói chuyện gì ạ? Tôi có thể tụng Kinh Tâm cho tiểu thư không?"
 "Ồ, vậy thì kể ta nghe cô mơ thấy gì đi? Ta nghe thấy cô lẩm bẩm trong giấc ngủ đấy."
 "Có lẽ tôi đang tụng Kinh Tâm trong mơ thôi ạ."
 "...Chúng ta có nhất thiết phải quay lại chuyện đó không? Thật lòng mà nói, làm việc với đống tài liệu này bắt đầu làm ta mệt mỏi rồi..."
-"Hmm... Tôi mơ thấy tiểu thư. Tiểu thư đứng giữa tuyết... trông thật đẹp."
+"Hừm... Tôi mơ thấy tiểu thư. Tiểu thư đứng giữa tuyết... trông thật đẹp."
 Sanhua mỉm cười ấm áp. Hành trình phía trước của cô không còn cô đơn nữa.</t>
         </is>
       </c>
@@ -25681,23 +25681,23 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Kể từ khi gia nhập &lt;te href=850130&gt;Liondance Troupe&lt;/te&gt;, Lingyang luôn đối xử với mọi người bằng sự nhiệt huyết, mong muốn trở thành ngọn lửa xua tan nỗi sợ hãi cho những người xung quanh. Nhưng số phận lại trêu ngươi khi cậu phát hiện Forte của mình lại liên quan đến thứ băng giá rét buốt.
+          <t>Kể từ khi gia nhập &lt;te href=850130&gt;Đoàn Múa Lân&lt;/te&gt;, Lingyang luôn đối xử với mọi người bằng sự nhiệt huyết, mong muốn trở thành ngọn lửa xua tan nỗi sợ hãi cho những người xung quanh. Nhưng số phận lại trêu ngươi khi cậu phát hiện Forte của mình lại liên quan đến thứ băng giá rét buốt.
 "Nhưng chẳng ai yêu cái lạnh cả," cậu suy nghĩ, "Dù đã sống sót qua cái lạnh vô số lần, mình vẫn sợ nó. Làm sao mình có thể giúp người khác vượt qua nỗi sợ bằng khả năng này?"
-Nỗi thất vọng đưa Lingyang trở lại bãi tập, nơi cậu lao mình vào điệu múa nhịp nhàng trên Plum Blossom Pole, như thể tìm kiếm một lối thoát cho những hỗn loạn trong lòng.
+Nỗi thất vọng đưa Lingyang trở lại bãi tập, nơi cậu lao mình vào điệu múa nhịp nhàng trên Cột Mận Hoa, như thể tìm kiếm một lối thoát cho những hỗn loạn trong lòng.
 Chính lúc đó, sư phụ của cậu tiến đến, cảm nhận được sự đấu tranh trong lòng Lingyang và khích lệ cậu chia sẻ tâm tư.
 "Haha, ra là vậy. À mà này, cậu nhóc, cậu vẫn chưa có tên à?" sư phụ hỏi.
 "Tên ư? Có quan trọng không?" Lingyang đáp.
 "Với con người thì có đấy. Tên mang theo những kỳ vọng và lời chúc phúc của cha mẹ. Nhưng liệu cậu có hoàn thành hay phản bội những kỳ vọng đó thì hoàn toàn là do cậu quyết định," sư phụ giải thích rồi tiếp tục, "Vì cậu không nhớ quá khứ và chúng ta cũng không tìm được cha mẹ cậu, sao không tự chọn cho mình một cái tên? Cậu nhóc à, trong tương lai, cậu muốn trở thành người như thế nào?"
 "Người ư?" Lingyang thắc mắc, khiến sư phụ đổi cách hỏi, "Thế bây giờ cậu muốn làm gì nhất?"
-"À! Con muốn đứng trên Plum Blossom Pole cao nhất thế giới! Cao hơn cả mặt trời ấy!"
+"À! Con muốn đứng trên Cột Mận Hoa cao nhất thế giới! Cao hơn cả mặt trời ấy!"
 "Haha, ước mơ lớn đấy! Nhưng đứng quá gần mặt trời có thể bị thiêu cháy và tan chảy đấy, biết không?"
-"Hmm... có thể sẽ hơi đau đầu, nhưng con không sợ! Con muốn mang lại niềm vui và bình yên cho mọi người. Và! Con cũng muốn trở thành người có thể mang lại hơi ấm và dũng khí cho họ! Nếu mặt trời làm con tan chảy, con sẽ trở nên nóng hơn cả mặt trời và làm nó tan chảy trước!"
+"Hừm... có thể sẽ hơi đau đầu, nhưng con không sợ! Con muốn mang lại niềm vui và bình yên cho mọi người. Và! Con cũng muốn trở thành người có thể mang lại hơi ấm và dũng khí cho họ! Nếu mặt trời làm con tan chảy, con sẽ trở nên nóng hơn cả mặt trời và làm nó tan chảy trước!"
 "Hahaha, tham vọng ghê nhỉ? Được rồi. Thế 'Lingyang' thì sao? Nó thể hiện khát vọng vượt qua mặt trời của cậu—'Dương' ấy."
 "Giờ cậu đã có tên, nghĩa là từ nay cậu là một cá nhân độc lập. Cậu có thể coi ngày hôm nay là sinh nhật của mình."
 "Sinh nhật? Đó là gì?"
 "À, sinh nhật là ngày con người dùng để suy ngẫm về sự trôi qua của thời gian và sự ngắn ngủi của cuộc đời. Quan trọng hơn, đó là ngày để kỷ niệm sự ra đời của chúng ta, biết ơn những điều kỳ diệu đã gặp trên hành trình trưởng thành."
 "Vậy thì..."
-"Happy birthday! Lingyang!"
+"Chúc mừng sinh nhật! Lingyang!"
 Các sư huynh, sư tỷ của Lingyang đột nhiên xuất hiện bên cạnh, đồng thanh hô vang "Lingyang".
 "Ling... yang..."
 Lingyang lặng lẽ nhẩm lại món quà quý giá nhất đời mình trong lòng. Cậu thì thầm như đang suy ngẫm ý nghĩa sâu xa của nó. Với trái tim đập rộn ràng, Lingyang thầm hứa sẽ sống xứng đáng với kỳ vọng trong cái tên ấy và bảo vệ những người cậu yêu quý.
@@ -25860,9 +25860,9 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Youhu luôn mang theo một chiếc hộp giống cuộn giấy chứa đầy những mô hình thu nhỏ của các món đồ cổ mà cô đã thẩm định, mỗi chiếc đều được tạo ra bằng Forte của cô. Những mô hình này không chỉ là vật kỷ niệm mà còn là công cụ tiện dụng để chống lại &lt;te href=850081&gt;Tacet Discords&lt;/te&gt;. Vào mùa hè, chúng còn có thể dùng làm hộp giữ lạnh. Chỉ cần bỏ trái cây vào cùng một mô hình đá lạnh, và voilà—đồ ăn nhẹ mát lạnh đã sẵn sàng!
+          <t>Youhu luôn mang theo một chiếc hộp giống cuộn giấy chứa đầy những mô hình thu nhỏ của các món đồ cổ mà cô đã thẩm định, mỗi chiếc đều được tạo ra bằng Forte của cô. Những mô hình này không chỉ là vật kỷ niệm mà còn là công cụ tiện dụng để chống lại &lt;te href=850081&gt;Tacet Discord&lt;/te&gt;. Vào mùa hè, chúng còn có thể dùng làm hộp giữ lạnh. Chỉ cần bỏ trái cây vào cùng một mô hình đá lạnh, và voilà—đồ ăn nhẹ mát lạnh đã sẵn sàng!
 Bên trong hộp còn có một cuốn sổ nhỏ, nơi cô ghi lại những bài thơ ngắn về mỗi món đồ cổ mà cô gặp:
-"Một gã ở &lt;te href=850085&gt;Ministry of Development&lt;/te&gt; nhờ tôi tìm chiếc bình sứ tráng men thất lạc từ &lt;te href=850093&gt;Huanglong&lt;/te&gt;. Ghi chú lại!"
+"Một gã ở &lt;te href=850085&gt;Bộ Phát Triển&lt;/te&gt; nhờ tôi tìm chiếc bình sứ tráng men thất lạc từ &lt;te href=850093&gt;Huanglong&lt;/te&gt;. Ghi chú lại!"
 "Gã thương nhân kia chắc chắn đã có được chiếc lư hương tam chân men ngọc từ con đường mờ ám! Tôi đã gợi ý hắn nên trả lại, nhưng ai biết hắn có nghe không. Phải để mắt tới hắn mới được."
 "Thợ mộc ở cổng thành đang chặt gỗ bằng con dao cổ hàng thế kỷ! Trơ tráo quá! Thật đáng xấu hổ! Tôi sẽ... bỏ qua lần này. Nhưng phải nói cho hắn biết giá trị thật của con dao sau."
 Những ghi chú thú vị này giúp cô giữ cho ký ức luôn tươi mới.
@@ -26040,18 +26040,18 @@
 Carlotta bước lên sàn nhảy, trao cho đại diện Fisalia một nụ cười lịch sự. 
 "Tối nay trông cô thật quyến rũ, cô Carlotta. Cô có kế hoạch gì sau này không?" 
 "Không, chỉ đơn giản là tận hưởng buổi tối thôi," Carlotta đáp, những ngón tay cô nhẹ nhàng đặt lên eo của người phụ nữ tuyệt đẹp, bàn tay nàng từ từ trượt lên cánh tay Carlotta. Lòng bàn tay họ chạm nhau, cơ thể họ đung đưa hòa quyện, những lớp váy xếp nếp như những cánh hoa đang nở rộ. 
-"Thôi nào, chắc chắn cô không chỉ đến đây để khiêu vũ đâu? Chắc hẳn có những người The Montellis khác ở đây phải không?" 
+"Thôi nào, chắc chắn cô không chỉ đến đây để khiêu vũ đâu? Chắc hẳn có những người Montellis khác ở đây phải không?" 
 "Cô biết đấy, tôi rất thích những buổi tiệc như thế này. Nhìn cách cô quan sát, tôi đoán gia tộc Fisalias có rất nhiều lợi ích trong đêm nay." 
 Người phụ nữ xinh đẹp thay đổi nhịp điệu, nắm chặt hơn khi cố giành lấy quyền dẫn dắt. Carlotta để cho lực kéo ấy dẫn dắt mình, xoay người dễ dàng trở lại vòng tay nàng. 
-"Order nắm giữ vận mệnh của thành phố này. Gia tộc Fisalias sẽ không để các người phá vỡ sự cân bằng mong manh. Tầm nhìn của The Montellis quá cực đoan." 
+"Order nắm giữ vận mệnh của thành phố này. Gia tộc Fisalias sẽ không để các người phá vỡ sự cân bằng mong manh. Tầm nhìn của Montellis quá cực đoan." 
 "Cô gọi chúng tôi là cực đoan, nhưng chính cô mới là kẻ thèm khát quyền lực. Cô muốn kiểm soát dòng chảy, như thể nó có thể đứng yên mãi được." 
-Điệu nhảy của họ ngày càng trở nên cuồng loạn khi cả hai đều cố giành thế thượng phong. Nó biến thành một điệu nhảy Dodge tinh tế, những khoảnh khắc tiếp xúc ngắn ngủi trước khi tách ra trong cùng một chuyển động uyển chuyển. Khi nhạc đạt đến cao trào, người phụ nữ lùi lại, liếc nhìn đám đông, ánh mắt tìm kiếm những thành viên The Montellis khác đang ẩn nấp. 
+Điệu nhảy của họ ngày càng trở nên cuồng loạn khi cả hai đều cố giành thế thượng phong. Nó biến thành một điệu nhảy né tránh tinh tế, những khoảnh khắc tiếp xúc ngắn ngủi trước khi tách ra trong cùng một chuyển động uyển chuyển. Khi nhạc đạt đến cao trào, người phụ nữ lùi lại, liếc nhìn đám đông, ánh mắt tìm kiếm những thành viên Montellis khác đang ẩn nấp. 
 Carlotta nắm chặt tay nàng, kéo cô trở lại điệu nhảy nhịp nhàng. Âm nhạc níu giữ họ bên nhau. Người phụ nữ không thể thoát ra, và nàng cũng không dám gây ồn ào. Tất cả những gì nàng có thể làm là nhìn Carlotta với ác ý. 
-"Gia tộc The Montellis có tai mắt ở khắp nơi. Từ đầu, cô đã nhắm đến những 'đứa con' của tôi. Tôi hy vọng cô đã sẵn sàng để khiêu vũ cho đến khi cái chết chia lìa chúng ta." 
+"Gia tộc Montellis có tai mắt ở khắp nơi. Từ đầu, cô đã nhắm đến những 'đứa con' của tôi. Tôi hy vọng cô đã sẵn sàng để khiêu vũ cho đến khi cái chết chia lìa chúng ta." 
 Điệu nhảy của họ đột nhiên mang một ý nghĩa mới. Carlotta dừng lại, xoay người, tấn công, và những mục tiêu ngã gục... Điệu tango của cô biến thành một điệu valse chết chóc duy nhất với những vệ sĩ và "đứa con" của người phụ nữ, cho đến nơi đây, cuộc chiến của họ bị cắt ngang bởi cơn mưa không ngừng. 
 Carlotta cảm thấy nọc độc thấm vào vết thương, chất độc làm tê liệt tâm trí đang tàn phá tĩnh mạch cô. Một thứ gì đó có vị kim loại chảy ra từ khóe miệng. Carlotta cười khẩy, thốt lên một tiếng cười đắng chát. 
 Đây có phải là số phận của người bạn nhảy cuối cùng của nàng ta không? Dù sao đi nữa, sớm muộn gì những kẻ dấn thân vào cái chết cũng sẽ ôm lấy nó. 
-Khi chất độc tước đi mọi giác quan, xé nát lý trí và sự tỉnh táo của Carlotta, cô cúi chào, rồi với một nụ cười, tỏa sáng rực rỡ như biến đêm thành ngày. Nếu cái chết là điều không thể tránh khỏi, tại sao lại phải kìm Dodgen điệu nhảy của cả một đời người...?</t>
+Khi chất độc tước đi mọi giác quan, xé nát lý trí và sự tỉnh táo của Carlotta, cô cúi chào, rồi với một nụ cười, tỏa sáng rực rỡ như biến đêm thành ngày. Nếu cái chết là điều không thể tránh khỏi, tại sao lại phải kìm nén điệu nhảy của cả một đời người...?</t>
         </is>
       </c>
     </row>
@@ -26141,7 +26141,7 @@
 Điều cô thực sự muốn và những gì cô đang làm... Carlotta thấy giữa chúng chẳng có mấy khác biệt. Cuộc đời cứ thế trôi, và qua đó, con người cần những niềm tin, lý tưởng hay người thân yêu để làm điểm tựa. Với Carlotta, trở thành một Montelli chính là điểm tựa—và gia tộc Montelli là tất cả.
 "Không, cháu đã nhầm rồi," ông nói khẽ, như thể nhìn thấu suy nghĩ của Carlotta, "Một Montelli chân chính không chỉ sống vì gia đình. Cô không tồn tại chỉ để tuân theo những quy tắc, dù là do ta hay gia tộc đặt ra. Cô phải cảm nhận thế giới và tự đặt ra quy tắc của riêng mình."
 "Ta muốn thấy cháu tỏa sáng vì ta tin cháu có ánh sáng từ bên trong. Trước khi cháu tự gò mình vào định nghĩa về một Montelli, cháu mới chỉ bắt đầu định ra quy tắc của riêng mình thôi."
-Bầu trời ngoài kia bắt đầu sáng dần... Cuối cùng, ông từ chối để Carlotta tiếp tục giữ vai trò Người Thừa Hành. Thay vào đó, ông bảo cô viết thư mời đại diện từ &lt;te href=850109&gt;the Black Shores&lt;/te&gt; đến Ragunna. Carlotta nhìn ra ngoài cửa sổ. Sau cơn mưa, Ragunna chìm trong màn sương xám xịt. Thành phố như một con thú đang say ngủ, chờ đợi sự xuất hiện của Carnevale để thức tỉnh.
+Bầu trời ngoài kia bắt đầu sáng dần... Cuối cùng, ông từ chối để Carlotta tiếp tục giữ vai trò Người Thừa Hành. Thay vào đó, ông bảo cô viết thư mời đại diện từ &lt;te href=850109&gt;Bờ Biển Đen&lt;/te&gt; đến Ragunna. Carlotta nhìn ra ngoài cửa sổ. Sau cơn mưa, Ragunna chìm trong màn sương xám xịt. Thành phố như một con thú đang say ngủ, chờ đợi sự xuất hiện của Carnevale để thức tỉnh.
 Lúc đó, Carlotta không hề biết rằng chính đêm mưa này, Francesco Montelli đã đưa ra một quyết định sẽ định hình tương lai của gia tộc Montelli. Ông sẽ dùng những biện pháp đặc biệt để trao lại quyền lựa chọn vào tay cô. Và cô, như chính con người ban đầu của mình, sẽ mở đường cho những gì sắp tới.</t>
         </is>
       </c>
@@ -26265,14 +26265,14 @@
 "Cháu làm gì thế hả? Cháy tiệm của ta à!"
 Cô bé giật mình vì tiếng quát, lập tức dập tắt ngọn lửa. Changqing nhìn thấy trang sách cô bé đang giữ chặt dần chuyển sang màu vàng, như thể sắp bắt lửa.
 "Cháu, cháu là...!"
-Cô bé vội Dodgem cuốn sách đi. Khuôn mặt đỏ bừng của cô lộ rõ vẻ hoảng loạn và tội lỗi khi nhìn những trang sách bị cháy sém.
+Cô bé vội ném cuốn sách đi. Khuôn mặt đỏ bừng của cô lộ rõ vẻ hoảng loạn và tội lỗi khi nhìn những trang sách bị cháy sém.
 "Xin lỗi... Ở đây tối quá, cháu chỉ muốn sáng hơn một chút..."
 Nhìn thấy cuốn sách yêu quý của mình bị hư hại, Changqing không khỏi nhớ đến việc doanh thu gần đây sụt giảm. Mặt ông tối sầm lại khi cầm cây chổi bên kệ sách, chuẩn bị đánh cô bé.
 Thế nhưng, cô bé nhanh nhẹn một cách đáng ngạc nhiên so với thân hình mảnh khảnh. Khi Changqing đuổi theo ra khỏi tiệm, tất cả những gì ông thấy chỉ là mái tóc đỏ rực biến mất trong đám đông chợ búa. Ông đứng trước cổng, vừa tức giận vừa bối rối.
 "Đừng bao giờ xuất hiện trước mặt ta nữa!"
 "Có chuyện gì thế?" Ông chủ tạp hóa bên cạnh bước ra với nụ cười hỏi. "Không phải cô bé có thể điều khiển lửa đó sao?"
 "Anh biết cô bé ấy à? Nó suýt thiêu rụi tiệm của tôi!"
-"Này, nó là đứa trẻ ngoan, tôi không đùa đâu. Mấy hôm trước còn giúp tôi chỉ để lấy vài cái bánh bao. Tội nghiệp, nó phải đi một mình từ nhỏ như vậy. Nghe nói quê hương nó bị &lt;te href=850081&gt;TD&lt;/te&gt; tấn công, không ai sống sót. Không biết làm sao nó lại trốn thoát được..."
+"Này, nó là đứa trẻ ngoan, tôi không đùa đâu. Mấy hôm trước còn giúp tôi chỉ để lấy vài cái bánh bao. Tội nghiệp, nó phải đi một mình từ nhỏ như vậy. Nghe nói quê hương nó bị &lt;te href=850081&gt;Bùng phát TD&lt;/te&gt; tấn công, không ai sống sót. Không biết làm sao nó lại trốn thoát được..."
 "Sao anh không nói sớm hơn?"
 "Chà, anh đâu có hỏi! Nhưng giờ chuyện đã thế này... chắc nó sẽ không quay lại nữa đâu."
 Cô bé biến mất vào ngõ hẻm, tiếng trẻ con nô đùa vọng lại từ những bức tường bên cạnh. Changqing nhìn cuốn sách nằm trên mặt đất, lòng tràn ngập cảm xúc khó tả.</t>
@@ -26349,9 +26349,9 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>"Calcharo "Kẻ Tàn Bạo"" từng là một trong những kẻ lưu vong ở Khu Vực Vô Pháp của New Federation. Hắn đã thành thạo đủ mọi thủ đoạn hèn hạ để sinh tồn từ lâu. Ngày nay, hắn còn trở nên tàn nhẫn hơn vì công việc lính đánh thuê: đầu độc, ám sát, mua chuộc, bắt cóc, bom mìn... Hắn sẽ làm bất cứ điều gì cần thiết để hoàn thành nhiệm vụ. Những câu chuyện về kỳ tích bất khả thi của Calcharo lan truyền không ngừng. Người ta kể hắn từng nằm phục kích trong sa mạc bảy ngày không nước, kẻ khác lại nói hắn từng đeo bom khắp người trong một cuộc đàm phán. Thậm chí có tin đồn hắn thuê sát thủ giả vờ ám sát mình để lấy lòng tin.
+          <t>"Calcharo "Kẻ Tàn Bạo"" từng là một trong những kẻ lưu vong ở Khu Vực Vô Pháp của Liên Bang Mới. Hắn đã thành thạo đủ mọi thủ đoạn hèn hạ để sinh tồn từ lâu. Ngày nay, hắn còn trở nên tàn nhẫn hơn vì công việc lính đánh thuê: đầu độc, ám sát, mua chuộc, bắt cóc, bom mìn... Hắn sẽ làm bất cứ điều gì cần thiết để hoàn thành nhiệm vụ. Những câu chuyện về kỳ tích bất khả thi của Calcharo lan truyền không ngừng. Người ta kể hắn từng nằm phục kích trong sa mạc bảy ngày không nước, kẻ khác lại nói hắn từng đeo bom khắp người trong một cuộc đàm phán. Thậm chí có tin đồn hắn thuê sát thủ giả vờ ám sát mình để lấy lòng tin.
 Dù có phần phóng đại, những lời đồn đó không hẳn là vô căn cứ với những ai từng biết Calcharo. Nhưng càng về sau, câu chuyện càng trở nên hoang đường...
-"Hắn một mình chặn đứng cả chiếc xe tải năm 12 tuổi; đến năm 15, Forte của hắn khiến cả New Federation phải khiếp sợ. Năm 18 tuổi, hắn đánh nhau với toàn bộ cảnh sát cả nước mà vẫn bình an vô sự..."
+"Hắn một mình chặn đứng cả chiếc xe tải năm 12 tuổi; đến năm 15, Forte của hắn khiến cả Liên Bang Mới phải khiếp sợ. Năm 18 tuổi, hắn đánh nhau với toàn bộ cảnh sát cả nước mà vẫn bình an vô sự..."
 "Ngực hắn là nơi trú ngụ của những linh hồn chết, trán hắn mang lời nguyền của thần linh. Dưới chân hắn giáng sấm sét, từ mắt hắn bắn ra ngọn lửa. Cơn thịnh nộ của hắn sẽ không nguôi cho đến khi trời đất cháy rụi..."
 "Hắn đã đi qua địa ngục và trở về không biết bao lần... Hắn sẽ luôn đến như tia chớp, như bóng ma, và đoạt lại tất cả những gì thuộc về mình..."
 Những tin đồn mới nhất về Calcharo đã trở thành đề tài bàn tán thường xuyên của các lính đánh thuê khi rảnh rỗi.
@@ -26554,30 +26554,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>"Tôi rất tiếc phải thông báo rằng 'Sparrow' và 'Canary' đã được xác nhận là đã qua đời. Danh tính của họ đã bị lộ và tổ chức tội phạm đã hành động nhanh chóng."
-"Không thể nào! Sao có thể..."
-Cơn giận dữ của chàng trai trẻ khiến anh làm đổ một chiếc chai, làm em bé trong nôi giật mình. Anh vội vàng ôm cô bé lên.
-"Nói đến đó, họ để lại một đứa trẻ cũng là Resonator. Điều này có thể khiến mọi chuyện phức tạp hơn... Có vẻ như từ giờ cô bé sẽ do anh chăm sóc. Nhưng vì hiện tại anh đang bị đình chỉ công tác, anh sẽ có nhiều thời gian cho cô bé đấy."
-"Tôi sẽ chăm sóc cô bé. Không phải việc của anh lo lắng."
-"Người thầy của anh trước đây đang điều tra chuyện gì đó. Anh có biết gì không?"
-"Tôi không biết gì về chuyện đó..."
-Chàng trai trẻ biết câu hỏi thực sự là về kẻ nội gián trong Cục An ninh Public, kẻ có thể đứng sau cuộc gặp đáng ngờ tối nay... Anh không thể nói một lời nào.
-"Các điều tra viên của chúng tôi sẽ đến nhà này vào ngày mai để điều tra thêm. Hãy hợp tác nhé."
-Anh không thể ngăn cản họ, nhất là khi đang bế theo một đứa trẻ.
-"Vậy ngày mai nhé. Tối nay tôi sẽ thu dọn đồ đạc và tìm chỗ mới để chuyển đi. Như vậy có được không?"
-"Tất nhiên, hãy tận dụng cơ hội này để bắt đầu lại từ đầu."
-Chàng trai giả vờ thu dọn đồ đạc trong khi bí mật để ý ánh nhìn khả nghi trong mắt &lt;te href=850087&gt;Patroller&lt;/te&gt;.
-...
-...
-Giữa ngọn lửa đang gầm rú, chàng trai trẻ ôm chặt đứa bé trong vòng tay. Đứa trẻ vẫn bình tĩnh, nhìn chằm chằm khi mọi người chạy qua họ.
-Khi một người lạ đến gần, chàng trai hạ mũ trùm đầu xuống và giấu đứa bé sâu hơn vào trong áo khoác.
-Không nhận ra anh, người lạ đi qua và biến mất vào bóng tối để báo cáo.
-"Xong rồi," người lạ nói.
-Chàng trai mỉm cười, biết rằng đây đều là một phần trong kế hoạch của họ.
-Anh đã tạo ra những con rối của chính mình và đứa bé bằng Forte của mình, đánh lừa kẻ thù nghĩ rằng họ đang say ngủ. Với sự đánh lừa này, họ có thể trốn thoát qua một lối đi bí mật và biến mất khỏi tầm truy đuổi của kẻ thù. Đó là cách duy nhất để đảm bảo an toàn cho họ và bảo vệ những bí mật được giấu trong ngôi nhà cũ của người thầy.
-Từ ngày hôm đó trở đi, anh và cô bé trong vòng tay sẽ không còn được biết đến bằng những cái tên cũ nữa. Họ sẽ có những danh tính mới: khuôn mặt mới, tên mới.
-Lặng lẽ, anh lấy ra một chiếc mặt nạ xấu xí từ trong túi và đeo lên mặt. Sau đó, che mắt đứa trẻ bằng tay, họ lặng lẽ rời khỏi ngọn lửa đang hoành hành và biến mất vào màn đêm mà không ngoảnh lại.
-"Từ giây phút này... ta sẽ được gọi là 'Dollmaker', còn con sẽ mang tên 'Yinlin' - cái tên mà bố mẹ con đã chọn từ lâu cho con."</t>
+          <t>"Ta rất tiếc phải thông báo rằng 'Sparrow' và 'Canary' đã được xác nhận tử nạn. Danh tính của họ đã bị lộ, và tổ chức tội phạm đã hành động ngay lập tức."</t>
         </is>
       </c>
     </row>
@@ -26659,20 +26636,20 @@
         <is>
           <t>Cắn răng chịu đựng cơn đau nhói bên sườn, Yinlin cố gượng dậy, chống tay vào chiếc bàn gần đó.
 Một bóng người hiện ra từ bóng tối, rút những lưỡi dao sắc nhọn của con rối cắm trên người hắn ra rồi vứt bỏ một cách thờ ơ.
-"Ta không hiểu tại sao ngươi lại liều mạng đột nhập tổ chức của ta chỉ để lấy mấy bản ghi chép về hai &lt;te href=850087&gt;Patrollers&lt;/te&gt; đã chết... Nhưng rõ ràng là ta đã thắng," hắn chế nhạo.
+"Ta không hiểu tại sao ngươi lại liều mạng đột nhập tổ chức của ta chỉ để lấy mấy bản ghi chép về hai &lt;te href=850087&gt;Patroller&lt;/te&gt; đã chết... Nhưng rõ ràng là ta đã thắng," hắn chế nhạo.
 Với nỗ lực cuối cùng, Yinlin triệu hồi một roi sét knítting lên đầu ngón tay và phóng về phía hắn, nhưng do cơn đau hành hạ, cô không thể nhắm chính xác và roi sét rơi xuống đất cách đó vài mét.
 "Forte của ta có thể gây rối loạn nhịp tim. Chừng nào ngươi còn là con người, thì không cách nào tránh được đâu."
 Khi &lt;te href=850072&gt;Tacet Mark&lt;/te&gt; trên cánh tay hắn sáng lên lần nữa, Yinlin mất hết sức lực và ngã quỵ xuống đất.
-"Đội của ta chưa có Resonators nào mạnh như ngươi... Nhưng ta lại có gián điệp trong hàng ngũ Patroller. Hừm, ngươi làm cách nào mà...?"
+"Đội của ta chưa có Resonator nào mạnh như ngươi... Nhưng ta lại có gián điệp trong hàng ngũ Patroller. Hừm, ngươi làm cách nào mà...?"
 Khi hắn đang nói, đột nhiên hắn nhận ra điều gì đó và nở một nụ cười nham hiểm.
-"À há, hóa ra ngươi là Agent à? Thật ngu ngốc khi liều mạng vì chuyện vặt vãnh này. Dù ngươi có phát hiện ra bí mật của ta đi chăng nữa, thì cũng chẳng thay đổi được gì đâu."
+"À há, hóa ra ngươi là Đặc Vụ à? Thật ngu ngốc khi liều mạng vì chuyện vặt vãnh này. Dù ngươi có phát hiện ra bí mật của ta đi chăng nữa, thì cũng chẳng thay đổi được gì đâu."
 Khi hơi thở của Yinlin dần yếu đi, hắn biết tim cô đã ngừng đập.
-"Đến lúc kết liễu ngươi rồi. Thật đáng tiếc. Đáng ra ngươi không nên dây vào bọn The Fractsidus..."
+"Đến lúc kết liễu ngươi rồi. Thật đáng tiếc. Đáng ra ngươi không nên dây vào bọn Fractsidus..."
 Nhưng ngay khi lưỡi dao của hắn sắp đâm xuống, một luồng sét mạnh bất ngờ truyền qua, khiến hắn tê liệt tại chỗ.
 "Sao... Sao ngươi có thể..."
 Trước khi ngất đi, hắn kịp nhìn thấy tia sét lóe lên trong lồng ngực Yinlin. Cô đã tự sốc điện để kéo trái tim mình trở lại từ bờ vực tử thần.
 Yinlin điều khiển con rối "Zapstring" của mình bằng những ngón tay khẽ rung, tiến về phía hắn trong khi bản thân cô đã kiệt sức không thể di chuyển. Từ túi hắn, cô lấy ra một tập tài liệu.
-"The Fractsidus... Đã đến lúc nhổ tận gốc bóng tối ẩn náu này rồi."</t>
+"Fractsidus... Đã đến lúc nhổ tận gốc bóng tối ẩn náu này rồi."</t>
         </is>
       </c>
     </row>
@@ -26744,7 +26721,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phòng tập Quyền Thuật Yuanwu từng nổi danh là nơi kế thừa môn phái &lt;te href=850114&gt;Leihuangquan&lt;/te&gt;. Nơi đây từng ghi dấu vô số vinh quang, mỗi đời sư phụ đều vang danh khắp &lt;te href=850093&gt;Huanglong&lt;/te&gt;.
+          <t xml:space="preserve">Phòng tập Quyền Thuật Yuanwu từng nổi danh là nơi kế thừa môn phái &lt;te href=850114&gt;Leihuangquyền&lt;/te&gt;. Nơi đây từng ghi dấu vô số vinh quang, mỗi đời sư phụ đều vang danh khắp &lt;te href=850093&gt;Huanglong&lt;/te&gt;.
 Danh tiếng của Leihuangquyền dựa trên lối đánh hùng hổ, nhưng chính sự mãnh liệt ấy thường phải trả giá đắt. Ba đời sư phụ cuối cùng đều kết thúc trong bi kịch, đặc biệt là người gần nhất – một cái kết thảm thương đến không ngờ. Nghe đồn, trong cơn hăng máu thi đấu, ông ta đã đấm xuyên qua thiết bị tập, vi phạm quy tắc và bị trục xuất. Để vơi đi nỗi đau sự nghiệp, ông lên thuyền du ngoạn, nào ngờ gặp phải cơn bão sét kinh hoàng. Trớ trêu thay, ông lại sở hữu kỹ năng điều khiển sấm sét, và số phận đã trêu ngươi khi để ông chết bởi chính sức mạnh mình từng điều khiển. Có lẽ nghiệp chướng không bao giờ tha thứ cho ai.
 Người môi giới bất động sản vừa dứt lời giới thiệu lịch sử phòng tập, liền dừng lại quan sát phản ứng của người đàn ông trung niên. "Tài sản này không mấy tốt lành đâu. Ông còn muốn mua không?" Người đàn ông chỉ mỉm cười gật đầu, không chút nao núng.
 "Thôi được, tôi đã nói hết rồi," người môi giới thở dài, cảnh báo, "Nếu ông vẫn muốn mua thì cứ mua, nhưng đừng biến nó thành phòng tập võ nữa. Không may lắm đấy."
@@ -26846,18 +26823,18 @@
 Trong những thời khắc như vậy, điều người dân cần nhất là một nguồn hy vọng đáng tin cậy, bất kể ai mang lại.
 Trong một sự kiện tái thiết, vị nữ quan trẻ đã thực hiện một "phép màu" mang tên "Sentinel Ban Phước". Ngôi làng hẻo lánh này đã bị thời tiết bất thường hoành hành nhiều năm. Dù Tacet Discord đã ngừng hoạt động, dân làng vẫn phải chịu đựng cái lạnh khắc nghiệt và bầu không khí u ám.
 Jinhsi yêu cầu dân làng nói lên mong ước của mình. Lúc đầu, im lặng bao trùm cho đến khi một tiếng hắt hơi phá vỡ bầu không khí. Rồi một giọng nói rụt rè cất lên: "Lạnh quá… Con ước gì ở đây ấm áp hơn một chút."
-Đứng giữa đám đông, Jinhsi cầm một chiếc Loong Scale, nhắm mắt lại và gật đầu: "Ta sẽ chuyển lời nguyện ước của các ngươi đến The Sentinel."
+Đứng giữa đám đông, Jinhsi cầm một chiếc Vảy Rồng, nhắm mắt lại và gật đầu: "Ta sẽ chuyển lời nguyện ước của các ngươi đến Sentinel."
 Ngay sau khi lời cô vừa dứt, sừng rồng mọc lên từ đầu cô, và một luồng ánh sáng giống Sentinel xuyên thủng đám mây đen cùng lớp tuyết dưới đất—chỉ trong chớp mắt, băng tan, đất đai lại hồi sinh.
 Chứng kiến cảnh tượng này, đám đông reo lên: "Sentinel… Sentinel đã hiện thân!" Mọi người ngước nhìn luồng sáng hình rồng với ánh mắt đầy kinh ngạc, niềm hy vọng trong họ lại bừng cháy.
-Tin tức về khả năng ban phước của vị nữ quan trẻ nhanh chóng lan truyền khắp Jinzhou. "Wishing" trở thành một phong tục phổ biến, người dân gửi gắm mong muốn của mình cho cô tại Tòa Thị Chính. Cô xem xét từng lời một và đưa ra những chiến lược hiệu quả để thực hiện.
+Tin tức về khả năng ban phước của vị nữ quan trẻ nhanh chóng lan truyền khắp Jinzhou. "Ước nguyện" trở thành một phong tục phổ biến, người dân gửi gắm mong muốn của mình cho cô tại Tòa Thị Chính. Cô xem xét từng lời một và đưa ra những chiến lược hiệu quả để thực hiện.
 "Thưa Magistrate, tôi lo lắng về việc Tacet Discord xâm nhập thành phố."—Taoqi, giám đốc Bộ Phòng Thủ, được giao nhiệm vụ củng cố tường thành phòng thủ.
 "Thưa Magistrate, con cầu nguyện cho cha con được trở về bình an và chiến tranh kết thúc."—Jinhsi ưu tiên nghiên cứu vũ khí Tacetite và kỹ thuật vật liệu, thúc đẩy chế tạo vũ khí mới chống lại Discord và nâng cấp phòng thủ nhanh hơn.
-"Thưa Magistrate, Exile đã xuất hiện trong thành phố. Con sợ lắm."—Jinhsi mở rộng &lt;te href=850089&gt;Patrol Station&lt;/te&gt;, tăng cường &lt;te href=850087&gt;Tuần Tra&lt;/te&gt; trong thành và điều thêm &lt;te href=850086&gt;Midnight Rangers&lt;/te&gt; canh gác bên ngoài.
+"Thưa Magistrate, Exile đã xuất hiện trong thành phố. Con sợ lắm."—Jinhsi mở rộng &lt;te href=850089&gt;Trạm Tuần Tra&lt;/te&gt;, tăng cường &lt;te href=850087&gt;Tuần Tra&lt;/te&gt; trong thành và điều thêm &lt;te href=850086&gt;Midnight Rangers&lt;/te&gt; canh gác bên ngoài.
 Trong vòng ba năm, tường thành phòng thủ được đổi mới, vũ khí mới ra đời, Tacet Discord bị đẩy lùi. Jinzhou cuối cùng cũng đón nhận hòa bình và thịnh vượng.
 Thời gian trôi qua, người dân dần nhận ra rằng "Sentinel Ban Phước" chỉ là lời nói dối vô hại của vị nữ quan trẻ.
 Nhưng họ cũng phát hiện ra sự tận tụy thực sự của cô trong việc giải quyết những vấn đề và lo lắng của họ, luôn có mặt kịp thời như một tia chớp.
 Đèn ở Tòa Thị Chính không bao giờ tắt, ngay cả vào những ngày lễ. Jinhsi làm việc không ngừng nghỉ đến tận khuya, lên kế hoạch khả thi để thực hiện ước nguyện của người dân.
-Và cuối cùng, họ hiểu rằng cô sở hữu một sức mạnh phi thường—không cần Loong Scale, cô vẫn có thể triệu hồi một luồng ánh sáng chói lòa xuyên thủng băng giá và đảo ngược thời gian.
+Và cuối cùng, họ hiểu rằng cô sở hữu một sức mạnh phi thường—không cần Vảy Rồng, cô vẫn có thể triệu hồi một luồng ánh sáng chói lòa xuyên thủng băng giá và đảo ngược thời gian.
 ...
 Ngày nay, ước nguyện đã trở thành thói quen của người dân Jinzhou, một thỏa thuận ngầm giữa họ và vị nữ quan trẻ của mình.
 "Thưa Magistrate, con mong cô có thể dành chút thời gian nghỉ ngơi và đến xem vở kịch mới của chúng con." Đây là lời ước cuối cùng trong năm.
@@ -27040,7 +27017,7 @@
 Aalto chỉ gật đầu im lặng, đồng cảm. Anh đưa Encore vào tòa nhà mà không gặp bất kỳ trở ngại nào.
 "Sao mọi người lúc nào cũng tin mấy câu chuyện của anh thế, Aalto? Nghe giả tạo quá đi!"
 "Anh thấy đấy, những câu chuyện của anh được thiết kế riêng cho từng tình huống."
-"What's that supposed to mean?"
+"Ý anh là sao?"
 "Anh ấy là một người cha đơn thân. Anh ấy sẽ thấy câu chuyện gia đình đầy xúc động của em rất dễ đồng cảm. Còn gì nữa, sao em lại bảo câu chuyện của anh giả tạo?"
 Cloudy và Cosmos nhảy lên vai Encore và đồng thanh kêu "Baa, baa baa."
 "Nhìn kìa! Lũ Woolies cũng nghĩ câu chuyện của anh nghe giả tạo đấy."
@@ -27120,17 +27097,17 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Không lâu sau khi Jiyan được bổ nhiệm làm tướng quân của Midnight Rangers, một đợt bùng phát Discord bất ngờ xảy ra. Chính trong trận chiến này, ông đã nghi ngờ về sự hồi sinh của Threnodian.
-Khi những người lính mệt mỏi đang hồi sức sau trận chiến ác liệt ở tiền tuyến, họ bỗng chứng kiến một cảnh tượng đáng sợ: những con quạ bóng tối lượn vòng trên bầu trời và hàng đàn Discord ào ạt tấn công vị trí của họ tại Norfall Barrens và đèo Desorock Highland.
+          <t>Không lâu sau khi Jiyan được bổ nhiệm làm tướng quân của Midnight Rangers, một đợt bùng phát Tacet Discord bất ngờ xảy ra. Chính trong trận chiến này, ông đã nghi ngờ về sự hồi sinh của Threnodian.
+Khi những người lính mệt mỏi đang hồi sức sau trận chiến ác liệt ở tiền tuyến, họ bỗng chứng kiến một cảnh tượng đáng sợ: những con quạ bóng tối lượn vòng trên bầu trời và hàng đàn Tacet Discord ào ạt tấn công vị trí của họ tại Norfall Barrens và đèo Desorock Highland.
 Đội quân ít ỏi biết rằng nếu không giữ vững cứ điểm này, toàn bộ Huanglong sẽ lâm nguy.
 Ngay cả những cựu binh dày dạn cũng chưa từng đối mặt với tình thế cấp bách đến vậy. Giữa hỗn loạn, duy chỉ có Jiyan vẫn giữ được bình tĩnh.
-"Tất cả các ngươi. Prepare chiến đấu."
+"Tất cả các ngươi. Chuẩn bị chiến đấu."
 "Điên rồi! Nếu thua ở đây, tất cả sẽ chấm dứt. Ta vẫn còn đường rút lui để bảo vệ thành phố!"
 "Lựa chọn đi: đứng lên với lòng dũng cảm, nắm lấy cơ hội. Hay bỏ chạy và đón nhận thất bại. Suốt mấy trăm năm qua, Midnight Rangers chưa bao giờ rút lui khỏi con đèo này. Hay các ngươi muốn bị ghi danh vào lịch sử như những kẻ hèn nhát?"
 Các cựu binh rời đi, lòng tràn ngập từ thất vọng đến phẫn nộ.
-Quyết tâm của Jiyan không hề lung lay. Ông cẩn thận phân tích hình ảnh thời gian thực từ các thiết bị giám sát và phát hiện mối liên hệ giữa Discord và những con quạ bóng tối trên cao. Nhanh chóng triệu tập các chỉ huy khác trong quân đội, Jiyan lên kế hoạch và dẫn dắt đội quân phối hợp đối đầu trực diện với kẻ thù. Họ sử dụng bộ mô phỏng âm thanh đặt trong thung lũng hẹp để phát ra tần số của quạ bóng tối. Đúng như dự đoán, Discord bị thu hút bởi âm thanh đó, tạo điều kiện dễ dàng để bắt giữ chúng.
-Trong khi đó, Midnight Rangers đóng quân tại Norfall Barrens được lệnh phối hợp với đồng đội ở Desorock Highland, thực hiện đòn tấn công gọng kìm vào Discord. Giữa cơn bão cát, Jiyan dũng mãnh tiêu diệt hàng loạt kẻ thù, mở đường cho đồng đội với sức mạnh vô song.
-Tacet Mark trên gáy Jiyan chớp nháy, dấu hiệu của việc sử dụng Forte quá mức, nhưng ông vẫn không ngừng chiến đấu. Thanh Qingloong của ông bay cao trên bầu trời như một lá cờ kiêu hãnh của quyết tâm, không bao giờ gục ngã.</t>
+Quyết tâm của Jiyan không hề lung lay. Ông cẩn thận phân tích hình ảnh thời gian thực từ các thiết bị giám sát và phát hiện mối liên hệ giữa Tacet Discord và những con quạ bóng tối trên cao. Nhanh chóng triệu tập các chỉ huy khác trong quân đội, Jiyan lên kế hoạch và dẫn dắt đội quân phối hợp đối đầu trực diện với kẻ thù. Họ sử dụng bộ mô phỏng âm thanh đặt trong thung lũng hẹp để phát ra tần số của quạ bóng tối. Đúng như dự đoán, Tacet Discord bị thu hút bởi âm thanh đó, tạo điều kiện dễ dàng để bắt giữ chúng.
+Trong khi đó, Midnight Rangers đóng quân tại Norfall Barrens được lệnh phối hợp với đồng đội ở Desorock Highland, thực hiện đòn tấn công gọng kìm vào Tacet Discord. Giữa cơn bão cát, Jiyan dũng mãnh tiêu diệt hàng loạt kẻ thù, mở đường cho đồng đội với sức mạnh vô song.
+Dấu Tacet trên gáy Jiyan chớp nháy, dấu hiệu của việc sử dụng Forte quá mức, nhưng ông vẫn không ngừng chiến đấu. Thanh Qingloong của ông bay cao trên bầu trời như một lá cờ kiêu hãnh của quyết tâm, không bao giờ gục ngã.</t>
         </is>
       </c>
     </row>
@@ -27205,13 +27182,13 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Jiyan là vị tướng trẻ nhất trong lịch sử &lt;te href=850086&gt;Midnight Rangers&lt;/te&gt;. Anh là Qingloong mà mọi người ngưỡng mộ, chiến binh bất bại không kẻ thù nào có thể chống lại. Thế nhưng, đến một lúc nào đó, Jiyan bắt đầu bị ám ảnh bởi một cơn ác mộng lặp đi lặp lại.
-Trong giấc mơ ấy, thành phố &lt;te href=850091&gt;Jinzhou&lt;/te&gt; chìm trong biển lửa, bị nuốt chửng bởi &lt;te href=850081&gt;Tacet Discords&lt;/te&gt;. Lũ quái vật hoành hành, hút lấy tần số của những người đã chết. Âm thanh hỗn loạn vang vọng khắp thành phố, tạo nên bản giao hưởng của sự hủy diệt.
-Trên chiến trường ngập lửa, một bóng người đơn độc chiến đấu không ngừng với ngọn giáo trong tay. Mỗi nhát chém xé toang không khí. One, two, three... Hàng trăm ngàn Tacet Discord ngã xuống dưới những đòn đánh dữ dội và không ngừng nghỉ của anh.
+          <t>Jiyan là vị tướng trẻ nhất trong lịch sử &lt;te href=850086&gt;Midnight Rangers&lt;/te&gt;. Anh là Thanh Long mà mọi người ngưỡng mộ, chiến binh bất bại không kẻ thù nào có thể chống lại. Thế nhưng, đến một lúc nào đó, Jiyan bắt đầu bị ám ảnh bởi một cơn ác mộng lặp đi lặp lại.
+Trong giấc mơ ấy, thành phố &lt;te href=850091&gt;Jinzhou&lt;/te&gt; chìm trong biển lửa, bị nuốt chửng bởi &lt;te href=850081&gt;Tacet Discord&lt;/te&gt;. Lũ quái vật hoành hành, hút lấy tần số của những người đã chết. Âm thanh hỗn loạn vang vọng khắp thành phố, tạo nên bản giao hưởng của sự hủy diệt.
+Trên chiến trường ngập lửa, một bóng người đơn độc chiến đấu không ngừng với ngọn giáo trong tay. Mỗi nhát chém xé toang không khí. Một, hai, ba... Hàng trăm ngàn Tacet Discord ngã xuống dưới những đòn đánh dữ dội và không ngừng nghỉ của anh.
 Dù đã cố gắng hết sức, người đàn ông ấy vẫn không thể dập tắt được bầy Tacet Discord đang tàn phá mảnh đất này. Ngày qua ngày, năm qua năm, anh chiến đấu trong vô vọng cho đến khi trở thành người sống sót duy nhất trên chiến trường hoang tàn. Tacet Discord biến thành những đồng đội đã ngã xuống, bao vây và tiến lại gần anh.
-"Thằng nhóc ngốc nghếch này! Sao chúng ta có thể tin tưởng giao mạng cho nó được?"
-"Ngươi nói sẽ bảo vệ chúng ta... nhưng tại sao?"
-"Jiyan, rốt cuộc ngươi chiến đấu vì cái gì?"
+"Thằng nhóc ngốc nghếch này! Sao chúng tao có thể tin tưởng giao mạng cho nó được?"
+"Mày nói sẽ bảo vệ chúng tao... nhưng tại sao?"
+"Jiyan, rốt cuộc mày chiến đấu vì cái gì?"
 Dù nổi tiếng là người điềm tĩnh và quyết đoán, ít ai biết rằng đôi khi anh bị giật mình tỉnh giấc bởi những cơn ác mộng, ám ảnh bởi tiếng nói của những người đã khuất.
 Là một vị tướng, nhiệm vụ của Jiyan không chỉ là bảo vệ biên giới mà còn là toàn bộ quốc gia. Mỗi quyết định và kế hoạch của anh đều mang theo trách nhiệm và hậu quả nặng nề.
 Đó là lý do anh luôn trầm ngâm, suy nghĩ và lên kế hoạch trước. Một ngày nào đó, có lẽ anh sẽ quay lại và trả lời những câu hỏi từ những người đã khuất.
@@ -27293,7 +27270,7 @@
 Một người lính khác, trước đó lơ là trong huấn luyện, vài ngày sau mới biết Phòng Hành chính của Midnight Rangers đã chi trả toàn bộ chi phí phẫu thuật cho mẹ anh.
 Khi bộ phận hậu cần thiếu hụt ngân sách, họ nhận được thông báo tăng kinh phí cho quý tới trước cả khi đơn xin ngân sách được chính thức gửi đi.
 Dù vấn đề lớn hay nhỏ, cũ hay mới, luôn có ai đó xuất hiện kịp thời để giải quyết khi cần thiết nhất. Như cơn mưa nhẹ tưới mát đất khô cằn, người ấy âm thầm sắp đặt mọi sự trợ giúp, đảm bảo không nơi nào bị bỏ quên.
-"Trưởng nhóm Đội 3 rõ ràng gặp khó khăn khi dùng chân trái trong buổi diễn tập. Tôi đã xem hồ sơ phẫu thuật của anh ta, có vẻ do tiếp xúc lâu với đầm lầy trong một nhiệm vụ trước. Chuyển đơn thuốc này cho y tế. Họ sẽ biết phải làm gì."
+"Đội trưởng Đội 3 rõ ràng gặp khó khăn khi dùng chân trái trong buổi diễn tập. Tôi đã xem hồ sơ phẫu thuật của anh ta, có vẻ do tiếp xúc lâu với đầm lầy trong một nhiệm vụ trước. Chuyển đơn thuốc này cho y tế. Họ sẽ biết phải làm gì."
 "Chuyển một khoản tiền vào tài khoản này dưới danh nghĩa Phòng Hành chính. Trừ thẳng vào tài khoản của tôi."
 "Tôi nhớ năm nay số lượng tân binh tăng 20%. Xác nhận lại với bộ phận Hậu cần. Nếu đúng, điều chỉnh ngân sách quý tới cho phù hợp."
 Đây là Jiyan, người chỉ tàn nhẫn với kẻ thù, còn với đồng đội, ông luôn dành cho họ sự dịu dàng.</t>
@@ -27384,7 +27361,7 @@
         <is>
           <t>"Squeakie, chị chóng mặt quá... 
 Lumi lẩm bẩm, dựa vào thành giường khi con tàu dưới chân rung lắc dữ dội. Sóng biển đập vào thân tàu ầm ầm, cơn chấn động mạnh đến mức như muốn kéo cả người xuống vực sâu. Cô ôm chặt chú chuột bông, nhắm mắt lại, chờ đợi chuyến đi khủng khiếp này kết thúc.
-Vài ngày sau, cảng cuối cùng cũng hiện ra trước mắt, nơi biển cả giao hòa với bầu trời. Tiếng mòng biển kêu xa xa, Lumi thở phào nhẹ nhõm khi đặt chân lên mặt đất vững chắc. "Ơn trời," cô thì thầm. Hai người đồng hành, Tangtang và Fulei, vẫn lảo đảo theo sau, mặt ngươi tái nhợt vì say sóng.
+Vài ngày sau, cảng cuối cùng cũng hiện ra trước mắt, nơi biển cả giao hòa với bầu trời. Tiếng mòng biển kêu xa xa, Lumi thở phào nhẹ nhõm khi đặt chân lên mặt đất vững chắc. "Ơn trời," cô thì thầm. Hai người đồng hành, Tangtang và Fulei, vẫn lảo đảo theo sau, mặt mày tái nhợt vì say sóng.
 "Hai đứa ổn không?" Lumi xoa xoa mái tóc xoăn, dẫn họ đến chiếc ghế gần đó để nghỉ ngơi.
 "Lumi, lần đầu chị đến &lt;te href=850096&gt;Rinascita&lt;/te&gt; cũng khủng khiếp như thế này à?" Tangtang hỏi, đầu vẫn gục gặc.
 Lumi cười khẩy. "Ừ đúng rồi! Vì thế chị mới bảo tụi em phải giữ sức khỏe chứ. Có những nơi còn khó đi hơn thế này nhiều."
@@ -27403,7 +27380,7 @@
 Lumi mỉm cười. "Cuộc sống luôn có những người đến rồi đi," cô tiếp tục. "Có người xuống tàu, có người lên tàu. Nhưng miễn là còn những người sẵn sàng gánh vác ngọn đuốc, khẩu hiệu 'Chúng tôi hứa, chúng tôi giao' của chúng ta sẽ mãi vững vàng."
 Lumi đứng dậy vươn vai. Squeakie đậu trên vai, dụi dụi má cô. "Nghỉ thêm mười phút nữa rồi lên đường nhé. À, hai đứa muốn ăn kem ba lớp nổi tiếng của Ragunna không? Chị bao!"
 "Có!"
-"Please đi chị!""</t>
+"Làm ơn đi chị!""</t>
         </is>
       </c>
     </row>
@@ -27484,10 +27461,10 @@
         <is>
           <t>&lt;i&gt;Sau nhịp trống, ta gọi trái tim nhảy múa trong bóng tối là vầng trăng. Vầng trăng ấy phần lớn được tạo nên bởi ngươi.&lt;/i&gt;
 Có những sinh mệnh sinh ra từ ngẫu nhiên. Có những sinh mệnh được tạo ra với mục đích.
-Khi thế giới dần tiến đến hồi kết băng giá, những kẻ được định sẵn để đối mặt với khoảnh khắc cuối cùng đã đặt hy vọng vào một cá nhân nhất định. Họ cầu chúc cho {Male=hắn;Female=nàng}, mong {Male=hắn;Female=nàng} sẽ dẫn dắt họ đến một ngày mai tươi sáng hơn. Nhưng cuộc hành trình cô độc này đòi hỏi một chiếc bình vĩnh cửu để hoàn thành những Dư Âm, và tất cả những gì họ có thể dâng tặng chỉ là một công cụ bền bỉ. Vậy là Người Giữ Bờ ra đời—một tạo vật có chủ đích, một kén tinh thể xanh nhạt chứa &lt;te href=850076&gt;Remnant Energy&lt;/te&gt; thu thập từ Mỏ Neo.
+Khi thế giới dần tiến đến hồi kết băng giá, những kẻ được định sẵn để đối mặt với khoảnh khắc cuối cùng đã đặt hy vọng vào một cá nhân nhất định. Họ cầu chúc cho {Male=him;Female=her}, mong {Male=he;Female=she} sẽ dẫn dắt họ đến một ngày mai tươi sáng hơn. Nhưng cuộc hành trình cô độc này đòi hỏi một chiếc bình vĩnh cửu để hoàn thành những Dư Âm, và tất cả những gì họ có thể dâng tặng chỉ là một công cụ bền bỉ. Vậy là Người Giữ Bờ ra đời—một tạo vật có chủ đích, một kén tinh thể xanh nhạt chứa &lt;te href=850076&gt;Năng Lượng Tàn Dư&lt;/te&gt; thu thập từ Mỏ Neo.
 Người Giữ Bờ đã biết mình phải làm gì từ rất lâu trước khi hiểu cách thực hiện. Nhưng một công cụ cần người dẫn dắt. Nàng lang thang vô định trong hư không cho đến khi, khi biển cả dâng trào đến bờ vực, nàng cảm nhận được một nhịp tim đang tiến gần trong làn gió biển mặn chát.
-Trong đêm tĩnh lặng, &lt;te href=850111&gt;Modulator&lt;/te&gt; Thiên Văn quét qua mặt đất khi tiếng gầm của &lt;te href=850075&gt;Lament&lt;/te&gt; dần tan vào khoảng không, chỉ còn lại nhịp tim đều đặn của {Male=hắn;Female=nàng}.
-"Có lẽ mặt đất dưới lòng đất cũng cần một bầu trời rực rỡ như bầu trời trên cao..." Bộ Điều Tần lẩm bẩm, lên kế hoạch cho tương lai. Khi {Male=hắn;Female=nàng} đưa tay kích hoạt hệ thống &lt;te href=850110&gt;Tethys&lt;/te&gt;, một sức hút bí ẩn từ viên tinh thể xanh kia đã lôi cuốn {Male=hắn;Female=nàng} lại gần. Sự giao thoa tần số của họ đã làm vỡ tan tinh thể, giải phóng một luồng năng lượng bùng nổ như tinh vân hay cánh bướm vừa thoát xác.
+Trong đêm tĩnh lặng, &lt;te href=850111&gt;Bộ Điều Tần&lt;/te&gt; Thiên Văn quét qua mặt đất khi tiếng gầm của &lt;te href=850075&gt;Lời Than Thở&lt;/te&gt; dần tan vào khoảng không, chỉ còn lại nhịp tim đều đặn của {Male=his;Female=her}.
+"Có lẽ mặt đất dưới lòng đất cũng cần một bầu trời rực rỡ như bầu trời trên cao..." Bộ Điều Tần lẩm bẩm, lên kế hoạch cho tương lai. Khi {Male=he;Female=she} đưa tay kích hoạt hệ thống &lt;te href=850110&gt;Tethys&lt;/te&gt;, một sức hút bí ẩn từ viên tinh thể xanh kia đã lôi cuốn {Male=him;Female=her} lại gần. Sự giao thoa tần số của họ đã làm vỡ tan tinh thể, giải phóng một luồng năng lượng bùng nổ như tinh vân hay cánh bướm vừa thoát xác.
 Năng lượng xoáy cuộn rồi kết tụ lại, hình thành nên một thiếu nữ, người đã chào đón kẻ đã đánh thức mình.
 "Ta là Người Giữ Bờ, một công cụ được tạo ra cho ngươi."
 "Ta sẽ đáp ứng nhu cầu của ngươi và thực hiện mệnh lệnh của ngươi. Ta sẽ hỗ trợ ngươi và Tethys phân tích nguồn gốc của Lời Than Thở."
@@ -27574,19 +27551,19 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Trích từ ấn bản đặc biệt của Pioneer Express: &lt;i&gt;Guardian Bóng Đêm: Hiện Thân Của Công Lý Hay Một Tên Tội Phạm Xảo Quyệt?&lt;/i&gt;
+          <t>Trích từ ấn bản đặc biệt của Pioneer Express: &lt;i&gt;Người Bảo Vệ Bóng Đêm: Hiện Thân Của Công Lý Hay Một Tên Tội Phạm Xảo Quyệt?&lt;/i&gt;
 "Ngay khi tôi sắp hét lên, họ đã sà xuống ngay trên đầu tôi! Hắn... Không, không, phải là cô ấy. Ừ, tôi nghĩ là phụ nữ. Cô ấy di chuyển nhanh đến mức, trong bóng tối của màn đêm, tôi chẳng nhìn rõ gì cả. Nhưng tôi thề, có thứ gì đó trên đầu cô ấy, giống như những chiếc kẹp tóc kỳ lạ. Hay có khi chỉ là tóc bay trong gió? Tôi không dám chắc..."
 —Sabrina (Nữ, 36 tuổi), một trong những nhân chứng đã tận mắt chứng kiến.
-"Cuối cùng, các huynh đệ của &lt;te href=800005&gt;Chamber of Discipline&lt;/te&gt; cũng đi đến thống nhất, tuyên bố tên tội phạm kia là một người chính nghĩa. Tôi đã kịch liệt phản đối phán quyết đó lúc ấy, và giờ vẫn vậy! Tên tội phạm này đã gây ra hàng chục vụ tấn công ở &lt;te href=850097&gt;Ragunna&lt;/te&gt;! Đúng, đúng, tôi biết những kẻ bị cô ta tấn công đều là tội phạm, nhưng chúng đáng ra phải bị Phòng Discipline bắt giữ dưới danh nghĩa của &lt;te href=850105&gt;Imperator&lt;/te&gt; và xét xử dưới ánh mắt trang nghiêm của &lt;te href=850083&gt;Sentinel&lt;/te&gt;! Chứ không phải bị một tên lưu manh ngoài đường xử lý theo kiểu công lý đường phố! Đây rõ ràng là thách thức quyền uy của Sentinel! Ở Ragunna, chỉ có Sentinel mới có quyền phán xét kẻ có tội!"
-—Một &lt;te href=850100&gt;Acolyte&lt;/te&gt; giấu tên của Phòng Discipline
+"Cuối cùng, các huynh đệ của &lt;te href=800005&gt;Phòng Kỷ Luật&lt;/te&gt; cũng đi đến thống nhất, tuyên bố tên tội phạm kia là một người chính nghĩa. Tôi đã kịch liệt phản đối phán quyết đó lúc ấy, và giờ vẫn vậy! Tên tội phạm này đã gây ra hàng chục vụ tấn công ở &lt;te href=850097&gt;Ragunna&lt;/te&gt;! Đúng, đúng, tôi biết những kẻ bị cô ta tấn công đều là tội phạm, nhưng chúng đáng ra phải bị Phòng Kỷ Luật bắt giữ dưới danh nghĩa của &lt;te href=850105&gt;Imperator&lt;/te&gt; và xét xử dưới ánh mắt trang nghiêm của &lt;te href=850083&gt;Sentinel&lt;/te&gt;! Chứ không phải bị một tên lưu manh ngoài đường xử lý theo kiểu công lý đường phố! Đây rõ ràng là thách thức quyền uy của Sentinel! Ở Ragunna, chỉ có Sentinel mới có quyền phán xét kẻ có tội!"
+—Một &lt;te href=850100&gt;Tín Đồ&lt;/te&gt; giấu tên của Phòng Kỷ Luật
 "Đúng, mấy người hàng xóm của tôi có thấy cô ta. Gần đây, phương pháp của cô ấy ngày càng cực đoan hơn. Họ còn gọi cô ấy là 'Kẻ Đồ Tể Tội Phạm'... Cô ta không giết người à? Tôi không tin đâu. Cô ấy đối phó với những kẻ xấu nhất mà. Tôi không nghĩ ai có thể kiềm chế khi mạng sống của mình đang bị đe dọa. Trừ khi cô ấy mạnh hơn bọn tội phạm rất nhiều, nhưng liệu có khả thi không?"
 —El Lawson (Nam, 42 tuổi), đến từ Thị trấn Egla, bình luận về sự can thiệp của nhân vật bí ẩn này trong vụ tấn công Plushie &lt;te href=850082&gt;Echoes&lt;/te&gt; bởi "Kẻ Giết Plushie". Vì cư dân Egla tuyệt đối không ra ngoài sau khi trời tối, nên không ai nhìn thấy mặt cô ta.
 "Tôi đã theo dõi kẻ báo thù được Sentinel phái đến này. Tại sao tôi lại tin cô ấy có liên hệ với Sentinel? Các người chưa nghe về Ngọn Lửa Trừng Phạt rực cháy xung quanh cô ấy sao? Những ngọn lửa thiêng liêng ấy hẳn phải là món quà của Sentinel. Càng đối mặt với cái ác lớn, ánh sáng càng bùng cháy dữ dội. Một số người gọi cô ấy là ác quỷ? Thật nực cười... Ác quỷ nào lại chiến đấu vì công lý chứ?"
-—Rhea (Nữ, 33 tuổi), Acolyte của Phòng Discipline. Cô từng tham gia điều tra về nhân vật bí ẩn này vài năm trước.
-"Tối hôm đó tôi làm việc muộn. Khi đi ngang qua cổng Phòng Discipline, tôi thấy Talos từ &lt;te href=850136&gt;Black Alley&lt;/te&gt; cùng băng đảng của hắn bị trói gô, tất cả đều bất tỉnh. Chà, có thể chỉ là ảo giác của tôi thôi, nhưng trong ánh sáng mờ nhạt của bình minh, tôi nghĩ mình thấy ai đó đang ngồi xổm trên mái nhà đối diện Phòng Discipline. Cô ấy biến mất trong nháy mắt. Tôi nhớ cô ấy đầy vết thương, như vừa trải qua một trận địa ngục. Gì cơ? Ý các người là cô ấy một mình hạ gục Talos và băng đảng hắn à?!"
+—Rhea (Nữ, 33 tuổi), Tín Đồ của Phòng Kỷ Luật. Cô từng tham gia điều tra về nhân vật bí ẩn này vài năm trước.
+"Tối hôm đó tôi làm việc muộn. Khi đi ngang qua cổng Phòng Kỷ Luật, tôi thấy Talos từ &lt;te href=850136&gt;Ngõ Đen&lt;/te&gt; cùng băng đảng của hắn bị trói gô, tất cả đều bất tỉnh. Chà, có thể chỉ là ảo giác của tôi thôi, nhưng trong ánh sáng mờ nhạt của bình minh, tôi nghĩ mình thấy ai đó đang ngồi xổm trên mái nhà đối diện Phòng Kỷ Luật. Cô ấy biến mất trong nháy mắt. Tôi nhớ cô ấy đầy vết thương, như vừa trải qua một trận địa ngục. Gì? Ý các người là cô ấy một mình hạ gục Talos và băng đảng hắn à?!"
 —Bản ghi âm lưu trữ từ nhiều năm trước. Người nói vẫn chưa rõ danh tính.
-Hầu hết các vụ việc này đều xảy ra từ nhiều năm trước, và những lời khai của nhân chứng thu thập được cho đến nay thường mâu thuẫn và thiếu chi tiết. Tuy nhiên, có một điều rõ ràng: &lt;te href=850137&gt;the second Dark Tide&lt;/te&gt; và sự kiện &lt;te href=850102&gt;Carnevale&lt;/te&gt; cách đây một thập kỷ đã gây ra tổn thất nặng nề cho Ragunna. Trong hỗn loạn sau đó, một nhân vật bí ẩn đã xuất hiện, trừng phạt cái ác dưới màn đêm. Trong những ngày đen tối ấy, nhiều người mất niềm tin đã lập băng đảng, hoành hành tội ác. Mãi cho đến khi người phụ nữ bí ẩn này lần lượt săn lùng và giao chúng cho nhà tù, trật tự mới được khôi phục ở Ragunna.
-Ít người trong thành phố muốn nhắc lại những năm tháng đau thương đó. Like truyền thống của Carnevale, người dân Ragunna tin rằng Imperator muốn họ đón nhận niềm vui thay vì đắm chìm trong vết thương quá khứ. Vì vậy, những ghi chép về nhân vật bí ẩn này—hay còn gọi là "Kẻ Đi Bộ Night Rực Lửa"—đã phai mờ thành truyền thuyết xa xưa. Tuy nhiên, gần đây trong dịp Carnevale, lại có lời đồn đoán rằng ai đó đã nhìn thấy một bóng dáng giống như huyền thoại năm xưa, lang thang trên phố.
+Hầu hết các vụ việc này đều xảy ra từ nhiều năm trước, và những lời khai của nhân chứng thu thập được cho đến nay thường mâu thuẫn và thiếu chi tiết. Tuy nhiên, có một điều rõ ràng: &lt;te href=850137&gt;Làn Sóng Bóng Tối thứ hai&lt;/te&gt; và sự kiện &lt;te href=850102&gt;Carnevale&lt;/te&gt; cách đây một thập kỷ đã gây ra tổn thất nặng nề cho Ragunna. Trong hỗn loạn sau đó, một nhân vật bí ẩn đã xuất hiện, trừng phạt cái ác dưới màn đêm. Trong những ngày đen tối ấy, nhiều người mất niềm tin đã lập băng đảng, hoành hành tội ác. Mãi cho đến khi người phụ nữ bí ẩn này lần lượt săn lùng và giao chúng cho nhà tù, trật tự mới được khôi phục ở Ragunna.
+Ít người trong thành phố muốn nhắc lại những năm tháng đau thương đó. Giống như truyền thống của Carnevale, người dân Ragunna tin rằng Imperator muốn họ đón nhận niềm vui thay vì đắm chìm trong vết thương quá khứ. Vì vậy, những ghi chép về nhân vật bí ẩn này—hay còn gọi là "Kẻ Đi Bộ Đêm Rực Lửa"—đã phai mờ thành truyền thuyết xa xưa. Tuy nhiên, gần đây trong dịp Carnevale, lại có lời đồn đoán rằng ai đó đã nhìn thấy một bóng dáng giống như huyền thoại năm xưa, lang thang trên phố.
 Với Ragunna, đây có phải là điềm báo của một cuộc khủng hoảng mới? Hay chỉ là kẻ bắt chước một anh hùng quá khứ? Chỉ có thời gian mới trả lời được.</t>
         </is>
       </c>
@@ -27678,20 +27655,20 @@
           <t>...Vẫn còn đủ thời gian.
 Zani phóng vội qua những con hẻm tối tăm, vết thương nhức nhối ở vai là lời nhắc nhở rõ ràng về lần thoát chết trong gang tấc. Tên thô lỗ kia, cổ tay hắn dày gần bằng cổ cô, suýt nữa đã hạ gục cô. Cô định hạ hắn bất tỉnh trước khi hắn kịp phản ứng, nhưng hắn nhanh hơn cô tưởng. May mà phản xạ của cô còn nhanh hơn hắn. Nếu không, con dao kia đã không chỉ để lại vết rách sâu ở vai mà còn đâm thẳng vào tim cô.
 Đây không phải là vết thương đầu tiên. Cô đã mất đếm từ lâu những vết sẹo tích lũy trong mấy tháng qua khi chiến đấu với tội phạm. Chúng rồi cũng lành thôi. Hơn nữa, cô chắc chắn rằng những kẻ gây ra vết thương cho cô đã phải trả giá đắt hơn cô nhiều.
-Chiến thuật của cô đơn giản: khiến bọn tội phạm khốn đốn mà không để lộ mặt, rồi biến mất trước khi Phòng Discipline đến dọn dẹp đống hỗn độn. Đó không phải vì chủ nghĩa anh hùng. Chỉ là cô không ngốc đến mức tự vẽ bia đỡ đạn lên lưng, rồi bị đuổi khỏi &lt;te href=850097&gt;Ragunna&lt;/te&gt;, phải trốn trong một thị trấn tồi tàn nào đó mà không được thưởng thức pizza hay Nectarwine.
+Chiến thuật của cô đơn giản: khiến bọn tội phạm khốn đốn mà không để lộ mặt, rồi biến mất trước khi Phòng Kỷ Luật đến dọn dẹp đống hỗn độn. Đó không phải vì chủ nghĩa anh hùng. Chỉ là cô không ngốc đến mức tự vẽ bia đỡ đạn lên lưng, rồi bị đuổi khỏi &lt;te href=850097&gt;Ragunna&lt;/te&gt;, phải trốn trong một thị trấn tồi tàn nào đó mà không được thưởng thức pizza hay Nectarwine.
 Luôn an toàn hơn khi là kẻ vô danh. Một người tầm thường. Một người không ai coi là mối đe dọa.
 Mục tiêu đêm nay là những kẻ bắt cóc. Cô đã theo dõi chúng nhiều ngày, và tên đầu sỏ – gã thô lỗ lúc nãy – không chỉ là tay sai đơn thuần. Hắn là một Resonator khó nhằn. Nhưng hắn đã phạm sai lầm chết người khi đi một mình, tạo cơ hội hoàn hảo cho cô ra tay. Giờ cô chỉ cần hạ gục đám còn lại trước khi chúng phát hiện sếp mình đã biến mất.
 Cô siết chặt nắm đấm đồng, xoay cổ tay.
-"Sếp chắc sắp về rồi nhỉ? Nhà con bé kia cũng không xa lắm," một gã cao gầy ngáp dài, liếc về phía cô bé đang co ro trong góc lồng gỗ, ôm con búp bê. Hắn nhướn cằm về phía cô bé, "Thế sau khi lấy tiền xong thì sao? Ta bảo thả nó đi cho rồi."
+"Sếp chắc sắp về rồi nhỉ? Nhà con bé kia cũng không xa lắm," một gã cao gầy ngáp dài, liếc về phía cô bé đang co ro trong góc lồng gỗ, ôm con búp bê. Hắn nhướn cằm về phía cô bé, "Thế sau khi lấy tiền xong thì sao? Tao bảo thả nó đi cho rồi."
 "Nhưng nó đã thấy mặt tụi mình rồi," gã thấp hơn thở dài. "Thả nó đi thì chắc chắn sẽ bị truy lùng bởi... tên gì ấy nhỉ? Kẻ Đi Bộ Đêm Cháy gì đó?"
-"Kẻ Đi Bộ Đêm Cháy," gã cao gầy sửa lại. "Ta hiểu tại sao sếp lo, nhưng đã hẹn là hẹn. Lấy tiền xong thì thả con bé đi. Giết nó là thừa."
+"Kẻ Đi Bộ Đêm Cháy," gã cao gầy sửa lại. "Tao hiểu tại sao sếp lo, nhưng đã hẹn là hẹn. Lấy tiền xong thì thả con bé đi. Giết nó là thừa."
 "Nhân danh &lt;te href=850105&gt;Imperator&lt;/te&gt;, Ragunna từ lâu đã là vùng đất không luật lệ," gã thấp lẩm bẩm, im lặng nặng nề bao trùm. Gã cao gầy quay sang nhìn cô bé trong lồng, nhưng lập tức ngoảnh mặt đi như bị bỏng.
-"...Ta cần hít thở tí không khí."
+"...Tao cần hít thở tí không khí."
 Gã cao gầy đứng dậy, cáu kỉnh, mở cửa sào huyệt. Luồng khí lạnh khiến hắn rùng mình, nhưng không kéo dài. Trước khi kịp phản ứng, một vật lạnh lẽo, cứng ngắc đập vào trán hắn, và bóng tối nuốt chửng hắn.
-"Ngươi... ngươi là ai, quỷ tha ma bắt?"
+"Mày... mày là ai, quỷ tha ma bắt?"
 Gã thấp loay hoay với khẩu súng ở phía bên kia bàn. Hắn suýt chạm được vào nó, nhưng kẻ đột nhập còn nhanh hơn. Ngay khi ý thức bắt đầu mờ nhạt, hắn cảm thấy đầu ngón tay mình chạm vào cán súng. Chỉ thế thôi.
 Xong rồi, Zani nghĩ, thở phào nhẹ nhõm. Vết thương ở vai lại rỉ máu, nhưng vẫn đáng giá.
-Với một cú đấm, cô phá vỡ ổ khóa trên lồng gỗ, lột áo khoác của gã cao gầy phủ lên người cô bé đang run rẩy. Cô đã gửi một lá thư nặc danh đến &lt;te href=800005&gt;Chamber of Discipline&lt;/te&gt; trên đường đến đây. Nếu mọi thứ suôn sẻ, họ sẽ đến sớm thôi. Đến lúc cô phải rời đi.
+Với một cú đấm, cô phá vỡ ổ khóa trên lồng gỗ, lột áo khoác của gã cao gầy phủ lên người cô bé đang run rẩy. Cô đã gửi một lá thư nặc danh đến &lt;te href=800005&gt;Phòng Kỷ Luật&lt;/te&gt; trên đường đến đây. Nếu mọi thứ suôn sẻ, họ sẽ đến sớm thôi. Đến lúc cô phải rời đi.
 "Chị... chị ơi..."
 Zani quay lại khi nghe tiếng gọi và thấy cô bé đứng sau lưng, ngập ngừng. Lấy hết can đảm, cô bé đưa món đồ chơi yêu quý của mình ra.
 "Cái này... cho chị! Cảm ơn chị đã cứu cháu!"
@@ -27773,17 +27750,17 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Công việc là công việc và cuộc sống là cuộc sống; duy trì ranh giới rõ ràng giữa hai điều này là điều cần thiết để mọi thứ vận hành trơn tru. 
-Taoqi luôn sống theo nguyên tắc này, và không gì ở &lt;te href=850091&gt;Jinzhou&lt;/te&gt; có thể ngăn cô rời khỏi công việc đúng giờ. 
-&lt;te href=850085&gt;Ministry of Development&lt;/te&gt; là một nơi bận rộn, với mọi người liên tục đến đi và gấp rút hoàn thành công việc. Giữa sự hỗn loạn đó, giọng nói nhẹ nhàng của Taoqi luôn có thể xoa dịu cơn bão. Giữa đống giấy tờ bừa bộn, nó mang lại sự bình yên và làm chậm nhịp độ.
-"Đã đến giờ tan làm. Đến lúc về nhà rồi." 
-"Xin chờ một chút, cô Taoqi. Chúng tôi có một tài liệu mới được ban hành cần cô xem qua."
-"Được rồi, để tôi xem nào... Có vẻ không gấp lắm. Tôi sẽ giải quyết vào ngày mai."
-Sau giờ làm, Taoqi có cách thư giãn riêng của mình. Đối với cô, "thư giãn" có thể có nhiều hình thức — từ một giấc ngủ ngon đến một buổi đi dạo nhẹ nhàng.
-Trên đường về nhà, Taoqi thích dạo bước qua những con phố của Jinzhou và trò chuyện với cư dân nơi đây. Cô thích nghe những câu chuyện của người già về lịch sử thành phố và những cuộc trò chuyện vui vẻ với trẻ em, điều đó gợi nhớ cho cô về niềm hy vọng trong Jinzhou. Cách thư giãn này giúp cô gắn kết hơn với thành phố mình đang sống và cũng đóng góp cho công việc của mình. 
-Trong quá khứ, &lt;te href=850086&gt;Midnight Rangers&lt;/te&gt; luôn phải vật lộn để chống lại những cuộc tấn công bất ngờ từ &lt;te href=850081&gt;Tacet Discords&lt;/te&gt;. Với chiến tuyến trải dài như vậy, gần như không thể phát hiện mọi lỗ hổng và họ luôn ở trong tình trạng dễ bị tổn thương. Vì vậy, họ đã tìm đến Taoqi để nhờ giúp đỡ.
-Cảm thấy căng thẳng và choáng ngợp, Taoqi đã nghỉ giải lao trên một chiếc xích đu gần đó. Khi cô quan sát những đứa trẻ chơi trong hố cát, một ý tưởng nảy ra trong đầu cô — giống như cách chúng lấp đầy những khoảng trống trong lâu đài cát của mình, họ cũng có thể lấp đầy những khoảng trống trên chiến tuyến. Cô đề xuất xây dựng một bức tường cát tại chiến tuyến trong các cuộc tấn công của Discord. Điều này sẽ rút ngắn chiến tuyến và hạn chế đường tấn công của kẻ địch. Với ít điểm cần phòng thủ hơn, Midnight Rangers sẽ có thêm thời gian để đánh giá từng đợt tấn công và phản ứng phù hợp dựa trên sự biến dạng khác nhau của cát. Nhờ ý tưởng thông minh của Taoqi, họ đã có thể bảo vệ bản thân tốt hơn trước các cuộc tấn công và có thêm thời gian nghỉ ngơi cần thiết trên chiến tuyến.
-Theo Taoqi, ngồi nhìn chằm chằm vào bàn làm việc cả ngày sẽ dẫn đến sự đơn điệu và mất kết nối với thực tế. Vì vậy, cô tìm kiếm những phương pháp thay thế để nâng cao hiệu quả. Chính trong thời gian rảnh rỗi, cô tình cờ tìm thấy những hướng dẫn và nguồn cảm hứng bất ngờ thông qua những cuộc gặp gỡ tình cờ.</t>
+          <t>Công việc là công việc, cuộc sống là cuộc sống; giữ ranh giới rõ ràng giữa hai thứ mới đảm bảo mọi thứ vận hành trơn tru. 
+Taoqi luôn sống theo nguyên tắc này, và chẳng gì ở &lt;te href=850091&gt;Jinzhou&lt;/te&gt; có thể ngăn cô rời công sở đúng giờ. 
+&lt;te href=850085&gt;Bộ Phát Triển&lt;/te&gt; lúc nào cũng bận rộn, người ra kẻ vào, tất cả đều hối hả với công việc của mình. Giữa dòng chảy hỗn loạn ấy, giọng nói nhẹ nhàng của Taoqi luôn như một luồng gió lặng, mang lại bình yên và làm chậm nhịp sống. 
+"Hết giờ làm rồi. Về thôi." 
+"Xin chờ một chút, cô Taoqi. Có tài liệu mới ban hành cần cô xem qua." 
+"Để tôi xem nào... Có vẻ không gấp. Để mai giải quyết." 
+Sau giờ làm, Taoqi có cách thư giãn rất riêng. Với cô, "thư giãn" có thể đến dưới nhiều hình thức—từ một giấc ngủ ngon đến một buổi dạo chơi nhẹ nhàng. 
+Trên đường về nhà, cô thích lang thang qua những con phố ở Jinzhou, trò chuyện với người dân nơi đây. Cô thích nghe những câu chuyện của các cụ về lịch sử thành phố, hay những cuộc trò chuyện vui vẻ với lũ trẻ, nhắc nhở cô về niềm hy vọng vẫn còn trong Jinzhou. Cách thư giãn này giúp cô gắn kết hơn với thành phố mình đang sống, đồng thời cũng góp phần vào công việc của mình. 
+Ngày trước, &lt;te href=850086&gt;Midnight Rangers&lt;/te&gt; luôn phải vật lộn chống lại những đợt tấn công bất ngờ của &lt;te href=850081&gt;Tacet Discord&lt;/te&gt;. Với chiến tuyến trải dài như vậy, gần như không thể phát hiện mọi lỗ hổng, và họ luôn ở thế bị động. Vì vậy, họ đã tìm đến Taoqi nhờ giúp đỡ. 
+Cảm thấy căng thẳng và choáng ngợp, Taoqi quyết định nghỉ ngơi trên chiếc xích đu gần đó. Khi nhìn lũ trẻ chơi trong hố cát, một ý tưởng chợt lóe lên trong đầu cô—giống như cách chúng lấp đầy những khoảng trống trong lâu đài cát, họ cũng có thể lấp đầy những khoảng trống trên chiến tuyến. Cô đề xuất xây dựng một bức tường cát tại tiền tuyến khi Tacet Discord tấn công. Điều này sẽ rút ngắn chiến tuyến và hạn chế đường tấn công của kẻ địch. Với ít điểm cần phòng thủ hơn, Midnight Rangers sẽ có thêm thời gian đánh giá từng đợt tấn công và phản ứng dựa trên sự biến đổi tần số do cát gây ra. Nhờ ý tưởng thông minh của Taoqi, họ đã bảo vệ bản thân tốt hơn và có thêm thời gian nghỉ ngơi quý giá trên chiến tuyến. 
+Theo Taoqi, ngồi lì một chỗ cả ngày sẽ dẫn đến sự đơn điệu và mất kết nối với thực tế. Vì vậy, cô luôn tìm kiếm những phương pháp khác để nâng cao hiệu quả. Chính trong những khoảng thời gian rảnh rỗi, cô lại tình cờ tìm thấy những chỉ dẫn và nguồn cảm hứng bất ngờ từ những cuộc gặp gỡ ngẫu nhiên.</t>
         </is>
       </c>
     </row>
@@ -27961,14 +27938,14 @@
         <is>
           <t>Một ngày nọ, chú Vi thợ rèn có một vị khách kỳ lạ.
 Đó là một cô bé trông gầy gò, ít nói. Nhưng yêu cầu của cô lại khác thường: cô nhờ chú sửa một thanh kiếm bị gãy.
-"Nó bị sao thế?" Uncle Wei nhíu ngươi hỏi. Uncle đã sửa không biết bao nhiêu vũ khí hư hỏng, nhưng vẫn không khỏi tò mò điều gì đã khiến lưỡi kiếm này hư hại nặng đến vậy.
+"Nó bị sao thế?" Chú Vi nhíu mày hỏi. Chú đã sửa không biết bao nhiêu vũ khí hư hỏng, nhưng vẫn không khỏi tò mò điều gì đã khiến lưỡi kiếm này hư hại nặng đến vậy.
 Trong đầu chú Vi hiện lên hình ảnh một gã đàn ông lực lưỡng vung kiếm với sức mạnh khủng khiếp, chém phá không thương tiếc mọi thứ cản đường. Làm sao mà một cô bé mảnh khảnh như thế lại có thể liên quan đến cảnh tượng đó?
 "Xin lỗi... cháu có lẽ đánh mạnh quá... Cháu không cố ý đâu..." cô bé đáp, vẻ ngượng ngùng. "Sửa khó lắm không chú?"
-Uncle Wei trố mắt nhìn cô. Ông dùng ngón tay chai sạn sờ vào lưỡi kiếm bị cong vênh rồi nói: "...Không sao. Để chú thử xem."
+Chú Vi trố mắt nhìn cô. Ông dùng ngón tay chai sạn sờ vào lưỡi kiếm bị cong vênh rồi nói: "...Không sao. Để chú thử xem."
 Với sự tỉ mỉ và điêu luyện, chú Vi nung nóng lưỡi kiếm cho đến khi đỏ rực rồi đập mạnh bằng búa. Tia lửa bắn ra, nhưng lưỡi kiếm vẫn không hề suy chuyển. Kinh nghiệm bao năm giúp chú kiểm tra và vuốt ve miếng kim loại hư hỏng, suy tính từng nhát búa. Rồi trong khoảnh khắc, chú phát hiện ra vấn đề.
 "Lưỡi kiếm này cứng nhưng thiếu dẻo. Trọng tâm bị lệch rồi, lại còn có tần số đặc biệt nữa. Khó sửa và mài bằng công cụ thông thường lắm."
 "Muốn sửa nó," chú Vi tiếp lời, "cháu cần vài viên phấn xám thật cứng chứa nhiều Tacetite. Nhưng thứ đó khó kiếm lắm, chỉ có ở nơi nguy hiểm, nhiều vách đá cheo leo thôi! Đừng mong đợi quá, cháu ơi."
-"Uncle nói Hoang Mạc Đá Desorock phải không ạ? Cho cháu chút thời gian. Cháu sẽ quay lại ngay!"
+"Chú nói Hoang Mạc Đá Desorock phải không ạ? Cho cháu chút thời gian. Cháu sẽ quay lại ngay!"
 Nói rồi, cô bé vụt chạy đi như gió, để lại chú Vi ngơ ngác và thanh kiếm cong vênh bị bỏ quên.
 Không lâu sau, cô quay lại, tay xách một khối phấn xám to tướng nhẹ tênh.
 "Thế này đủ chưa chú?" cô hỏi, khiến chú Vi ngạc nhiên vì cô trở về quá nhanh từ Hoang Mạc Đá Desorock nguy hiểm.
@@ -28042,11 +28019,11 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Mọi gánh hàng rong ở Jinzhou đều biết Danjin. Sau cơn mưa, khi mặt trời ló dạng và không khí ẩm ướt, họ lại bày hàng. Tiếng xoong nồi va vào nhau hòa cùng mùi si-rô ngọt ngào. Đó là lúc Danjin xuất hiện, đưa ra một xấp &lt;te href=850104&gt;Shell Credits&lt;/te&gt; gọn gàng để đổi lấy món ăn yêu thích: hai miếng &lt;te href=850115&gt;Loong Whiskers Crisp&lt;/te&gt;. Cô luôn cất một miếng vào túi trước, rồi mới háo hức bẻ miếng còn lại, thưởng thức từng mẩu như thể đó là viên ngọc quý.
-Một bà bán hàng thấy Danjin luôn đến một mình, không khỏi thương cảm: Ngay cả món ăn vặt rẻ nhất ở Jinzhou như Loong Whiskers Crisp cũng trở nên quý giá với cô bé này. Muốn chia sẻ chút lòng tốt, bà bắt đầu tặng Danjin thêm vài món ăn vặt mà các cô gái cùng tuổi thích—từ Sugar Phèn xinh xắn đến Kẹo Bông mềm mại, và nhiều thứ khác. Lúc đầu, Danjin luôn từ chối, vì cô ngại nhận lòng tốt của người khác mà không có lý do chính đáng, và vì ví tiền của cô cũng cạn dần do liên tục sửa chữa vũ khí.
+          <t>Mọi gánh hàng rong ở Jinzhou đều biết Danjin. Sau cơn mưa, khi mặt trời ló dạng và không khí ẩm ướt, họ lại bày hàng. Tiếng xoong nồi va vào nhau hòa cùng mùi si-rô ngọt ngào. Đó là lúc Danjin xuất hiện, đưa ra một xấp &lt;te href=850104&gt;Shell Credits&lt;/te&gt; gọn gàng để đổi lấy món ăn yêu thích: hai miếng &lt;te href=850115&gt;Bánh Giòn Râu Rồng&lt;/te&gt;. Cô luôn cất một miếng vào túi trước, rồi mới háo hức bẻ miếng còn lại, thưởng thức từng mẩu như thể đó là viên ngọc quý.
+Một bà bán hàng thấy Danjin luôn đến một mình, không khỏi thương cảm: Ngay cả món ăn vặt rẻ nhất ở Jinzhou như Bánh Giòn Râu Rồng cũng trở nên quý giá với cô bé này. Muốn chia sẻ chút lòng tốt, bà bắt đầu tặng Danjin thêm vài món ăn vặt mà các cô gái cùng tuổi thích—từ Đường Phèn xinh xắn đến Kẹo Bông mềm mại, và nhiều thứ khác. Lúc đầu, Danjin luôn từ chối, vì cô ngại nhận lòng tốt của người khác mà không có lý do chính đáng, và vì ví tiền của cô cũng cạn dần do liên tục sửa chữa vũ khí.
 Nhưng bà bán hàng nhất quyết rằng chẳng phiền gì khi cho Danjin thêm chút đồ ngọt, vì bà luôn chuẩn bị dư món ăn vặt cho em gái ở nhà—một cô bé cùng tuổi với Danjin và rất thích đồ ngọt. Xúc động trước tấm lòng chân thành ấy, Danjin cuối cùng cũng gật đầu nhận thêm đồ ăn.
-Kể từ hôm đó, mỗi lần bà bán hàng tặng Danjin thêm đồ ngọt, một món quà bí ẩn lại xuất hiện trên gánh hàng của bà. Sugar phèn thì có Pearl Leaf, Kẹo Bông thì có Gai Cây. Những loại thảo dược này rất quan trọng trong việc làm dịu chứng rối loạn hoảng sợ của em gái bà—điều mà bà thậm chí còn chưa kể cho Danjin.
-Có lẽ sớm muộn gì, em gái bà cũng sẽ có thể tự mình ra khỏi nhà, và cùng Danjin thưởng thức Loong Whiskers Crisp mới ra lò.</t>
+Kể từ hôm đó, mỗi lần bà bán hàng tặng Danjin thêm đồ ngọt, một món quà bí ẩn lại xuất hiện trên gánh hàng của bà. Đường phèn thì có Lá Ngọc Trai, Kẹo Bông thì có Gai Cây. Những loại thảo dược này rất quan trọng trong việc làm dịu chứng rối loạn hoảng sợ của em gái bà—điều mà bà thậm chí còn chưa kể cho Danjin.
+Có lẽ sớm muộn gì, em gái bà cũng sẽ có thể tự mình ra khỏi nhà, và cùng Danjin thưởng thức Bánh Giòn Râu Rồng mới ra lò.</t>
         </is>
       </c>
     </row>
@@ -28127,9 +28104,9 @@
       <c r="M403" t="inlineStr">
         <is>
           <t>Nàng tỉnh giấc sau cơn mơ.
-Bốn bức tường của khoang y tế chìm dần vào bóng tối. Bị bao trùm trong sự im lặng nặng nề do hệ thống cách âm, Camellya chớp mắt, ánh nhìn khô khốc quay sang bên phải. Các chỉ số trên màn hình Terminal đã trở lại bình thường. Xiềng xích trên cổ tay và mắt cá chân đã nới lỏng, thế nhưng nàng vẫn cảm thấy yếu ớt, buộc phải nằm yên trong không gian chật hẹp của khoang.
+Bốn bức tường của khoang y tế chìm dần vào bóng tối. Bị bao trùm trong sự im lặng nặng nề do hệ thống cách âm, Camellya chớp mắt, ánh nhìn khô khốc quay sang bên phải. Các chỉ số trên màn hình Thiết bị đầu cuối đã trở lại bình thường. Xiềng xích trên cổ tay và mắt cá chân đã nới lỏng, thế nhưng nàng vẫn cảm thấy yếu ớt, buộc phải nằm yên trong không gian chật hẹp của khoang.
 Nàng cố nhớ lại những gì đã xảy ra. Nàng cố gắng giữ vẻ bình tĩnh mong manh để hồi tưởng, nhưng ký ức đã mất như một vực thẳm không đáy—nhìn vào chỉ thấy bóng tối. Ký ức của nàng lại một lần nữa vỡ vụn.
-Chỉ mới ở cùng &lt;te href=850109&gt;the Black Shores&lt;/te&gt; được một năm, Camellya vừa mới vượt qua bài test để trở thành Bloom Bearer chính thức. Giờ đây, nàng được tiếp cận nhiều hơn với kho lưu trữ thông tin của hệ thống &lt;te href=850110&gt;Tethys&lt;/te&gt;.
+Chỉ mới ở cùng &lt;te href=850109&gt;Black Shores&lt;/te&gt; được một năm, Camellya vừa mới vượt qua bài kiểm tra để trở thành Bloom Bearer chính thức. Giờ đây, nàng được tiếp cận nhiều hơn với kho lưu trữ thông tin của hệ thống &lt;te href=850110&gt;Tethys&lt;/te&gt;.
 Trước khi đến đó, nàng đã lang thang khắp &lt;te href=850079&gt;Solaris&lt;/te&gt; trong một thời gian dài.
 Hang động nơi nàng lần đầu tỉnh dậy không có dấu vết của bất kỳ ai khác, chỉ có những loài thực vật quái dị bám trên vách đá. Chân trần, Camellya lội qua dòng nước cho đến khi ra khỏi hang, phát hiện một ngôi làng hoang tàn. Bàn chân nàng va phải thứ gì đó—một tấm bia đá với dòng chữ mờ nhạt: "Làng Petalfall".
 Nàng mất rất nhiều thời gian để thoát khỏi nơi bị bỏ hoang ấy. Khi đói, nàng săn thú rừng để ăn. Khi khát, nàng uống nước suối trên núi. Phải mất vài tháng băng rừng vượt suối, nàng mới đến được một nơi đông đúc người qua lại. Sau này nàng mới biết, ngôi làng đó có lẽ đã bị lãng quên hàng trăm năm rồi.
@@ -28137,10 +28114,10 @@
 Ban đầu, mọi thứ trên Solaris đều khiến nàng tò mò. Nhưng khi dần hiểu biết nhiều hơn, nàng nhanh chóng cảm thấy chán ngán. Việc đến với Black Shores chỉ là một sự tình cờ, thế nhưng Camellya lại cảm thấy một sự quen thuộc kỳ lạ với nơi này. Một năm sau, nàng tìm thấy tên mình trong hệ thống Tethys và biết rằng mình từng sống và làm việc ở đó, khi ấy được gọi là Lady Flora. Thật kỳ lạ khi nàng quên hết mọi thứ nhưng vẫn nhớ tên "Camellya".
 Vì tò mò, nàng bắt đầu điều tra về Black Shores, háo hức khám phá quá khứ của mình và câu chuyện về Lady Flora. Điều gì đã thực sự xảy ra với nàng?
 Khi những suy nghĩ ấy hiện lên, một cơn đau nhói lại xuyên qua đầu nàng, và bông hoa trong ngực đột nhiên phình to, sẫm màu thành tím thẫm. Những chiếc gai sắc nhọn của mạch máu đe dọa xé toạc khoang y tế. Những mảnh ký ức vụn vặt lóe lên trong tâm trí—À, Lady Flora đã cấm nàng nhớ về quá khứ. Camellya thốt lên một tiếng thét đau đớn bị nghẹn lại khi xiềng xích siết chặt tay chân nàng một lần nữa, và tiếng chuông báo động inh ỏi vang lên. Nhân viên y tế sẽ đến ngay thôi.
-Nhưng nàng biết họ chẳng thể làm gì được. Họ đã test nàng kỹ lưỡng, kết luận rằng triệu chứng &lt;te href=850073&gt;Overclocking&lt;/te&gt; của nàng là duy nhất và không thể chữa trị, chỉ có thể kiểm soát bằng cách kiềm chế. Cái chết có thể mang lại sự giải thoát, nhưng ở tình trạng hiện tại, nàng thậm chí không thể chết một cách đơn giản.
+Nhưng nàng biết họ chẳng thể làm gì được. Họ đã kiểm tra nàng kỹ lưỡng, kết luận rằng triệu chứng &lt;te href=850073&gt;Overclocking&lt;/te&gt; của nàng là duy nhất và không thể chữa trị, chỉ có thể kiểm soát bằng cách kiềm chế. Cái chết có thể mang lại sự giải thoát, nhưng ở tình trạng hiện tại, nàng thậm chí không thể chết một cách đơn giản.
 Tất cả những gì nàng có thể làm là chờ đợi, chờ đợi ân huệ của tử thần. Sự thụ động này khiến tinh thần nàng bức bối. Nếu không thể quyết định kết cục, ít nhất nàng cũng muốn kiểm soát quá trình.
 "Ta sẽ đi theo bản năng cho đến khi tử thần tìm đến ta."
-"It hurts!" nàng nghĩ.
+"Đau quá!" nàng nghĩ.
 Dù đau đớn, Camellya vẫn cười lớn.</t>
         </is>
       </c>
@@ -29441,7 +29418,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Tên khoa học "Resinacrustidum lapis", thuộc loài Resinacrustidum. Discord này thường hoạt động cùng với Vanguard Junrocks. Điểm khác biệt giữa hai loài là loài này có nhiều Tacetite hơn trên vỏ, do đó hoạt động năng lượng mạnh mẽ và bất ổn hơn. Tác động bên ngoài có thể gây nổ. Đã có ghi nhận về việc chúng bị các Discord khác dùng làm vũ khí Dodgem.</t>
+          <t>Tên khoa học "Resinacrustidum lapis", thuộc loài Resinacrustidum. Tacet Discord này thường hoạt động cùng với Vanguard Junrocks. Điểm khác biệt giữa hai loài là loài này có nhiều Tacetite hơn trên vỏ, do đó hoạt động năng lượng mạnh mẽ và bất ổn hơn. Tác động bên ngoài có thể gây nổ. Đã có ghi nhận về việc chúng bị các Tacet Discord khác dùng làm vũ khí ném.</t>
         </is>
       </c>
     </row>
@@ -29509,8 +29486,8 @@
       <c r="M424" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Electro]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#1891e7&gt;Electro DMG&lt;/color&gt;. 
-Tên nhị thức "Flautist", loài Devourer. Chi trên bên trái của Kẻ săn mồi Electro đã tiến hóa thành cung tên, có thể tích tụ năng lượng Electro để bắn ở khoảng cách xa hơn.</t>
+Mục tiêu này có &lt;color=#b49f50&gt;Kháng Electro DMG cao&lt;/color&gt;. 
+Tên nhị thức "Flautist", loài Devourer. Chi trước bên trái của Kẻ săn mồi Electro đã tiến hóa thành cung tên, có thể tích tụ năng lượng Electro để bắn xa hơn.</t>
         </is>
       </c>
     </row>
@@ -29643,7 +29620,7 @@
       <c r="M426" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Glacio]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; trước &lt;color=#1891e7&gt;Glacio DMG&lt;/color&gt;. 
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; trước &lt;color=#1891e7&gt;Sát Thương Glacio&lt;/color&gt;. 
 Tên khoa học "Devorsonidum glacies", loài Devourer. Glacio Predator đã tiến hóa cấu trúc cơ thể giống như "áo choàng" của con người, được cho là để thu thập Năng Lượng Glacio nhanh hơn nhằm hình thành "giáo" để tấn công tầm xa.</t>
         </is>
       </c>
@@ -29777,8 +29754,8 @@
       <c r="M428" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Aero]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#1891e7&gt;Aero DMG&lt;/color&gt;. 
-Tên nhị thức "Devorsonidum spiritalis", một thành viên của chi Devorsonidum. Khác với các "Predator" TD khác tập trung năng lượng để tấn công, vũ khí Dodgem của Aero Predator là một phần cấu trúc cơ thể và có thể được thu hồi bằng năng lượng Aero của chính nó sau khi Dodgem.</t>
+Mục tiêu này có &lt;color=#b49f50&gt;Kháng Aero DMG cao&lt;/color&gt;. 
+Tên nhị thức "Devorsonidum spiritalis", thuộc chi Devorsonidum. Khác với các Tacet Discord "Thú săn mồi" khác tích tụ năng lượng để tấn công, vũ khí ném của Kẻ săn mồi Aero là một phần cấu trúc cơ thể, và có thể thu hồi bằng năng lượng Aero của chính nó sau khi ném.</t>
         </is>
       </c>
     </row>
@@ -29843,7 +29820,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Vũ khí Dodgem của Aero Predator có khả năng bám đuổi kẻ địch. Hãy cẩn thận với quỹ đạo của nó, nếu không cậu sẽ chịu sát thương nặng.</t>
+          <t>Vũ khí ném của Aero Predator có khả năng bám đuổi kẻ địch. Hãy cẩn thận với quỹ đạo của nó, nếu không cậu sẽ chịu sát thương nặng.</t>
         </is>
       </c>
     </row>
@@ -29911,8 +29888,8 @@
       <c r="M430" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Fusion]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; trước &lt;color=#1891e7&gt;Fusion DMG&lt;/color&gt;. 
-Tên khoa học "Devorsonidum fusio", thuộc chi Devorsonidum. Hai chi trước của nó giống như hai ngọn giáo dài ngắn khác nhau, có thể tấn công bằng cách đâm và chém. Mức độ nguy hiểm trung bình. Trong lúc tấn công, Echo này được quan sát thấy thực hiện động tác giống như chào, có lẽ là bắt chước vụng về cách sử dụng kiếm của con người.</t>
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; trước &lt;color=#1891e7&gt;Sát Thương Fusion&lt;/color&gt;. 
+Tên khoa học "Devorsonidum fusio", thuộc chi Devorsonidum. Hai chi trước của nó giống như hai ngọn giáo dài ngắn khác nhau, có thể tấn công bằng cách đâm và chém. Mức độ nguy hiểm trung bình. Trong lúc tấn công, Tổ Tacet này được quan sát thấy thực hiện động tác giống như chào, có lẽ là bắt chước vụng về cách sử dụng kiếm của con người.</t>
         </is>
       </c>
     </row>
@@ -30045,7 +30022,7 @@
       <c r="M432" t="inlineStr">
         <is>
           <t>&lt;color=#7e1f57&gt;[Havoc]&lt;/color&gt;
-Mục tiêu có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; trước &lt;color=#7e1f57&gt;Havoc DMG&lt;/color&gt;. 
+Mục tiêu có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; trước &lt;color=#7e1f57&gt;Sát Thương Havoc&lt;/color&gt;. 
 Tên nhị thức "Tambourinist", thuộc chi Disorder. Ngoại hình giống con người, có ham muốn tấn công mạnh mẽ. Mức độ nguy hiểm cao. Tacet Discord này có các bộ phận trông giống "vải", được cho là cấu trúc tiến hóa để bắt chước trang phục con người, dù chức năng vẫn chưa rõ.</t>
         </is>
       </c>
@@ -30114,7 +30091,7 @@
       <c r="M433" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Fusion]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; trước &lt;color=#1891e7&gt;Fusion DMG&lt;/color&gt;. 
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; trước &lt;color=#1891e7&gt;Sát Thương Fusion&lt;/color&gt;. 
 Tên khoa học "Strepoplasmidum fusio", thuộc chi Strepoplasmidum. Không có trí thông minh. Do cơ thể hình kìm, Snip Snap đôi khi được gọi là "quái vật kìm". Năng lượng Fusion ở loài này được quan sát ở mức thấp.</t>
         </is>
       </c>
@@ -30248,7 +30225,7 @@
       <c r="M435" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Spectro]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; trước &lt;color=#1891e7&gt;Spectro DMG&lt;/color&gt;. 
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; trước &lt;color=#1891e7&gt;Sát Thương Spectro&lt;/color&gt;. 
 Tên khoa học là "Strepoplasmidum spectrum", thuộc chi Strepoplasmidum. Chúng được đặt tên như vậy do thiếu trí thông minh và hành vi đơn giản. Năng lượng Spectro được phát hiện ở mức thấp.</t>
         </is>
       </c>
@@ -30314,7 +30291,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Khi Zig Zag bị đánh bại, năng lượng Spectro còn sót lại trong cơ thể nó có thể gây ra vụ nổ, nhưng có thể bị ngăn chặn bằng một đòn tấn công kịp thời. Nếu vụ nổ thành công, nó sẽ để lại một vòng năng lượng Diffusion làm chậm Resonators bên trong.</t>
+          <t>Khi Zig Zag bị đánh bại, năng lượng Spectro còn sót lại trong cơ thể nó có thể gây ra vụ nổ, nhưng có thể bị ngăn chặn bằng một đòn tấn công kịp thời. Nếu vụ nổ thành công, nó sẽ để lại một vòng năng lượng Khuếch tán làm chậm các Resonator bên trong.</t>
         </is>
       </c>
     </row>
@@ -30382,7 +30359,7 @@
       <c r="M437" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Aero]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#1891e7&gt;Aero DMG&lt;/color&gt;.
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; đối với &lt;color=#1891e7&gt;Sát Thương Aero&lt;/color&gt;.
 Tên khoa học "Strepoplasmidum spiritalis", thuộc chi Strepoplasmidum. Không có trí tuệ. Vì khối năng lượng Aero tụ lại ở "đầu" phát ra âm thanh giống như gió thổi, nên nó có tên là "Whiff Whaff".</t>
         </is>
       </c>
@@ -30448,7 +30425,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Khi Whiff Whaff bị đánh bại, năng lượng Aero còn sót lại trong cơ thể nó có thể gây ra vụ nổ, nhưng có thể bị ngăn chặn bằng một đòn tấn công kịp thời. Nếu vụ nổ thành công, nó sẽ để lại một Storm Eye tiếp tục hút người chơi vào trong và gây Sát Thương Theo Thời Gian trong phạm vi.</t>
+          <t>Khi Whiff Whaff bị đánh bại, năng lượng Aero còn sót lại trong cơ thể nó có thể gây ra vụ nổ, nhưng có thể bị ngăn chặn bằng một đòn tấn công kịp thời. Nếu vụ nổ thành công, nó sẽ để lại một Mắt Bão tiếp tục hút người chơi vào trong và gây Sát Thương Theo Thời Gian trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -30516,7 +30493,7 @@
       <c r="M439" t="inlineStr">
         <is>
           <t>&lt;color=#7e1f57&gt;[Havoc]&lt;/color&gt;
-Mục tiêu có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; trước &lt;color=#7e1f57&gt;Havoc DMG&lt;/color&gt;. 
+Mục tiêu có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; trước &lt;color=#7e1f57&gt;Sát Thương Havoc&lt;/color&gt;. 
 Tên nhị thức "Strepoplasmidum ruptura", thuộc chi Strepoplasmidum. Có thể sử dụng năng lượng Havoc ở mức cơ bản để tấn công, không có trí tuệ.</t>
         </is>
       </c>
@@ -30650,7 +30627,7 @@
       <c r="M441" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Glacio]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; trước &lt;color=#1891e7&gt;Glacio DMG&lt;/color&gt;. 
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; trước &lt;color=#1891e7&gt;Sát Thương Glacio&lt;/color&gt;. 
 Tên khoa học "Tetraodon lateo", một Sinh Vật Đột Biến thuộc chi Tetraodon. Phân bố rộng rãi ở mọi vùng nước ngọt. Chiếc lá hình bèo trên đỉnh đầu đóng vai trò như lớp ngụy trang, giúp nó phục kích con mồi hiệu quả.</t>
         </is>
       </c>
@@ -30716,7 +30693,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Gulpuff có thể Dodgen không khí trong túi khí của mình và phun ra để hất tung kẻ địch lên không trung, gây sát thương rơi đáng kể.</t>
+          <t>Gulpuff có thể nén không khí trong túi khí của mình và phun ra để hất tung kẻ địch lên không trung, gây sát thương rơi đáng kể.</t>
         </is>
       </c>
     </row>
@@ -30784,8 +30761,8 @@
       <c r="M443" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Aero]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#1891e7&gt;Aero DMG&lt;/color&gt;. 
-Tên nhị thức "Tetraodon spiritalis", một Sinh Vật Đột Biến thuộc chi Tetraodon. Được cho là có họ hàng với Gulpuff, mặc dù vị trí sinh thái của chúng có đôi chút khác biệt. Chirpuff chủ yếu sống trên không, săn bắt côn trùng.</t>
+Mục tiêu này có &lt;color=#b49f50&gt;Kháng Aero DMG cao&lt;/color&gt;. 
+Tên nhị thức "Tetraodon spiritalis", một Sinh Vật Đột Biến thuộc chi Tetraodon. Được cho là có họ hàng với Gulpuff, dù vị trí sinh thái của chúng có đôi chút khác biệt. Chirpuff chủ yếu sống trên không và săn bắt côn trùng.</t>
         </is>
       </c>
     </row>
@@ -30850,7 +30827,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Chirpuff có thể Dodgen không khí trong túi khí và phun ra để hất kẻ địch lên cao, gây sát thương rơi đáng kể.</t>
+          <t>Chirpuff có thể nén không khí trong túi khí và phun ra để hất kẻ địch lên cao, gây sát thương rơi đáng kể.</t>
         </is>
       </c>
     </row>
@@ -30918,7 +30895,7 @@
       <c r="M445" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Glacio]&lt;/color&gt;
-Kẻ địch này &lt;color=#b49f50&gt;immune&lt;/color&gt; với &lt;color=#1891e7&gt;Glacio DMG&lt;/color&gt;. 
+Kẻ địch này &lt;color=#b49f50&gt;miễn nhiễm&lt;/color&gt; với &lt;color=#1891e7&gt;Sát Thương Glacio&lt;/color&gt;. 
 Glacio Prism thuộc chi Resinacrustidum, có cấu trúc vỏ độc đáo có thể kích thích phản ứng hóa học với hơi nước trong không khí để hấp thụ lượng nhiệt lớn trong thời gian ngắn và chuyển hóa thành Năng Lượng Glacio để tấn công.</t>
         </is>
       </c>
@@ -30987,7 +30964,7 @@
       <c r="M446" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Fusion]&lt;/color&gt;
-Mục tiêu này &lt;color=#b49f50&gt;immune&lt;/color&gt; với &lt;color=#1891e7&gt;Fusion DMG&lt;/color&gt;. 
+Mục tiêu này &lt;color=#b49f50&gt;miễn nhiễm&lt;/color&gt; với &lt;color=#1891e7&gt;Fusion DMG&lt;/color&gt;. 
 Thuộc chi Resinacrustidum, Fusion Prism có khả năng tăng nhiệt độ nhanh chóng và duy trì nhiệt độ cao, có lẽ do môi trường sống có nhiệt độ cao. Lớp vỏ ngoài của nó có cấu trúc tương tự đá núi lửa, giúp chứa đựng lượng lớn năng lượng Fusion.</t>
         </is>
       </c>
@@ -31056,8 +31033,8 @@
       <c r="M447" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Spectro Prism]&lt;/color&gt;
-Kẻ địch này &lt;color=#b49f50&gt;immune&lt;/color&gt; với &lt;color=#1891e7&gt;Spectro DMG&lt;/color&gt;. 
-Là một thành viên của chi Resinacrustidum, Spectro Prism có cấu trúc vỏ khoáng độc đáo có thể bẫy photon hiệu quả, cho phép nó tích trữ năng lượng Spectro khổng lồ và phát ra dưới dạng chùm sáng. Nhiều năm trước, một quần thể Spectro Prism bùng nổ ở một quốc gia với tin đồn rằng Di Vật của nó là nguyên liệu cho những ngọn đèn sáng vĩnh cửu. Câu chuyện kết thúc bằng một bi kịch cướp đi hàng ngàn sinh mạng. *"Cấm sử dụng cho mục đích chiếu sáng"* - &lt;i&gt;Sổ tay Sử dụng Di Vật (Bản New Federation)&lt;/i&gt;</t>
+Kẻ địch này &lt;color=#b49f50&gt;miễn nhiễm&lt;/color&gt; với &lt;color=#1891e7&gt;Sát Thương Spectro&lt;/color&gt;. 
+Là một thành viên của chi Resinacrustidum, Spectro Prism có cấu trúc vỏ khoáng độc đáo có thể bẫy photon hiệu quả, cho phép nó tích trữ năng lượng Spectro khổng lồ và phát ra dưới dạng chùm sáng. Nhiều năm trước, một quần thể Spectro Prism bùng nổ ở một quốc gia với tin đồn rằng Di Vật của nó là nguyên liệu cho những ngọn đèn sáng vĩnh cửu. Câu chuyện kết thúc bằng một bi kịch cướp đi hàng ngàn sinh mạng. *"Cấm sử dụng cho mục đích chiếu sáng"* - &lt;i&gt;Sổ tay Sử dụng Di Vật (Bản Liên Bang Mới)&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -31125,8 +31102,8 @@
       <c r="M448" t="inlineStr">
         <is>
           <t>&lt;color=#7e1f57&gt;[Havoc]&lt;/color&gt;
-Mục tiêu &lt;color=#b49f50&gt;immune&lt;/color&gt; với &lt;color=#7e1f57&gt;Havoc DMG&lt;/color&gt;. 
-Gần đây, quan điểm cho rằng "Havoc Prism thuộc chi Resinacrustidum" đang bị đặt dấu hỏi tại New Federation và Lương Đảo, sau khi một nghiên cứu mới của các học giả Lương Đảo khẳng định lớp vỏ của "Havoc Prism" chỉ là sự bắt chước các Prism Tacet Discord khác, hình thành từ năng lượng cô đặc.</t>
+Mục tiêu &lt;color=#b49f50&gt;miễn nhiễm&lt;/color&gt; với &lt;color=#7e1f57&gt;Sát Thương Havoc&lt;/color&gt;. 
+Gần đây, quan điểm cho rằng "Havoc Prism thuộc chi Resinacrustidum" đang bị đặt dấu hỏi tại Liên Bang Mới và Lương Đảo, sau khi một nghiên cứu mới của các học giả Lương Đảo khẳng định lớp vỏ của "Havoc Prism" chỉ là sự bắt chước các Prism Tacet Discord khác, hình thành từ năng lượng cô đặc.</t>
         </is>
       </c>
     </row>
@@ -31194,7 +31171,7 @@
       <c r="M449" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Spectro]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; trước &lt;color=#1891e7&gt;Spectro DMG&lt;/color&gt;.
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; trước &lt;color=#1891e7&gt;Sát Thương Spectro&lt;/color&gt;.
 Tên khoa học "Acanthacorydalis squapenna". Loài hoạt động ban ngày. Thường xuất hiện ở ven nước tại các khu vực ấm áp và ẩm ướt trên khắp Huanglong. Dù hơi hung hăng, chúng dễ bị săn bắt bởi Geohide Saurian và các loài săn mồi khác, nên không quá nguy hiểm. Theo tên khoa học, chúng thuộc họ Corydalidae chứ không phải bướm.</t>
         </is>
       </c>
@@ -31393,7 +31370,7 @@
       <c r="M452" t="inlineStr">
         <is>
           <t>&lt;color=#7e1f57&gt;[Havoc]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#7e1f57&gt;Havoc DMG&lt;/color&gt;. 
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; đối với &lt;color=#7e1f57&gt;Sát Thương Havoc&lt;/color&gt;. 
 Tên khoa học "Myospalax actinoaftia", một loài sinh vật đột biến gặm nhấm phổ biến, thường xuất hiện ở đồng cỏ, rừng ôn đới và vùng núi. Chúng có thói quen tích trữ thức ăn trong hang. Những người gặp nạn ngoài hoang dã có thể tìm thấy nguồn dinh dưỡng khẩn cấp trong hang của Excarat.</t>
         </is>
       </c>
@@ -31462,7 +31439,7 @@
       <c r="M453" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Fusion]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; trước &lt;color=#1891e7&gt;Fusion DMG&lt;/color&gt;. 
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; trước &lt;color=#1891e7&gt;Sát Thương Fusion&lt;/color&gt;. 
 Một con Thằn Lằn Địa Ẩn non. Loài này không có tập tính chăm sóc con non, nên những con non chỉ có thể sống sót bằng cách bắt chước hành vi săn mồi của con trưởng thành, nhặt nhạnh thức ăn thừa hoặc, nếu cần, săn bắt chính đồng loại non của mình.</t>
         </is>
       </c>
@@ -31531,7 +31508,7 @@
       <c r="M454" t="inlineStr">
         <is>
           <t>&lt;color=#7e1f57&gt;[Havoc]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#7e1f57&gt;Havoc DMG&lt;/color&gt;. 
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; đối với &lt;color=#7e1f57&gt;Sát Thương Havoc&lt;/color&gt;. 
 Một cá thể Roseshroom non. Nó có đặc tính ưa bóng râm và ưa nước giống như cá thể trưởng thành. Nghiên cứu cho thấy ở giai đoạn chưa trưởng thành, Roseshroom chưa có khả năng hấp thụ dinh dưỡng từ Tacetite, do đó phải thu thập chất dinh dưỡng từ những cá thể Roseshroom trưởng thành gần đó để sinh tồn.</t>
         </is>
       </c>
@@ -31730,7 +31707,7 @@
       <c r="M457" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Aero]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#1891e7&gt;Aero DMG&lt;/color&gt;.
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; đối với &lt;color=#1891e7&gt;Sát Thương Aero&lt;/color&gt;.
 Một Hoochief non. Chúng chỉ xuất hiện ở Khu Rừng Mờ, giống như những con trưởng thành. Dù không thể so sánh về thể chất, nhưng trí tuệ của chúng không hề thua kém. Những con Hoochief trưởng thành dạy chúng săn mồi và phục kích người đi đường trong rừng.</t>
         </is>
       </c>
@@ -31799,7 +31776,7 @@
       <c r="M458" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Glacio]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; trước &lt;color=#1891e7&gt;Glacio DMG&lt;/color&gt;. 
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; trước &lt;color=#1891e7&gt;Sát Thương Glacio&lt;/color&gt;. 
 Tên khoa học là 'Hoartoise', một Sinh Vật Đột Biến thuộc loài bò sát trên cạn. Nó có tính khí hung dữ, thường khiêu khích và lao vào tấn công những sinh vật to lớn hơn mình. Hành vi này có liên quan đến đột biến hay không vẫn chưa rõ. Ở Huanglong, rùa thường gắn liền với sự điềm tĩnh và tinh tế, ngoại trừ Hoartoise.</t>
         </is>
       </c>
@@ -31868,8 +31845,8 @@
       <c r="M459" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Fusion]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#1891e7&gt;Fusion DMG&lt;/color&gt;.
-Một cá thể Dreadmane thuộc hệ Fusion còn non trẻ. Với thân hình nhỏ hơn, chúng hoàn toàn nghe lời những con Dreadmane trưởng thành. Ở giai đoạn này, bờm của sói con gần giống với sói trưởng thành, giúp chúng tự bảo vệ mình trước các đòn tấn công Fusion. Tuy nhiên, chúng vẫn thiếu kinh nghiệm và kỹ năng săn mồi theo bầy. Những con sói trưởng thành sẽ dạy chúng cách săn mồi, đồng thời bảo vệ chúng. Đôi khi sự bảo vệ đó bao gồm việc chịu những sát thương chí mạng.</t>
+Mục tiêu này có &lt;color=#b49f50&gt;Kháng Fusion DMG cao&lt;/color&gt;. 
+Một cá thể Dreadmane Fusion non. Với thân hình nhỏ hơn, chúng hoàn toàn phục tùng những con trưởng thành. Ở giai đoạn này, bờm của sói con gần giống với sói trưởng thành, giúp chúng tránh được các đòn tấn công Fusion. Tuy nhiên, chúng vẫn thiếu kinh nghiệm và kỹ năng săn mồi theo bầy. Những con trưởng thành sẽ dạy chúng cách săn mồi, đồng thời bảo vệ chúng. Đôi khi sự bảo vệ ấy phải trả giá bằng những vết thương chí mạng.</t>
         </is>
       </c>
     </row>
@@ -31934,7 +31911,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Những Dreadmane Hợp Thể Trẻ có thể Dodge đòn tấn công của kẻ địch ngay cả trước khi chúng ra đòn, dù không phải lúc nào cũng thành công.</t>
+          <t>Những Dreadmane Hợp Thể Trẻ có thể né tránh đòn tấn công của kẻ địch ngay cả trước khi chúng ra đòn, dù không phải lúc nào cũng thành công.</t>
         </is>
       </c>
     </row>
@@ -32002,8 +31979,8 @@
       <c r="M461" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Electro]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#1891e7&gt;Electro DMG&lt;/color&gt;.
-Một phân loài của Ardea purpurea chỉ tìm thấy duy nhất ở Huanglong.</t>
+Mục tiêu này có &lt;color=#b49f50&gt;Kháng Electro DMG cao&lt;/color&gt;. 
+Một phân loài của Ardea purpurea chỉ có ở Huanglong.</t>
         </is>
       </c>
     </row>
@@ -32071,7 +32048,7 @@
       <c r="M462" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Aero]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#1891e7&gt;Aero DMG&lt;/color&gt;.
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; đối với &lt;color=#1891e7&gt;Sát Thương Aero&lt;/color&gt;.
 Diệc Lông Lam ở Huanglong có nghĩa là "vẻ đẹp nguy hiểm".</t>
         </is>
       </c>
@@ -32140,8 +32117,8 @@
       <c r="M463" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Electro]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#1891e7&gt;Electro DMG&lt;/color&gt;.
-Tên nhị thức "Flautist", một thành viên thuộc chi Devorsonidum. Những cây sáo của chúng không bao giờ có thể được thổi. Chúng chỉ là sự bắt chước nghèo nàn hành vi của con người.</t>
+Mục tiêu này có &lt;color=#b49f50&gt;Kháng Electro DMG cao&lt;/color&gt;. 
+Tên nhị thức "Flautist", thuộc chi Devorsonidum. Những chiếc sáo của chúng chẳng bao giờ có thể thổi được. Chúng chỉ là sự bắt chước vụng về hành vi của con người mà thôi.</t>
         </is>
       </c>
     </row>
@@ -32209,7 +32186,7 @@
       <c r="M464" t="inlineStr">
         <is>
           <t>&lt;color=#7e1f57&gt;[Havoc]&lt;/color&gt;
-Mục tiêu có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; trước &lt;color=#7e1f57&gt;Havoc DMG&lt;/color&gt;. 
+Mục tiêu có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; trước &lt;color=#7e1f57&gt;Sát Thương Havoc&lt;/color&gt;. 
 Tacet Discord này có thể kết hợp Năng Lượng Havoc với bộ phận giống "trống lục lạc" và can thiệp vào hành động của người chơi trong chiến đấu.</t>
         </is>
       </c>
@@ -32278,7 +32255,7 @@
       <c r="M465" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Spectro]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#1891e7&gt;Spectro DMG&lt;/color&gt;. 
+Kẻ địch này có &lt;color=#b49f50&gt;kháng cao&lt;/color&gt; đối với &lt;color=#1891e7&gt;Sát Thương Spectro&lt;/color&gt;. 
 Tên khoa học "Devorsonidum spectrum", thuộc chi Devorsonidum. Nếu đến gần, nó có thể đâm sầm và húc mạnh vào người chơi.</t>
         </is>
       </c>
@@ -32412,7 +32389,7 @@
       <c r="M467" t="inlineStr">
         <is>
           <t>&lt;color=#7e1f57&gt;[Havoc]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#7e1f57&gt;Havoc DMG&lt;/color&gt;. 
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; đối với &lt;color=#7e1f57&gt;Sát Thương Havoc&lt;/color&gt;. 
 Tên khoa học "Tambourinist", thuộc chi Devorsonidum. Ngoại hình của nó cho thấy dấu hiệu tiến hóa theo hướng hình người.</t>
         </is>
       </c>
@@ -32546,7 +32523,7 @@
       <c r="M469" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Fusion]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; trước &lt;color=#1891e7&gt;Fusion DMG&lt;/color&gt;. 
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; trước &lt;color=#1891e7&gt;Sát Thương Fusion&lt;/color&gt;. 
 Tên khoa học "Aigialosauridae lapis", một Sinh Vật Đột Biến ăn thịt, sống theo bầy đàn. Con trưởng thành có thể cao gấp 1,5 lần người trưởng thành.</t>
         </is>
       </c>
@@ -32615,7 +32592,7 @@
       <c r="M470" t="inlineStr">
         <is>
           <t>&lt;color=#7e1f57&gt;[Havoc]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#7e1f57&gt;Havoc DMG&lt;/color&gt;. 
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; đối với &lt;color=#7e1f57&gt;Sát Thương Havoc&lt;/color&gt;. 
 Tên khoa học "Agaricus mimicus". Một loài thực vật ưa bóng râm và ưa ẩm, thường tụ tập thành đàn trong các hang động ẩm ướt giàu Tacetite.</t>
         </is>
       </c>
@@ -32749,7 +32726,7 @@
       <c r="M472" t="inlineStr">
         <is>
           <t>&lt;color=#7e1f57&gt;[Havoc]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#7e1f57&gt;Havoc DMG&lt;/color&gt;. 
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; đối với &lt;color=#7e1f57&gt;Sát Thương Havoc&lt;/color&gt;. 
 Tên khoa học ba phần "Chrysocyon brachyurus terreo". Dreadmane trưởng thành có kích thước lớn hơn, hoạt động về đêm và sống theo bầy đàn, với tính xã hội và hung hãn cao.</t>
         </is>
       </c>
@@ -32815,7 +32792,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Dreadmane Đứt Gãy có thể Dodge đòn tấn công của kẻ địch ngay cả trước khi chúng ra đòn, dù không phải lúc nào cũng thành công. Khi chịu đủ sát thương, Dreadmane sẽ bước vào trạng thái cuồng nộ và kích động đồng loại xung quanh bằng tiếng hú. Đồng thời, các đòn tấn công của nó sẽ tạo ra thêm tinh thể năng lượng Havoc để tấn công tầm xa.</t>
+          <t>Dreadmane Đứt Gãy có thể né tránh đòn tấn công của kẻ địch ngay cả trước khi chúng ra đòn, dù không phải lúc nào cũng thành công. Khi chịu đủ sát thương, Dreadmane sẽ bước vào trạng thái cuồng nộ và kích động đồng loại xung quanh bằng tiếng hú. Đồng thời, các đòn tấn công của nó sẽ tạo ra thêm tinh thể năng lượng Havoc để tấn công tầm xa.</t>
         </is>
       </c>
     </row>
@@ -32883,8 +32860,8 @@
       <c r="M474" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Aero]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#1891e7&gt;Aero DMG&lt;/color&gt;. 
-Tên nhị thức "Hoolock vexo". Chúng chỉ được phát hiện tại Dim Forest. Đây là Mutant Organism có mức độ thông minh cao nhất được tìm thấy ở Huanglong.</t>
+Mục tiêu này có &lt;color=#b49f50&gt;Kháng Aero DMG cao&lt;/color&gt;. 
+Tên nhị thức "Hoolock vexo". Chúng chỉ xuất hiện ở Khu Rừng Mờ. Đây là Sinh Vật Đột Biến có trí thông minh cao nhất từng được tìm thấy ở Huanglong.</t>
         </is>
       </c>
     </row>
@@ -33017,8 +32994,8 @@
       <c r="M476" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Aero]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#1891e7&gt;Aero DMG&lt;/color&gt;. 
-Là một phần của loài nhân tạo, chỉ xuất hiện ở Dim Forest. Loại Discord này thường sử dụng các phương tiện bị bỏ hoang làm vỏ bọc và di chuyển nhanh chóng. Một khi đã nhắm mục tiêu, nó sẽ không bao giờ từ bỏ, do đó có tên gọi là "Carapace".</t>
+Mục tiêu này có &lt;color=#b49f50&gt;Kháng Aero DMG cao&lt;/color&gt;. 
+Thuộc loài nhân tạo, chỉ xuất hiện ở Khu Rừng Mờ. Loài Tacet Discord này thường chiếm dụng các phương tiện bị bỏ hoang làm vỏ bọc và di chuyển rất nhanh. Một khi đã nhắm được con mồi, chúng sẽ không bao giờ từ bỏ, vì vậy mới có tên là "Carapace".</t>
         </is>
       </c>
     </row>
@@ -33086,8 +33063,8 @@
       <c r="M477" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Havoc]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#7e1f57&gt;Havoc DMG&lt;/color&gt;.
-Những thủ lĩnh Lưu Đày. Chủ yếu là Resonators. Tại khu vực Huanglong, chẳng hạn, các thủ lĩnh Lưu Đày thường là những người bị trục xuất khỏi Mornguard vì nhiều lý do khác nhau, nên kinh nghiệm chiến đấu và khả năng của họ vượt xa những kẻ Lưu Đày thông thường.</t>
+Kẻ địch này có &lt;color=#b49f50&gt;kháng cao&lt;/color&gt; đối với &lt;color=#7e1f57&gt;Sát Thương Havoc&lt;/color&gt;. 
+Những thủ lĩnh Lưu Đày. Chủ yếu là Resonator. Ở vùng Huanglong chẳng hạn, thủ lĩnh Lưu Đày thường là những kẻ bị trục xuất khỏi Mornguard vì nhiều lý do, nên kinh nghiệm chiến đấu và khả năng của họ vượt xa những Lưu Đày bình thường.</t>
         </is>
       </c>
     </row>
@@ -33152,7 +33129,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Sau khi chịu một lượng sát thương nhất định, nỗi đau và cơn thịnh nộ sẽ khiến Exile Trưởng tăng đáng kể ham muốn tấn công.</t>
+          <t>Sau khi chịu một lượng sát thương nhất định, nỗi đau và cơn thịnh nộ sẽ khiến Kẻ Lưu Đày Trưởng tăng đáng kể ham muốn tấn công.</t>
         </is>
       </c>
     </row>
@@ -33220,7 +33197,7 @@
       <c r="M479" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Spectro]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#1891e7&gt;Spectro DMG&lt;/color&gt;. 
+Kẻ địch này có &lt;color=#b49f50&gt;kháng cao&lt;/color&gt; đối với &lt;color=#1891e7&gt;Sát Thương Spectro&lt;/color&gt;. 
 Những Lưu Đày lão luyện đảm nhận vai trò sĩ quan và thợ máy trong đội. Vẻ ngoài mảnh khảnh của họ có thể bị hiểu nhầm là thiếu khả năng chiến đấu, nhưng những kẻ có suy nghĩ đó chắc chắn sẽ phải trả giá đắt.</t>
         </is>
       </c>
@@ -33286,7 +33263,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Exile Technician có thể bảo vệ đồng đội bằng khiên và tăng cường khiên sau khi hứng chịu một lượng sát thương nhất định.</t>
+          <t>Kỹ Sư Lưu Đày có thể bảo vệ đồng đội bằng khiên và tăng cường khiên sau khi hứng chịu một lượng sát thương nhất định.</t>
         </is>
       </c>
     </row>
@@ -33354,8 +33331,8 @@
       <c r="M481" t="inlineStr">
         <is>
           <t>&lt;color=#7e1f57&gt;[Havoc]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#7e1f57&gt;Havoc DMG&lt;/color&gt;.
-Các thành viên của đơn vị Executioner đều là Resonators được huấn luyện khắc nghiệt. Khi khoác lên mình mặt nạ và áo choàng, họ đã từ bỏ bản ngã cũ và cống hiến cho "Bóng Ma Vô Diện". Những Executioner sống sót qua vô số trận chiến sẽ có cơ hội được thăng cấp.</t>
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; đối với &lt;color=#7e1f57&gt;Sát Thương Havoc&lt;/color&gt;.
+Các thành viên của đơn vị Executioner đều là Resonator được huấn luyện khắc nghiệt. Khi khoác lên mình mặt nạ và áo choàng, họ đã từ bỏ bản ngã cũ và cống hiến cho "Bóng Ma Vô Diện". Những Executioner sống sót qua vô số trận chiến sẽ có cơ hội được thăng cấp.</t>
         </is>
       </c>
     </row>
@@ -33488,8 +33465,8 @@
       <c r="M483" t="inlineStr">
         <is>
           <t>&lt;color=#9656d8&gt;[Electro]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#9656d8&gt;Electro DMG&lt;/color&gt;. 
-Thundering Mephis có hình dạng giống sự kết hợp giữa người và thằn lằn. Nó có thể sử dụng Wutheron trong Tacet Field để thực hiện các động tác cơ động tốc độ cao.</t>
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng Electro cao hơn&lt;/color&gt;. 
+Thundering Mephis trông như sự kết hợp giữa người và thằn lằn. Nó có thể sử dụng Wutheron trong Tổ Tacet để di chuyển tốc độ cao.</t>
         </is>
       </c>
     </row>
@@ -33622,7 +33599,7 @@
       <c r="M485" t="inlineStr">
         <is>
           <t>&lt;color=#e15226&gt;[Fusion]&lt;/color&gt; 
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#e15226&gt;Fusion DMG&lt;/color&gt;. 
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; đối với &lt;color=#e15226&gt;Sát Thương Fusion&lt;/color&gt;. 
 Tacet Discord thường không cần "phương tiện" để di chuyển, nhưng hình dạng của Inferno Rider lại giống một tay đua trên xe máy. Có lẽ hình dạng này bắt nguồn từ sự bắt chước vụng về hành vi của con người.&lt;/color&gt;</t>
         </is>
       </c>
@@ -33691,8 +33668,8 @@
       <c r="M486" t="inlineStr">
         <is>
           <t>&lt;color=#7e1f57&gt;[Havoc]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#7e1f57&gt;Havoc DMG&lt;/color&gt;. 
-"Impermanence Heron ba đầu" không phải là miêu tả chính xác về con quái thú này. Mặc dù hệ thần kinh của từng đầu hoạt động độc lập, nhưng hai "đầu" ở hai bên được cho là các cơ quan đột biến để bảo vệ não chính. Khi tình thế nguy cấp, "đầu" chính sẽ nuốt chửng hai đầu còn lại để tăng cường khả năng chiến đấu.</t>
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; đối với &lt;color=#7e1f57&gt;Sát Thương Havoc&lt;/color&gt;. 
+"Diệc Vô Thường ba đầu" không phải là miêu tả chính xác về con quái thú này. Mặc dù hệ thần kinh của từng đầu hoạt động độc lập, nhưng hai "đầu" ở hai bên được cho là các cơ quan đột biến để bảo vệ não chính. Khi tình thế nguy cấp, "đầu" chính sẽ nuốt chửng hai đầu còn lại để tăng cường khả năng chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -33760,8 +33737,8 @@
       <c r="M487" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Glacio]&lt;/color&gt; 
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#1891e7&gt;Glacio DMG&lt;/color&gt;.
-Lampylumen Myriad là tập hợp của những Echo nhỏ giống côn trùng gọi là "Glowflies", cực kỳ nhạy cảm với các tần số âm thanh khác nhau. Chúng có thể xác định vị trí con mồi qua âm thanh hoặc hấp thụ và bắt chước tần số của chúng. Cái kén của chúng được cho là bắt chước hình dạng của các sinh vật côn trùng.</t>
+Kẻ địch này có &lt;color=#b49f50&gt;kháng cao&lt;/color&gt; đối với &lt;color=#1891e7&gt;Sát Thương Glacio&lt;/color&gt;.
+Lampylumen Myriad là tập hợp của những Tổ Tacet nhỏ giống côn trùng gọi là "Glowflies", cực kỳ nhạy cảm với các tần số âm thanh khác nhau. Chúng có thể xác định vị trí con mồi qua âm thanh hoặc hấp thụ và bắt chước tần số của chúng. Cái kén của chúng được cho là bắt chước hình dạng của các sinh vật côn trùng.</t>
         </is>
       </c>
     </row>
@@ -33826,7 +33803,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Discord này dựa vào kén dưới đất để duy trì bay lượn. Khi bay, nó sử dụng ánh sáng huỳnh quang để xác định mục tiêu và tấn công tầm xa. Phá hủy các kén dưới đất có thể khiến nó rơi xuống. Tấn công vào đuôi – điểm yếu khác của nó – cũng có thể hạ gục nó.</t>
+          <t>Tacet Discord này dựa vào kén dưới đất để duy trì bay lượn. Khi bay, nó sử dụng ánh sáng huỳnh quang để xác định mục tiêu và tấn công tầm xa. Phá hủy các kén dưới đất có thể khiến nó rơi xuống. Tấn công vào đuôi – điểm yếu khác của nó – cũng có thể hạ gục nó.</t>
         </is>
       </c>
     </row>
@@ -33894,7 +33871,7 @@
       <c r="M489" t="inlineStr">
         <is>
           <t>&lt;color=#46c3d4&gt;[Aero]&lt;/color&gt; 
-Kẻ địch này có &lt;color=#46c3d4&gt;higher RES&lt;/color&gt; đối với &lt;color=#46c3d4&gt;Aero DMG&lt;/color&gt;. 
+Kẻ địch này có &lt;color=#46c3d4&gt;Kháng cao&lt;/color&gt; đối với &lt;color=#46c3d4&gt;Sát Thương Aero&lt;/color&gt;. 
 Từng là trò tiêu khiển của con người, sau trở thành mục tiêu tấn công và cuối cùng là mối phiền toái, Felilian Beringal bị giam cầm trong rừng. Nhưng nó đã biến cột trói buộc mình thành vũ khí và trở thành kẻ thống trị bầy Hoochief. Giờ đây, nó trút lại những gì con người đã làm lên những kẻ bị khỉ bắt giữ.</t>
         </is>
       </c>
@@ -33963,8 +33940,8 @@
       <c r="M490" t="inlineStr">
         <is>
           <t>&lt;color=#d4bf5f&gt;[Spectro]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;high RES&lt;/color&gt; đối với &lt;color=#d4bf5f&gt;Spectro DMG&lt;/color&gt;.
-Mourning Aix có hình dáng thanh thoát, trông như một loài chim. Ban đầu chúng sống thành từng cặp, nhưng con còn lại đã bị con người đánh bại, xác của nó tạo thành một "trụ cột" nơi Mourning Aix làm tổ. "Trụ cột" này sẽ hỗ trợ tấn công theo tiếng kêu của Mourning Aix. Điều này được suy đoán là một dạng đồng tiến hóa của Echo.</t>
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; đối với &lt;color=#d4bf5f&gt;Sát Thương Spectro&lt;/color&gt;.
+Mourning Aix có hình dáng thanh thoát, trông như một loài chim. Ban đầu chúng sống thành từng cặp, nhưng con còn lại đã bị con người đánh bại, xác của nó tạo thành một "trụ cột" nơi Mourning Aix làm tổ. "Trụ cột" này sẽ hỗ trợ tấn công theo tiếng kêu của Mourning Aix. Điều này được suy đoán là một dạng đồng tiến hóa của Tổ Tacet.</t>
         </is>
       </c>
     </row>
@@ -34097,8 +34074,8 @@
       <c r="M492" t="inlineStr">
         <is>
           <t>&lt;color=#7e1f57&gt;[Havoc]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#7e1f57&gt;Havoc DMG&lt;/color&gt;. 
-Một bản sao của "Crownless" đến từ Threnody. Về ngoại hình, nó giống một hiệp sĩ mặc giáp trắng, và khi sức mạnh tăng lên, đôi cánh đỏ như máu sẽ giương ra—có lẽ nhờ khả năng điều khiển tạm thời cấu trúc Wutheron trong cơ thể, giúp tăng cường khả năng di chuyển và Tấn Công ngay lập tức. Gần đây, người ta còn quan sát thấy nó có thể tạo ra cấu trúc cơ thể mô phỏng "vũ khí" của con người. Không ai biết nó có thể đột biến đến mức nào, nhưng chắc chắn một điều: nó thuộc hệ Havoc, trái ngược hoàn toàn với vẻ ngoài.</t>
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; đối với &lt;color=#7e1f57&gt;Sát Thương Havoc&lt;/color&gt;. 
+Một bản sao của "Crownless" đến từ Threnody. Về ngoại hình, nó giống một hiệp sĩ mặc giáp trắng, và khi sức mạnh tăng lên, đôi cánh đỏ như máu sẽ giương ra—có lẽ nhờ khả năng điều khiển tạm thời cấu trúc Wutheron trong cơ thể, giúp tăng cường khả năng di chuyển và ATK ngay lập tức. Gần đây, người ta còn quan sát thấy nó có thể tạo ra cấu trúc cơ thể mô phỏng "vũ khí" của con người. Không ai biết nó có thể đột biến đến mức nào, nhưng chắc chắn một điều: nó thuộc hệ Havoc, trái ngược hoàn toàn với vẻ ngoài.</t>
         </is>
       </c>
     </row>
@@ -34166,7 +34143,7 @@
       <c r="M493" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Glacio]&lt;/color&gt; 
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#1891e7&gt;Glacio DMG&lt;/color&gt;. 
+Kẻ địch này có &lt;color=#b49f50&gt;kháng cao&lt;/color&gt; đối với &lt;color=#1891e7&gt;Sát Thương Glacio&lt;/color&gt;. 
 Chiếc chuông cổ trên lưng Geochelone che giấu lõi Tacetreite của nó. Khi bị đánh trúng, chuông sẽ cộng hưởng với lõi, tạo ra một làn sóng âm thanh năng lượng Glacio. Lưu ý rằng sóng âm này có thể gây tổn thương vĩnh viễn vùng Broca trong não người, dẫn đến mất ngôn ngữ vĩnh viễn.</t>
         </is>
       </c>
@@ -34232,7 +34209,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Tăng Sát Thương Physical</t>
+          <t>ATK | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Tăng Sát Thương Vật Lý</t>
         </is>
       </c>
     </row>
@@ -34297,7 +34274,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Summon Vanguard Junrock lao về phía trước, gây Sát Thương vật lý cho kẻ địch trên đường đi.</t>
+          <t>Triệu hồi Tiền Phong Junrock lao về phía trước, gây Sát Thương vật lý cho kẻ địch trên đường đi.</t>
         </is>
       </c>
     </row>
@@ -34427,7 +34404,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Tăng Sát Thương Physical</t>
+          <t>ATK | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Tăng Sát Thương Vật Lý</t>
         </is>
       </c>
     </row>
@@ -34557,7 +34534,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>[Tấn Công] [HP] [Phòng Ngự] [Crit. DMG] [Energy Regen] [Electro DMG Bonus]</t>
+          <t>[ATK] [HP] [Phòng Ngự] [Crit. DMG] [Hồi Năng Lượng] [Tăng Sát Thương Electro]</t>
         </is>
       </c>
     </row>
@@ -34622,7 +34599,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Summon Kẻ Săn Mồi Điện để bắn mưa tên, mỗi mũi tên gây Sát Thương Điện.</t>
+          <t>Triệu hồi Kẻ Săn Mồi Điện để bắn mưa tên, mỗi mũi tên gây Sát Thương Điện.</t>
         </is>
       </c>
     </row>
@@ -34687,7 +34664,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
